--- a/output/yearly_population_iteration_4_growth_param_0.5.xlsx
+++ b/output/yearly_population_iteration_4_growth_param_0.5.xlsx
@@ -780,13 +780,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4000</v>
+        <v>6172</v>
       </c>
       <c r="C2" t="n">
-        <v>5559</v>
+        <v>8171</v>
       </c>
       <c r="D2" t="n">
-        <v>24988</v>
+        <v>22459</v>
       </c>
     </row>
     <row r="3">
@@ -794,13 +794,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2986</v>
+        <v>3564</v>
       </c>
       <c r="C3" t="n">
-        <v>7441</v>
+        <v>6681</v>
       </c>
       <c r="D3" t="n">
-        <v>16720</v>
+        <v>14096</v>
       </c>
     </row>
     <row r="4">
@@ -808,13 +808,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2624</v>
+        <v>2797</v>
       </c>
       <c r="C4" t="n">
-        <v>6549</v>
+        <v>5200</v>
       </c>
       <c r="D4" t="n">
-        <v>8961</v>
+        <v>6433</v>
       </c>
     </row>
     <row r="5">
@@ -822,13 +822,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1801</v>
+        <v>1873</v>
       </c>
       <c r="C5" t="n">
-        <v>5299</v>
+        <v>4697</v>
       </c>
       <c r="D5" t="n">
-        <v>3498</v>
+        <v>2328</v>
       </c>
     </row>
     <row r="6">
@@ -836,13 +836,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>973</v>
+        <v>1103</v>
       </c>
       <c r="C6" t="n">
-        <v>3389</v>
+        <v>3924</v>
       </c>
       <c r="D6" t="n">
-        <v>1377</v>
+        <v>1028</v>
       </c>
     </row>
     <row r="7">
@@ -850,13 +850,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>432</v>
+        <v>528</v>
       </c>
       <c r="C7" t="n">
-        <v>1766</v>
+        <v>2658</v>
       </c>
       <c r="D7" t="n">
-        <v>683</v>
+        <v>626</v>
       </c>
     </row>
     <row r="8">
@@ -864,13 +864,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>155</v>
+        <v>202</v>
       </c>
       <c r="C8" t="n">
-        <v>765</v>
+        <v>1269</v>
       </c>
       <c r="D8" t="n">
-        <v>435</v>
+        <v>426</v>
       </c>
     </row>
     <row r="9">
@@ -878,13 +878,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>63</v>
+        <v>73</v>
       </c>
       <c r="C9" t="n">
-        <v>342</v>
+        <v>484</v>
       </c>
       <c r="D9" t="n">
-        <v>307</v>
+        <v>301</v>
       </c>
     </row>
     <row r="10">
@@ -895,7 +895,7 @@
         <v>38</v>
       </c>
       <c r="C10" t="n">
-        <v>208</v>
+        <v>228</v>
       </c>
       <c r="D10" t="n">
         <v>245</v>
@@ -906,10 +906,10 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C11" t="n">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="D11" t="n">
         <v>201</v>
@@ -923,10 +923,10 @@
         <v>17</v>
       </c>
       <c r="C12" t="n">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="D12" t="n">
-        <v>162</v>
+        <v>159</v>
       </c>
     </row>
     <row r="13">
@@ -937,7 +937,7 @@
         <v>11</v>
       </c>
       <c r="C13" t="n">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="D13" t="n">
         <v>124</v>
@@ -951,10 +951,10 @@
         <v>6</v>
       </c>
       <c r="C14" t="n">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D14" t="n">
-        <v>99</v>
+        <v>97</v>
       </c>
     </row>
     <row r="15">
@@ -962,10 +962,10 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C15" t="n">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D15" t="n">
         <v>82</v>
@@ -996,7 +996,7 @@
         <v>38</v>
       </c>
       <c r="D17" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="18">
@@ -1007,10 +1007,10 @@
         <v>1</v>
       </c>
       <c r="C18" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D18" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="19">
@@ -1024,7 +1024,7 @@
         <v>31</v>
       </c>
       <c r="D19" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="20">
@@ -1049,7 +1049,7 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="D21" t="n">
         <v>8</v>
@@ -1091,13 +1091,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4958</v>
+        <v>7038</v>
       </c>
       <c r="C2" t="n">
-        <v>10766</v>
+        <v>7871</v>
       </c>
       <c r="D2" t="n">
-        <v>26397</v>
+        <v>23497</v>
       </c>
     </row>
     <row r="3">
@@ -1105,13 +1105,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2806</v>
+        <v>3796</v>
       </c>
       <c r="C3" t="n">
-        <v>5849</v>
+        <v>6472</v>
       </c>
       <c r="D3" t="n">
-        <v>16681</v>
+        <v>14241</v>
       </c>
     </row>
     <row r="4">
@@ -1119,13 +1119,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2381</v>
+        <v>2668</v>
       </c>
       <c r="C4" t="n">
-        <v>6760</v>
+        <v>5774</v>
       </c>
       <c r="D4" t="n">
-        <v>9794</v>
+        <v>7352</v>
       </c>
     </row>
     <row r="5">
@@ -1133,13 +1133,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1903</v>
+        <v>2019</v>
       </c>
       <c r="C5" t="n">
-        <v>5752</v>
+        <v>4776</v>
       </c>
       <c r="D5" t="n">
-        <v>4230</v>
+        <v>2887</v>
       </c>
     </row>
     <row r="6">
@@ -1147,13 +1147,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1207</v>
+        <v>1292</v>
       </c>
       <c r="C6" t="n">
-        <v>4149</v>
+        <v>4182</v>
       </c>
       <c r="D6" t="n">
-        <v>1650</v>
+        <v>1191</v>
       </c>
     </row>
     <row r="7">
@@ -1161,13 +1161,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>583</v>
+        <v>684</v>
       </c>
       <c r="C7" t="n">
-        <v>2447</v>
+        <v>3202</v>
       </c>
       <c r="D7" t="n">
-        <v>778</v>
+        <v>678</v>
       </c>
     </row>
     <row r="8">
@@ -1175,13 +1175,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>234</v>
+        <v>293</v>
       </c>
       <c r="C8" t="n">
-        <v>1186</v>
+        <v>1827</v>
       </c>
       <c r="D8" t="n">
-        <v>460</v>
+        <v>444</v>
       </c>
     </row>
     <row r="9">
@@ -1189,13 +1189,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>87</v>
+        <v>109</v>
       </c>
       <c r="C9" t="n">
-        <v>508</v>
+        <v>799</v>
       </c>
       <c r="D9" t="n">
-        <v>321</v>
+        <v>315</v>
       </c>
     </row>
     <row r="10">
@@ -1203,10 +1203,10 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="C10" t="n">
-        <v>260</v>
+        <v>323</v>
       </c>
       <c r="D10" t="n">
         <v>247</v>
@@ -1220,7 +1220,7 @@
         <v>27</v>
       </c>
       <c r="C11" t="n">
-        <v>178</v>
+        <v>185</v>
       </c>
       <c r="D11" t="n">
         <v>204</v>
@@ -1234,10 +1234,10 @@
         <v>18</v>
       </c>
       <c r="C12" t="n">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="D12" t="n">
-        <v>163</v>
+        <v>160</v>
       </c>
     </row>
     <row r="13">
@@ -1251,7 +1251,7 @@
         <v>106</v>
       </c>
       <c r="D13" t="n">
-        <v>127</v>
+        <v>126</v>
       </c>
     </row>
     <row r="14">
@@ -1262,10 +1262,10 @@
         <v>6</v>
       </c>
       <c r="C14" t="n">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="D14" t="n">
-        <v>99</v>
+        <v>97</v>
       </c>
     </row>
     <row r="15">
@@ -1273,10 +1273,10 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C15" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D15" t="n">
         <v>82</v>
@@ -1287,7 +1287,7 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C16" t="n">
         <v>49</v>
@@ -1307,7 +1307,7 @@
         <v>39</v>
       </c>
       <c r="D17" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="18">
@@ -1318,10 +1318,10 @@
         <v>1</v>
       </c>
       <c r="C18" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D18" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="19">
@@ -1335,7 +1335,7 @@
         <v>31</v>
       </c>
       <c r="D19" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="20">
@@ -1360,7 +1360,7 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="D21" t="n">
         <v>9</v>
@@ -1402,13 +1402,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6092</v>
+        <v>7251</v>
       </c>
       <c r="C2" t="n">
-        <v>19376</v>
+        <v>10172</v>
       </c>
       <c r="D2" t="n">
-        <v>25685</v>
+        <v>27844</v>
       </c>
     </row>
     <row r="3">
@@ -1416,13 +1416,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2973</v>
+        <v>4096</v>
       </c>
       <c r="C3" t="n">
-        <v>6934</v>
+        <v>6312</v>
       </c>
       <c r="D3" t="n">
-        <v>16779</v>
+        <v>14440</v>
       </c>
     </row>
     <row r="4">
@@ -1430,13 +1430,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2203</v>
+        <v>2641</v>
       </c>
       <c r="C4" t="n">
-        <v>6169</v>
+        <v>5886</v>
       </c>
       <c r="D4" t="n">
-        <v>10487</v>
+        <v>8120</v>
       </c>
     </row>
     <row r="5">
@@ -1444,13 +1444,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1870</v>
+        <v>2026</v>
       </c>
       <c r="C5" t="n">
-        <v>6048</v>
+        <v>5033</v>
       </c>
       <c r="D5" t="n">
-        <v>4808</v>
+        <v>3371</v>
       </c>
     </row>
     <row r="6">
@@ -1458,13 +1458,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1345</v>
+        <v>1434</v>
       </c>
       <c r="C6" t="n">
-        <v>4703</v>
+        <v>4338</v>
       </c>
       <c r="D6" t="n">
-        <v>1959</v>
+        <v>1403</v>
       </c>
     </row>
     <row r="7">
@@ -1472,13 +1472,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>734</v>
+        <v>823</v>
       </c>
       <c r="C7" t="n">
-        <v>3089</v>
+        <v>3584</v>
       </c>
       <c r="D7" t="n">
-        <v>889</v>
+        <v>729</v>
       </c>
     </row>
     <row r="8">
@@ -1486,13 +1486,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>321</v>
+        <v>391</v>
       </c>
       <c r="C8" t="n">
-        <v>1667</v>
+        <v>2320</v>
       </c>
       <c r="D8" t="n">
-        <v>491</v>
+        <v>464</v>
       </c>
     </row>
     <row r="9">
@@ -1500,13 +1500,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>123</v>
+        <v>152</v>
       </c>
       <c r="C9" t="n">
-        <v>748</v>
+        <v>1163</v>
       </c>
       <c r="D9" t="n">
-        <v>335</v>
+        <v>328</v>
       </c>
     </row>
     <row r="10">
@@ -1514,10 +1514,10 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>52</v>
+        <v>59</v>
       </c>
       <c r="C10" t="n">
-        <v>344</v>
+        <v>490</v>
       </c>
       <c r="D10" t="n">
         <v>250</v>
@@ -1531,7 +1531,7 @@
         <v>29</v>
       </c>
       <c r="C11" t="n">
-        <v>206</v>
+        <v>229</v>
       </c>
       <c r="D11" t="n">
         <v>206</v>
@@ -1545,10 +1545,10 @@
         <v>19</v>
       </c>
       <c r="C12" t="n">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="D12" t="n">
-        <v>164</v>
+        <v>161</v>
       </c>
     </row>
     <row r="13">
@@ -1562,7 +1562,7 @@
         <v>115</v>
       </c>
       <c r="D13" t="n">
-        <v>129</v>
+        <v>128</v>
       </c>
     </row>
     <row r="14">
@@ -1573,10 +1573,10 @@
         <v>6</v>
       </c>
       <c r="C14" t="n">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="D14" t="n">
-        <v>99</v>
+        <v>97</v>
       </c>
     </row>
     <row r="15">
@@ -1584,10 +1584,10 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C15" t="n">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="D15" t="n">
         <v>82</v>
@@ -1598,7 +1598,7 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C16" t="n">
         <v>52</v>
@@ -1612,13 +1612,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C17" t="n">
         <v>41</v>
       </c>
       <c r="D17" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="18">
@@ -1629,10 +1629,10 @@
         <v>1</v>
       </c>
       <c r="C18" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D18" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="19">
@@ -1646,7 +1646,7 @@
         <v>31</v>
       </c>
       <c r="D19" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="20">
@@ -1671,7 +1671,7 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="D21" t="n">
         <v>10</v>
@@ -1713,13 +1713,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5564</v>
+        <v>6751</v>
       </c>
       <c r="C2" t="n">
-        <v>13485</v>
+        <v>7079</v>
       </c>
       <c r="D2" t="n">
-        <v>21353</v>
+        <v>22968</v>
       </c>
     </row>
     <row r="3">
@@ -1727,13 +1727,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3726</v>
+        <v>4797</v>
       </c>
       <c r="C3" t="n">
-        <v>11277</v>
+        <v>9603</v>
       </c>
       <c r="D3" t="n">
-        <v>18524</v>
+        <v>15663</v>
       </c>
     </row>
     <row r="4">
@@ -1741,13 +1741,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1727</v>
+        <v>1872</v>
       </c>
       <c r="C4" t="n">
-        <v>9122</v>
+        <v>7995</v>
       </c>
       <c r="D4" t="n">
-        <v>10169</v>
+        <v>7630</v>
       </c>
     </row>
     <row r="5">
@@ -1755,13 +1755,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1242</v>
+        <v>1325</v>
       </c>
       <c r="C5" t="n">
-        <v>4608</v>
+        <v>4251</v>
       </c>
       <c r="D5" t="n">
-        <v>3212</v>
+        <v>2281</v>
       </c>
     </row>
     <row r="6">
@@ -1769,13 +1769,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>678</v>
+        <v>760</v>
       </c>
       <c r="C6" t="n">
-        <v>3027</v>
+        <v>3512</v>
       </c>
       <c r="D6" t="n">
-        <v>871</v>
+        <v>714</v>
       </c>
     </row>
     <row r="7">
@@ -1783,13 +1783,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>296</v>
+        <v>361</v>
       </c>
       <c r="C7" t="n">
-        <v>1633</v>
+        <v>2273</v>
       </c>
       <c r="D7" t="n">
-        <v>481</v>
+        <v>454</v>
       </c>
     </row>
     <row r="8">
@@ -1797,13 +1797,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>113</v>
+        <v>140</v>
       </c>
       <c r="C8" t="n">
-        <v>733</v>
+        <v>1139</v>
       </c>
       <c r="D8" t="n">
-        <v>328</v>
+        <v>321</v>
       </c>
     </row>
     <row r="9">
@@ -1811,10 +1811,10 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="C9" t="n">
-        <v>337</v>
+        <v>480</v>
       </c>
       <c r="D9" t="n">
         <v>245</v>
@@ -1828,7 +1828,7 @@
         <v>26</v>
       </c>
       <c r="C10" t="n">
-        <v>201</v>
+        <v>224</v>
       </c>
       <c r="D10" t="n">
         <v>201</v>
@@ -1845,7 +1845,7 @@
         <v>147</v>
       </c>
       <c r="D11" t="n">
-        <v>160</v>
+        <v>157</v>
       </c>
     </row>
     <row r="12">
@@ -1859,7 +1859,7 @@
         <v>112</v>
       </c>
       <c r="D12" t="n">
-        <v>126</v>
+        <v>125</v>
       </c>
     </row>
     <row r="13">
@@ -1870,10 +1870,10 @@
         <v>5</v>
       </c>
       <c r="C13" t="n">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="D13" t="n">
-        <v>97</v>
+        <v>95</v>
       </c>
     </row>
     <row r="14">
@@ -1881,10 +1881,10 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C14" t="n">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="D14" t="n">
         <v>80</v>
@@ -1895,7 +1895,7 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C15" t="n">
         <v>50</v>
@@ -1909,13 +1909,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C16" t="n">
         <v>40</v>
       </c>
       <c r="D16" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="17">
@@ -1926,10 +1926,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D17" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="18">
@@ -1943,7 +1943,7 @@
         <v>30</v>
       </c>
       <c r="D18" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="19">
@@ -1968,7 +1968,7 @@
         <v>8</v>
       </c>
       <c r="C20" t="n">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="D20" t="n">
         <v>10</v>
@@ -2024,13 +2024,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3538</v>
+        <v>4153</v>
       </c>
       <c r="C2" t="n">
-        <v>6057</v>
+        <v>3132</v>
       </c>
       <c r="D2" t="n">
-        <v>15058</v>
+        <v>16370</v>
       </c>
     </row>
     <row r="3">
@@ -2038,13 +2038,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3862</v>
+        <v>4844</v>
       </c>
       <c r="C3" t="n">
-        <v>11131</v>
+        <v>7717</v>
       </c>
       <c r="D3" t="n">
-        <v>18019</v>
+        <v>15904</v>
       </c>
     </row>
     <row r="4">
@@ -2052,13 +2052,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2165</v>
+        <v>2560</v>
       </c>
       <c r="C4" t="n">
-        <v>10167</v>
+        <v>8861</v>
       </c>
       <c r="D4" t="n">
-        <v>11160</v>
+        <v>8701</v>
       </c>
     </row>
     <row r="5">
@@ -2066,13 +2066,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1363</v>
+        <v>1460</v>
       </c>
       <c r="C5" t="n">
-        <v>6553</v>
+        <v>5799</v>
       </c>
       <c r="D5" t="n">
-        <v>4075</v>
+        <v>2871</v>
       </c>
     </row>
     <row r="6">
@@ -2080,13 +2080,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>797</v>
+        <v>889</v>
       </c>
       <c r="C6" t="n">
-        <v>3743</v>
+        <v>3975</v>
       </c>
       <c r="D6" t="n">
-        <v>1088</v>
+        <v>861</v>
       </c>
     </row>
     <row r="7">
@@ -2094,13 +2094,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>277</v>
+        <v>338</v>
       </c>
       <c r="C7" t="n">
-        <v>2115</v>
+        <v>2765</v>
       </c>
       <c r="D7" t="n">
-        <v>526</v>
+        <v>492</v>
       </c>
     </row>
     <row r="8">
@@ -2108,13 +2108,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>95</v>
+        <v>116</v>
       </c>
       <c r="C8" t="n">
-        <v>989</v>
+        <v>1492</v>
       </c>
       <c r="D8" t="n">
-        <v>337</v>
+        <v>330</v>
       </c>
     </row>
     <row r="9">
@@ -2122,10 +2122,10 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C9" t="n">
-        <v>372</v>
+        <v>514</v>
       </c>
       <c r="D9" t="n">
         <v>256</v>
@@ -2139,10 +2139,10 @@
         <v>15</v>
       </c>
       <c r="C10" t="n">
-        <v>220</v>
+        <v>236</v>
       </c>
       <c r="D10" t="n">
-        <v>208</v>
+        <v>207</v>
       </c>
     </row>
     <row r="11">
@@ -2156,7 +2156,7 @@
         <v>163</v>
       </c>
       <c r="D11" t="n">
-        <v>167</v>
+        <v>164</v>
       </c>
     </row>
     <row r="12">
@@ -2167,10 +2167,10 @@
         <v>4</v>
       </c>
       <c r="C12" t="n">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="D12" t="n">
-        <v>130</v>
+        <v>128</v>
       </c>
     </row>
     <row r="13">
@@ -2178,13 +2178,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C13" t="n">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="D13" t="n">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="14">
@@ -2192,7 +2192,7 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C14" t="n">
         <v>49</v>
@@ -2212,7 +2212,7 @@
         <v>39</v>
       </c>
       <c r="D15" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="16">
@@ -2223,10 +2223,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D16" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="17">
@@ -2240,7 +2240,7 @@
         <v>29</v>
       </c>
       <c r="D17" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="18">
@@ -2265,7 +2265,7 @@
         <v>7</v>
       </c>
       <c r="C19" t="n">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="D19" t="n">
         <v>9</v>
@@ -2335,13 +2335,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3283</v>
+        <v>4065</v>
       </c>
       <c r="C2" t="n">
-        <v>11080</v>
+        <v>4332</v>
       </c>
       <c r="D2" t="n">
-        <v>17047</v>
+        <v>16861</v>
       </c>
     </row>
     <row r="3">
@@ -2349,13 +2349,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3134</v>
+        <v>3871</v>
       </c>
       <c r="C3" t="n">
-        <v>7765</v>
+        <v>4956</v>
       </c>
       <c r="D3" t="n">
-        <v>16405</v>
+        <v>14898</v>
       </c>
     </row>
     <row r="4">
@@ -2363,13 +2363,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2459</v>
+        <v>3003</v>
       </c>
       <c r="C4" t="n">
-        <v>10515</v>
+        <v>8127</v>
       </c>
       <c r="D4" t="n">
-        <v>11940</v>
+        <v>9612</v>
       </c>
     </row>
     <row r="5">
@@ -2377,13 +2377,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1519</v>
+        <v>1705</v>
       </c>
       <c r="C5" t="n">
-        <v>8047</v>
+        <v>7145</v>
       </c>
       <c r="D5" t="n">
-        <v>5039</v>
+        <v>3679</v>
       </c>
     </row>
     <row r="6">
@@ -2391,13 +2391,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>948</v>
+        <v>1038</v>
       </c>
       <c r="C6" t="n">
-        <v>4921</v>
+        <v>4725</v>
       </c>
       <c r="D6" t="n">
-        <v>1503</v>
+        <v>1139</v>
       </c>
     </row>
     <row r="7">
@@ -2405,13 +2405,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>412</v>
+        <v>479</v>
       </c>
       <c r="C7" t="n">
-        <v>2820</v>
+        <v>3300</v>
       </c>
       <c r="D7" t="n">
-        <v>597</v>
+        <v>537</v>
       </c>
     </row>
     <row r="8">
@@ -2419,13 +2419,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>139</v>
+        <v>168</v>
       </c>
       <c r="C8" t="n">
-        <v>1439</v>
+        <v>2005</v>
       </c>
       <c r="D8" t="n">
-        <v>357</v>
+        <v>347</v>
       </c>
     </row>
     <row r="9">
@@ -2433,13 +2433,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="C9" t="n">
-        <v>599</v>
+        <v>873</v>
       </c>
       <c r="D9" t="n">
-        <v>265</v>
+        <v>264</v>
       </c>
     </row>
     <row r="10">
@@ -2450,10 +2450,10 @@
         <v>19</v>
       </c>
       <c r="C10" t="n">
-        <v>274</v>
+        <v>333</v>
       </c>
       <c r="D10" t="n">
-        <v>212</v>
+        <v>209</v>
       </c>
     </row>
     <row r="11">
@@ -2464,10 +2464,10 @@
         <v>9</v>
       </c>
       <c r="C11" t="n">
-        <v>182</v>
+        <v>187</v>
       </c>
       <c r="D11" t="n">
-        <v>168</v>
+        <v>167</v>
       </c>
     </row>
     <row r="12">
@@ -2478,10 +2478,10 @@
         <v>4</v>
       </c>
       <c r="C12" t="n">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="D12" t="n">
-        <v>133</v>
+        <v>130</v>
       </c>
     </row>
     <row r="13">
@@ -2489,10 +2489,10 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="D13" t="n">
         <v>100</v>
@@ -2520,10 +2520,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D15" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="16">
@@ -2534,10 +2534,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
+        <v>34</v>
+      </c>
+      <c r="D16" t="n">
         <v>35</v>
-      </c>
-      <c r="D16" t="n">
-        <v>36</v>
       </c>
     </row>
     <row r="17">
@@ -2551,7 +2551,7 @@
         <v>31</v>
       </c>
       <c r="D17" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="18">
@@ -2576,7 +2576,7 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D19" t="n">
         <v>6</v>
@@ -2646,13 +2646,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>1991</v>
+        <v>2447</v>
       </c>
       <c r="C2" t="n">
-        <v>5393</v>
+        <v>2067</v>
       </c>
       <c r="D2" t="n">
-        <v>11902</v>
+        <v>11758</v>
       </c>
     </row>
     <row r="3">
@@ -2660,13 +2660,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3058</v>
+        <v>3779</v>
       </c>
       <c r="C3" t="n">
-        <v>8614</v>
+        <v>4608</v>
       </c>
       <c r="D3" t="n">
-        <v>16104</v>
+        <v>14768</v>
       </c>
     </row>
     <row r="4">
@@ -2674,13 +2674,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2724</v>
+        <v>3318</v>
       </c>
       <c r="C4" t="n">
-        <v>10460</v>
+        <v>7733</v>
       </c>
       <c r="D4" t="n">
-        <v>12584</v>
+        <v>10273</v>
       </c>
     </row>
     <row r="5">
@@ -2688,13 +2688,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1594</v>
+        <v>1791</v>
       </c>
       <c r="C5" t="n">
-        <v>9772</v>
+        <v>8547</v>
       </c>
       <c r="D5" t="n">
-        <v>5294</v>
+        <v>3896</v>
       </c>
     </row>
     <row r="6">
@@ -2702,13 +2702,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>757</v>
+        <v>855</v>
       </c>
       <c r="C6" t="n">
-        <v>5733</v>
+        <v>5647</v>
       </c>
       <c r="D6" t="n">
-        <v>1457</v>
+        <v>1125</v>
       </c>
     </row>
     <row r="7">
@@ -2716,13 +2716,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>128</v>
+        <v>155</v>
       </c>
       <c r="C7" t="n">
-        <v>2811</v>
+        <v>3542</v>
       </c>
       <c r="D7" t="n">
-        <v>592</v>
+        <v>544</v>
       </c>
     </row>
     <row r="8">
@@ -2730,13 +2730,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>46</v>
+        <v>51</v>
       </c>
       <c r="C8" t="n">
-        <v>1010</v>
+        <v>1445</v>
       </c>
       <c r="D8" t="n">
-        <v>377</v>
+        <v>371</v>
       </c>
     </row>
     <row r="9">
@@ -2747,10 +2747,10 @@
         <v>17</v>
       </c>
       <c r="C9" t="n">
-        <v>268</v>
+        <v>326</v>
       </c>
       <c r="D9" t="n">
-        <v>285</v>
+        <v>282</v>
       </c>
     </row>
     <row r="10">
@@ -2761,10 +2761,10 @@
         <v>8</v>
       </c>
       <c r="C10" t="n">
-        <v>178</v>
+        <v>183</v>
       </c>
       <c r="D10" t="n">
-        <v>164</v>
+        <v>163</v>
       </c>
     </row>
     <row r="11">
@@ -2775,10 +2775,10 @@
         <v>3</v>
       </c>
       <c r="C11" t="n">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="D11" t="n">
-        <v>130</v>
+        <v>127</v>
       </c>
     </row>
     <row r="12">
@@ -2789,7 +2789,7 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="D12" t="n">
         <v>98</v>
@@ -2817,10 +2817,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D14" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="15">
@@ -2831,10 +2831,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
+        <v>33</v>
+      </c>
+      <c r="D15" t="n">
         <v>34</v>
-      </c>
-      <c r="D15" t="n">
-        <v>35</v>
       </c>
     </row>
     <row r="16">
@@ -2848,7 +2848,7 @@
         <v>30</v>
       </c>
       <c r="D16" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="17">
@@ -2873,7 +2873,7 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D18" t="n">
         <v>5</v>
@@ -2957,13 +2957,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2656</v>
+        <v>3490</v>
       </c>
       <c r="C2" t="n">
-        <v>4054</v>
+        <v>3495</v>
       </c>
       <c r="D2" t="n">
-        <v>16174</v>
+        <v>14423</v>
       </c>
     </row>
     <row r="3">
@@ -2971,13 +2971,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2262</v>
+        <v>2747</v>
       </c>
       <c r="C3" t="n">
-        <v>6453</v>
+        <v>3110</v>
       </c>
       <c r="D3" t="n">
-        <v>14509</v>
+        <v>13508</v>
       </c>
     </row>
     <row r="4">
@@ -2985,13 +2985,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2495</v>
+        <v>3093</v>
       </c>
       <c r="C4" t="n">
-        <v>9409</v>
+        <v>6132</v>
       </c>
       <c r="D4" t="n">
-        <v>12742</v>
+        <v>10651</v>
       </c>
     </row>
     <row r="5">
@@ -2999,13 +2999,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1820</v>
+        <v>2131</v>
       </c>
       <c r="C5" t="n">
-        <v>9959</v>
+        <v>8091</v>
       </c>
       <c r="D5" t="n">
-        <v>6182</v>
+        <v>4695</v>
       </c>
     </row>
     <row r="6">
@@ -3013,13 +3013,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>966</v>
+        <v>1097</v>
       </c>
       <c r="C6" t="n">
-        <v>7367</v>
+        <v>6848</v>
       </c>
       <c r="D6" t="n">
-        <v>1968</v>
+        <v>1482</v>
       </c>
     </row>
     <row r="7">
@@ -3027,13 +3027,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>269</v>
+        <v>318</v>
       </c>
       <c r="C7" t="n">
-        <v>3981</v>
+        <v>4435</v>
       </c>
       <c r="D7" t="n">
-        <v>687</v>
+        <v>617</v>
       </c>
     </row>
     <row r="8">
@@ -3041,13 +3041,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="C8" t="n">
-        <v>1647</v>
+        <v>2212</v>
       </c>
       <c r="D8" t="n">
-        <v>400</v>
+        <v>389</v>
       </c>
     </row>
     <row r="9">
@@ -3055,13 +3055,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C9" t="n">
-        <v>501</v>
+        <v>686</v>
       </c>
       <c r="D9" t="n">
-        <v>293</v>
+        <v>289</v>
       </c>
     </row>
     <row r="10">
@@ -3072,10 +3072,10 @@
         <v>8</v>
       </c>
       <c r="C10" t="n">
-        <v>207</v>
+        <v>226</v>
       </c>
       <c r="D10" t="n">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="11">
@@ -3086,10 +3086,10 @@
         <v>2</v>
       </c>
       <c r="C11" t="n">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="D11" t="n">
-        <v>135</v>
+        <v>131</v>
       </c>
     </row>
     <row r="12">
@@ -3100,10 +3100,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="D12" t="n">
-        <v>98</v>
+        <v>99</v>
       </c>
     </row>
     <row r="13">
@@ -3114,7 +3114,7 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D13" t="n">
         <v>60</v>
@@ -3128,10 +3128,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
+        <v>44</v>
+      </c>
+      <c r="D14" t="n">
         <v>45</v>
-      </c>
-      <c r="D14" t="n">
-        <v>46</v>
       </c>
     </row>
     <row r="15">
@@ -3142,10 +3142,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D15" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="16">
@@ -3159,7 +3159,7 @@
         <v>58</v>
       </c>
       <c r="D16" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="17">
@@ -3268,13 +3268,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>1840</v>
+        <v>2475</v>
       </c>
       <c r="C2" t="n">
-        <v>4029</v>
+        <v>2179</v>
       </c>
       <c r="D2" t="n">
-        <v>12770</v>
+        <v>10442</v>
       </c>
     </row>
     <row r="3">
@@ -3282,13 +3282,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2088</v>
+        <v>2615</v>
       </c>
       <c r="C3" t="n">
-        <v>5079</v>
+        <v>2991</v>
       </c>
       <c r="D3" t="n">
-        <v>13929</v>
+        <v>13012</v>
       </c>
     </row>
     <row r="4">
@@ -3296,13 +3296,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2240</v>
+        <v>2757</v>
       </c>
       <c r="C4" t="n">
-        <v>8349</v>
+        <v>4932</v>
       </c>
       <c r="D4" t="n">
-        <v>12697</v>
+        <v>10786</v>
       </c>
     </row>
     <row r="5">
@@ -3310,13 +3310,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1921</v>
+        <v>2312</v>
       </c>
       <c r="C5" t="n">
-        <v>9949</v>
+        <v>7537</v>
       </c>
       <c r="D5" t="n">
-        <v>6805</v>
+        <v>5226</v>
       </c>
     </row>
     <row r="6">
@@ -3324,13 +3324,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1102</v>
+        <v>1276</v>
       </c>
       <c r="C6" t="n">
-        <v>8331</v>
+        <v>7508</v>
       </c>
       <c r="D6" t="n">
-        <v>2306</v>
+        <v>1785</v>
       </c>
     </row>
     <row r="7">
@@ -3338,13 +3338,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>239</v>
+        <v>284</v>
       </c>
       <c r="C7" t="n">
-        <v>5015</v>
+        <v>5305</v>
       </c>
       <c r="D7" t="n">
-        <v>774</v>
+        <v>682</v>
       </c>
     </row>
     <row r="8">
@@ -3352,13 +3352,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>49</v>
+        <v>57</v>
       </c>
       <c r="C8" t="n">
-        <v>2146</v>
+        <v>2766</v>
       </c>
       <c r="D8" t="n">
-        <v>415</v>
+        <v>401</v>
       </c>
     </row>
     <row r="9">
@@ -3366,13 +3366,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C9" t="n">
-        <v>553</v>
+        <v>774</v>
       </c>
       <c r="D9" t="n">
-        <v>290</v>
+        <v>288</v>
       </c>
     </row>
     <row r="10">
@@ -3383,10 +3383,10 @@
         <v>3</v>
       </c>
       <c r="C10" t="n">
-        <v>212</v>
+        <v>230</v>
       </c>
       <c r="D10" t="n">
-        <v>177</v>
+        <v>175</v>
       </c>
     </row>
     <row r="11">
@@ -3400,7 +3400,7 @@
         <v>127</v>
       </c>
       <c r="D11" t="n">
-        <v>135</v>
+        <v>133</v>
       </c>
     </row>
     <row r="12">
@@ -3411,7 +3411,7 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="D12" t="n">
         <v>91</v>
@@ -3425,7 +3425,7 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D13" t="n">
         <v>61</v>
@@ -3439,10 +3439,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D14" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="15">
@@ -3456,7 +3456,7 @@
         <v>56</v>
       </c>
       <c r="D15" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="16">
@@ -3579,13 +3579,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2566</v>
+        <v>3236</v>
       </c>
       <c r="C2" t="n">
-        <v>3783</v>
+        <v>5722</v>
       </c>
       <c r="D2" t="n">
-        <v>16865</v>
+        <v>11066</v>
       </c>
     </row>
     <row r="3">
@@ -3593,13 +3593,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>1689</v>
+        <v>2160</v>
       </c>
       <c r="C3" t="n">
-        <v>4230</v>
+        <v>2374</v>
       </c>
       <c r="D3" t="n">
-        <v>12930</v>
+        <v>11870</v>
       </c>
     </row>
     <row r="4">
@@ -3607,13 +3607,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1921</v>
+        <v>2353</v>
       </c>
       <c r="C4" t="n">
-        <v>6808</v>
+        <v>4009</v>
       </c>
       <c r="D4" t="n">
-        <v>12476</v>
+        <v>10778</v>
       </c>
     </row>
     <row r="5">
@@ -3621,13 +3621,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1851</v>
+        <v>2249</v>
       </c>
       <c r="C5" t="n">
-        <v>9127</v>
+        <v>6329</v>
       </c>
       <c r="D5" t="n">
-        <v>7268</v>
+        <v>5814</v>
       </c>
     </row>
     <row r="6">
@@ -3635,13 +3635,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1268</v>
+        <v>1511</v>
       </c>
       <c r="C6" t="n">
-        <v>8854</v>
+        <v>7456</v>
       </c>
       <c r="D6" t="n">
-        <v>2837</v>
+        <v>2191</v>
       </c>
     </row>
     <row r="7">
@@ -3649,13 +3649,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>434</v>
+        <v>526</v>
       </c>
       <c r="C7" t="n">
-        <v>6232</v>
+        <v>6175</v>
       </c>
       <c r="D7" t="n">
-        <v>946</v>
+        <v>804</v>
       </c>
     </row>
     <row r="8">
@@ -3663,13 +3663,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>87</v>
+        <v>107</v>
       </c>
       <c r="C8" t="n">
-        <v>3072</v>
+        <v>3635</v>
       </c>
       <c r="D8" t="n">
-        <v>449</v>
+        <v>427</v>
       </c>
     </row>
     <row r="9">
@@ -3677,13 +3677,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="C9" t="n">
-        <v>1042</v>
+        <v>1425</v>
       </c>
       <c r="D9" t="n">
-        <v>299</v>
+        <v>296</v>
       </c>
     </row>
     <row r="10">
@@ -3694,10 +3694,10 @@
         <v>4</v>
       </c>
       <c r="C10" t="n">
-        <v>307</v>
+        <v>392</v>
       </c>
       <c r="D10" t="n">
-        <v>186</v>
+        <v>183</v>
       </c>
     </row>
     <row r="11">
@@ -3708,7 +3708,7 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>149</v>
+        <v>156</v>
       </c>
       <c r="D11" t="n">
         <v>136</v>
@@ -3722,7 +3722,7 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="D12" t="n">
         <v>93</v>
@@ -3750,7 +3750,7 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D14" t="n">
         <v>36</v>
@@ -3767,7 +3767,7 @@
         <v>59</v>
       </c>
       <c r="D15" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="16">
@@ -3778,7 +3778,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="D16" t="n">
         <v>7</v>
@@ -3890,13 +3890,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4456</v>
+        <v>8240</v>
       </c>
       <c r="C2" t="n">
-        <v>6027</v>
+        <v>13228</v>
       </c>
       <c r="D2" t="n">
-        <v>19772</v>
+        <v>3322</v>
       </c>
     </row>
     <row r="3">
@@ -4201,13 +4201,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>1875</v>
+        <v>2341</v>
       </c>
       <c r="C2" t="n">
-        <v>2239</v>
+        <v>3295</v>
       </c>
       <c r="D2" t="n">
-        <v>12547</v>
+        <v>8233</v>
       </c>
     </row>
     <row r="3">
@@ -4215,13 +4215,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2278</v>
+        <v>2861</v>
       </c>
       <c r="C3" t="n">
-        <v>4588</v>
+        <v>3332</v>
       </c>
       <c r="D3" t="n">
-        <v>14315</v>
+        <v>12739</v>
       </c>
     </row>
     <row r="4">
@@ -4229,13 +4229,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2675</v>
+        <v>3279</v>
       </c>
       <c r="C4" t="n">
-        <v>9861</v>
+        <v>6081</v>
       </c>
       <c r="D4" t="n">
-        <v>12763</v>
+        <v>11017</v>
       </c>
     </row>
     <row r="5">
@@ -4243,13 +4243,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1188</v>
+        <v>1437</v>
       </c>
       <c r="C5" t="n">
-        <v>12897</v>
+        <v>9989</v>
       </c>
       <c r="D5" t="n">
-        <v>6650</v>
+        <v>5259</v>
       </c>
     </row>
     <row r="6">
@@ -4257,13 +4257,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>401</v>
+        <v>486</v>
       </c>
       <c r="C6" t="n">
-        <v>7582</v>
+        <v>7439</v>
       </c>
       <c r="D6" t="n">
-        <v>2178</v>
+        <v>1759</v>
       </c>
     </row>
     <row r="7">
@@ -4271,13 +4271,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>80</v>
+        <v>98</v>
       </c>
       <c r="C7" t="n">
-        <v>3010</v>
+        <v>3562</v>
       </c>
       <c r="D7" t="n">
-        <v>551</v>
+        <v>520</v>
       </c>
     </row>
     <row r="8">
@@ -4285,13 +4285,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="C8" t="n">
-        <v>1021</v>
+        <v>1396</v>
       </c>
       <c r="D8" t="n">
-        <v>293</v>
+        <v>290</v>
       </c>
     </row>
     <row r="9">
@@ -4302,10 +4302,10 @@
         <v>3</v>
       </c>
       <c r="C9" t="n">
-        <v>300</v>
+        <v>384</v>
       </c>
       <c r="D9" t="n">
-        <v>182</v>
+        <v>179</v>
       </c>
     </row>
     <row r="10">
@@ -4316,7 +4316,7 @@
         <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>146</v>
+        <v>152</v>
       </c>
       <c r="D10" t="n">
         <v>133</v>
@@ -4330,7 +4330,7 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="D11" t="n">
         <v>91</v>
@@ -4358,7 +4358,7 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D13" t="n">
         <v>35</v>
@@ -4375,7 +4375,7 @@
         <v>57</v>
       </c>
       <c r="D14" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="15">
@@ -4386,7 +4386,7 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="D15" t="n">
         <v>6</v>
@@ -4512,13 +4512,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6649</v>
+        <v>7151</v>
       </c>
       <c r="C2" t="n">
-        <v>6092</v>
+        <v>8617</v>
       </c>
       <c r="D2" t="n">
-        <v>22956</v>
+        <v>13189</v>
       </c>
     </row>
     <row r="3">
@@ -4526,13 +4526,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>1894</v>
+        <v>3499</v>
       </c>
       <c r="C3" t="n">
-        <v>3037</v>
+        <v>6666</v>
       </c>
       <c r="D3" t="n">
-        <v>3961</v>
+        <v>1197</v>
       </c>
     </row>
     <row r="4">
@@ -4557,7 +4557,7 @@
         <v>193</v>
       </c>
       <c r="C5" t="n">
-        <v>385</v>
+        <v>381</v>
       </c>
       <c r="D5" t="n">
         <v>1161</v>
@@ -4571,7 +4571,7 @@
         <v>200</v>
       </c>
       <c r="C6" t="n">
-        <v>454</v>
+        <v>459</v>
       </c>
       <c r="D6" t="n">
         <v>816</v>
@@ -4596,7 +4596,7 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C8" t="n">
         <v>260</v>
@@ -4610,7 +4610,7 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C9" t="n">
         <v>205</v>
@@ -4823,13 +4823,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4476</v>
+        <v>4651</v>
       </c>
       <c r="C2" t="n">
-        <v>5219</v>
+        <v>8680</v>
       </c>
       <c r="D2" t="n">
-        <v>32875</v>
+        <v>17412</v>
       </c>
     </row>
     <row r="3">
@@ -4837,13 +4837,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3503</v>
+        <v>4378</v>
       </c>
       <c r="C3" t="n">
-        <v>4109</v>
+        <v>6700</v>
       </c>
       <c r="D3" t="n">
-        <v>6860</v>
+        <v>3123</v>
       </c>
     </row>
     <row r="4">
@@ -4851,13 +4851,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>857</v>
+        <v>1554</v>
       </c>
       <c r="C4" t="n">
-        <v>1824</v>
+        <v>3949</v>
       </c>
       <c r="D4" t="n">
-        <v>1979</v>
+        <v>1422</v>
       </c>
     </row>
     <row r="5">
@@ -4868,7 +4868,7 @@
         <v>125</v>
       </c>
       <c r="C5" t="n">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="D5" t="n">
         <v>1198</v>
@@ -4896,7 +4896,7 @@
         <v>158</v>
       </c>
       <c r="C7" t="n">
-        <v>406</v>
+        <v>409</v>
       </c>
       <c r="D7" t="n">
         <v>584</v>
@@ -4907,7 +4907,7 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="C8" t="n">
         <v>307</v>
@@ -4952,7 +4952,7 @@
         <v>43</v>
       </c>
       <c r="C11" t="n">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="D11" t="n">
         <v>270</v>
@@ -4966,7 +4966,7 @@
         <v>28</v>
       </c>
       <c r="C12" t="n">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="D12" t="n">
         <v>206</v>
@@ -5134,13 +5134,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6061</v>
+        <v>4860</v>
       </c>
       <c r="C2" t="n">
-        <v>12208</v>
+        <v>7218</v>
       </c>
       <c r="D2" t="n">
-        <v>29141</v>
+        <v>27837</v>
       </c>
     </row>
     <row r="3">
@@ -5148,13 +5148,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3276</v>
+        <v>3762</v>
       </c>
       <c r="C3" t="n">
-        <v>4120</v>
+        <v>6728</v>
       </c>
       <c r="D3" t="n">
-        <v>10528</v>
+        <v>5184</v>
       </c>
     </row>
     <row r="4">
@@ -5162,13 +5162,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1849</v>
+        <v>2492</v>
       </c>
       <c r="C4" t="n">
-        <v>3040</v>
+        <v>5398</v>
       </c>
       <c r="D4" t="n">
-        <v>2855</v>
+        <v>1705</v>
       </c>
     </row>
     <row r="5">
@@ -5176,13 +5176,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>405</v>
+        <v>685</v>
       </c>
       <c r="C5" t="n">
-        <v>1095</v>
+        <v>2219</v>
       </c>
       <c r="D5" t="n">
-        <v>1292</v>
+        <v>1190</v>
       </c>
     </row>
     <row r="6">
@@ -5190,10 +5190,10 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="C6" t="n">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="D6" t="n">
         <v>908</v>
@@ -5204,10 +5204,10 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="C7" t="n">
-        <v>401</v>
+        <v>407</v>
       </c>
       <c r="D7" t="n">
         <v>626</v>
@@ -5218,7 +5218,7 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="C8" t="n">
         <v>357</v>
@@ -5235,7 +5235,7 @@
         <v>91</v>
       </c>
       <c r="C9" t="n">
-        <v>268</v>
+        <v>265</v>
       </c>
       <c r="D9" t="n">
         <v>371</v>
@@ -5260,10 +5260,10 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C11" t="n">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="D11" t="n">
         <v>280</v>
@@ -5277,7 +5277,7 @@
         <v>31</v>
       </c>
       <c r="C12" t="n">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="D12" t="n">
         <v>213</v>
@@ -5291,7 +5291,7 @@
         <v>21</v>
       </c>
       <c r="C13" t="n">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="D13" t="n">
         <v>173</v>
@@ -5319,10 +5319,10 @@
         <v>12</v>
       </c>
       <c r="C15" t="n">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="D15" t="n">
-        <v>120</v>
+        <v>122</v>
       </c>
     </row>
     <row r="16">
@@ -5333,10 +5333,10 @@
         <v>12</v>
       </c>
       <c r="C16" t="n">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="D16" t="n">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="17">
@@ -5445,13 +5445,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5917</v>
+        <v>6748</v>
       </c>
       <c r="C2" t="n">
-        <v>7657</v>
+        <v>7187</v>
       </c>
       <c r="D2" t="n">
-        <v>23409</v>
+        <v>22607</v>
       </c>
     </row>
     <row r="3">
@@ -5459,13 +5459,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3737</v>
+        <v>3519</v>
       </c>
       <c r="C3" t="n">
-        <v>7209</v>
+        <v>6082</v>
       </c>
       <c r="D3" t="n">
-        <v>12616</v>
+        <v>8262</v>
       </c>
     </row>
     <row r="4">
@@ -5473,13 +5473,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2150</v>
+        <v>2663</v>
       </c>
       <c r="C4" t="n">
-        <v>3557</v>
+        <v>5987</v>
       </c>
       <c r="D4" t="n">
-        <v>4167</v>
+        <v>2287</v>
       </c>
     </row>
     <row r="5">
@@ -5487,13 +5487,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>922</v>
+        <v>1294</v>
       </c>
       <c r="C5" t="n">
-        <v>2080</v>
+        <v>3769</v>
       </c>
       <c r="D5" t="n">
-        <v>1510</v>
+        <v>1242</v>
       </c>
     </row>
     <row r="6">
@@ -5501,13 +5501,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>240</v>
+        <v>352</v>
       </c>
       <c r="C6" t="n">
-        <v>693</v>
+        <v>1256</v>
       </c>
       <c r="D6" t="n">
-        <v>961</v>
+        <v>932</v>
       </c>
     </row>
     <row r="7">
@@ -5518,10 +5518,10 @@
         <v>143</v>
       </c>
       <c r="C7" t="n">
-        <v>352</v>
+        <v>356</v>
       </c>
       <c r="D7" t="n">
-        <v>660</v>
+        <v>666</v>
       </c>
     </row>
     <row r="8">
@@ -5529,13 +5529,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="C8" t="n">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="D8" t="n">
-        <v>478</v>
+        <v>471</v>
       </c>
     </row>
     <row r="9">
@@ -5546,7 +5546,7 @@
         <v>97</v>
       </c>
       <c r="C9" t="n">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="D9" t="n">
         <v>380</v>
@@ -5560,7 +5560,7 @@
         <v>70</v>
       </c>
       <c r="C10" t="n">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="D10" t="n">
         <v>342</v>
@@ -5571,7 +5571,7 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C11" t="n">
         <v>189</v>
@@ -5585,13 +5585,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C12" t="n">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="D12" t="n">
-        <v>217</v>
+        <v>220</v>
       </c>
     </row>
     <row r="13">
@@ -5602,10 +5602,10 @@
         <v>22</v>
       </c>
       <c r="C13" t="n">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="D13" t="n">
-        <v>176</v>
+        <v>174</v>
       </c>
     </row>
     <row r="14">
@@ -5616,10 +5616,10 @@
         <v>15</v>
       </c>
       <c r="C14" t="n">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="D14" t="n">
-        <v>148</v>
+        <v>149</v>
       </c>
     </row>
     <row r="15">
@@ -5630,7 +5630,7 @@
         <v>12</v>
       </c>
       <c r="C15" t="n">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="D15" t="n">
         <v>122</v>
@@ -5647,7 +5647,7 @@
         <v>73</v>
       </c>
       <c r="D16" t="n">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="17">
@@ -5658,7 +5658,7 @@
         <v>10</v>
       </c>
       <c r="C17" t="n">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D17" t="n">
         <v>78</v>
@@ -5689,7 +5689,7 @@
         <v>62</v>
       </c>
       <c r="D19" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="20">
@@ -5756,13 +5756,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6148</v>
+        <v>6357</v>
       </c>
       <c r="C2" t="n">
-        <v>11040</v>
+        <v>6356</v>
       </c>
       <c r="D2" t="n">
-        <v>30537</v>
+        <v>30351</v>
       </c>
     </row>
     <row r="3">
@@ -5770,13 +5770,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3485</v>
+        <v>3658</v>
       </c>
       <c r="C3" t="n">
-        <v>6094</v>
+        <v>5435</v>
       </c>
       <c r="D3" t="n">
-        <v>12578</v>
+        <v>9171</v>
       </c>
     </row>
     <row r="4">
@@ -5784,13 +5784,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1824</v>
+        <v>1913</v>
       </c>
       <c r="C4" t="n">
-        <v>4501</v>
+        <v>4887</v>
       </c>
       <c r="D4" t="n">
-        <v>4870</v>
+        <v>2814</v>
       </c>
     </row>
     <row r="5">
@@ -5798,13 +5798,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>791</v>
+        <v>1021</v>
       </c>
       <c r="C5" t="n">
-        <v>2078</v>
+        <v>3571</v>
       </c>
       <c r="D5" t="n">
-        <v>1545</v>
+        <v>1121</v>
       </c>
     </row>
     <row r="6">
@@ -5812,13 +5812,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>272</v>
+        <v>381</v>
       </c>
       <c r="C6" t="n">
-        <v>923</v>
+        <v>1656</v>
       </c>
       <c r="D6" t="n">
-        <v>802</v>
+        <v>740</v>
       </c>
     </row>
     <row r="7">
@@ -5826,13 +5826,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>85</v>
+        <v>105</v>
       </c>
       <c r="C7" t="n">
-        <v>331</v>
+        <v>502</v>
       </c>
       <c r="D7" t="n">
-        <v>515</v>
+        <v>520</v>
       </c>
     </row>
     <row r="8">
@@ -5840,13 +5840,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C8" t="n">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="D8" t="n">
-        <v>360</v>
+        <v>352</v>
       </c>
     </row>
     <row r="9">
@@ -5854,13 +5854,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C9" t="n">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="D9" t="n">
-        <v>270</v>
+        <v>272</v>
       </c>
     </row>
     <row r="10">
@@ -5868,13 +5868,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C10" t="n">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="D10" t="n">
-        <v>235</v>
+        <v>233</v>
       </c>
     </row>
     <row r="11">
@@ -5896,13 +5896,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C12" t="n">
         <v>91</v>
       </c>
       <c r="D12" t="n">
-        <v>147</v>
+        <v>148</v>
       </c>
     </row>
     <row r="13">
@@ -5916,7 +5916,7 @@
         <v>73</v>
       </c>
       <c r="D13" t="n">
-        <v>117</v>
+        <v>116</v>
       </c>
     </row>
     <row r="14">
@@ -5941,7 +5941,7 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D15" t="n">
         <v>79</v>
@@ -5969,10 +5969,10 @@
         <v>3</v>
       </c>
       <c r="C17" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D17" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="18">
@@ -5980,10 +5980,10 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C18" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D18" t="n">
         <v>38</v>
@@ -6025,7 +6025,7 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D21" t="n">
         <v>5</v>
@@ -6067,13 +6067,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4545</v>
+        <v>5103</v>
       </c>
       <c r="C2" t="n">
-        <v>8045</v>
+        <v>7832</v>
       </c>
       <c r="D2" t="n">
-        <v>31963</v>
+        <v>22015</v>
       </c>
     </row>
     <row r="3">
@@ -6081,13 +6081,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3982</v>
+        <v>4120</v>
       </c>
       <c r="C3" t="n">
-        <v>7698</v>
+        <v>5135</v>
       </c>
       <c r="D3" t="n">
-        <v>14669</v>
+        <v>12054</v>
       </c>
     </row>
     <row r="4">
@@ -6095,13 +6095,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2321</v>
+        <v>2404</v>
       </c>
       <c r="C4" t="n">
-        <v>5312</v>
+        <v>5111</v>
       </c>
       <c r="D4" t="n">
-        <v>6275</v>
+        <v>4010</v>
       </c>
     </row>
     <row r="5">
@@ -6109,13 +6109,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1149</v>
+        <v>1305</v>
       </c>
       <c r="C5" t="n">
-        <v>3453</v>
+        <v>4254</v>
       </c>
       <c r="D5" t="n">
-        <v>2121</v>
+        <v>1401</v>
       </c>
     </row>
     <row r="6">
@@ -6123,13 +6123,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>491</v>
+        <v>639</v>
       </c>
       <c r="C6" t="n">
-        <v>1565</v>
+        <v>2702</v>
       </c>
       <c r="D6" t="n">
-        <v>933</v>
+        <v>802</v>
       </c>
     </row>
     <row r="7">
@@ -6137,13 +6137,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>160</v>
+        <v>218</v>
       </c>
       <c r="C7" t="n">
-        <v>661</v>
+        <v>1135</v>
       </c>
       <c r="D7" t="n">
-        <v>558</v>
+        <v>555</v>
       </c>
     </row>
     <row r="8">
@@ -6151,13 +6151,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>66</v>
+        <v>73</v>
       </c>
       <c r="C8" t="n">
-        <v>279</v>
+        <v>367</v>
       </c>
       <c r="D8" t="n">
-        <v>385</v>
+        <v>374</v>
       </c>
     </row>
     <row r="9">
@@ -6165,7 +6165,7 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="C9" t="n">
         <v>209</v>
@@ -6182,10 +6182,10 @@
         <v>33</v>
       </c>
       <c r="C10" t="n">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="D10" t="n">
-        <v>236</v>
+        <v>237</v>
       </c>
     </row>
     <row r="11">
@@ -6199,7 +6199,7 @@
         <v>130</v>
       </c>
       <c r="D11" t="n">
-        <v>199</v>
+        <v>197</v>
       </c>
     </row>
     <row r="12">
@@ -6221,13 +6221,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C13" t="n">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="D13" t="n">
-        <v>119</v>
+        <v>118</v>
       </c>
     </row>
     <row r="14">
@@ -6235,13 +6235,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C14" t="n">
         <v>63</v>
       </c>
       <c r="D14" t="n">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="15">
@@ -6280,10 +6280,10 @@
         <v>2</v>
       </c>
       <c r="C17" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D17" t="n">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="18">
@@ -6297,7 +6297,7 @@
         <v>33</v>
       </c>
       <c r="D18" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="19">
@@ -6305,7 +6305,7 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C19" t="n">
         <v>31</v>
@@ -6336,7 +6336,7 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="D21" t="n">
         <v>6</v>
@@ -6378,13 +6378,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3727</v>
+        <v>4996</v>
       </c>
       <c r="C2" t="n">
-        <v>10276</v>
+        <v>9758</v>
       </c>
       <c r="D2" t="n">
-        <v>26576</v>
+        <v>28362</v>
       </c>
     </row>
     <row r="3">
@@ -6392,13 +6392,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3509</v>
+        <v>3784</v>
       </c>
       <c r="C3" t="n">
-        <v>6836</v>
+        <v>5691</v>
       </c>
       <c r="D3" t="n">
-        <v>16379</v>
+        <v>12719</v>
       </c>
     </row>
     <row r="4">
@@ -6406,13 +6406,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2696</v>
+        <v>2790</v>
       </c>
       <c r="C4" t="n">
-        <v>6530</v>
+        <v>5017</v>
       </c>
       <c r="D4" t="n">
-        <v>7695</v>
+        <v>5316</v>
       </c>
     </row>
     <row r="5">
@@ -6420,13 +6420,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1493</v>
+        <v>1605</v>
       </c>
       <c r="C5" t="n">
-        <v>4380</v>
+        <v>4577</v>
       </c>
       <c r="D5" t="n">
-        <v>2814</v>
+        <v>1834</v>
       </c>
     </row>
     <row r="6">
@@ -6434,13 +6434,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>736</v>
+        <v>879</v>
       </c>
       <c r="C6" t="n">
-        <v>2526</v>
+        <v>3476</v>
       </c>
       <c r="D6" t="n">
-        <v>1116</v>
+        <v>886</v>
       </c>
     </row>
     <row r="7">
@@ -6448,13 +6448,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>280</v>
+        <v>370</v>
       </c>
       <c r="C7" t="n">
-        <v>1114</v>
+        <v>1933</v>
       </c>
       <c r="D7" t="n">
-        <v>618</v>
+        <v>592</v>
       </c>
     </row>
     <row r="8">
@@ -6462,13 +6462,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>98</v>
+        <v>125</v>
       </c>
       <c r="C8" t="n">
-        <v>469</v>
+        <v>739</v>
       </c>
       <c r="D8" t="n">
-        <v>406</v>
+        <v>400</v>
       </c>
     </row>
     <row r="9">
@@ -6476,13 +6476,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C9" t="n">
-        <v>242</v>
+        <v>284</v>
       </c>
       <c r="D9" t="n">
-        <v>297</v>
+        <v>291</v>
       </c>
     </row>
     <row r="10">
@@ -6496,7 +6496,7 @@
         <v>188</v>
       </c>
       <c r="D10" t="n">
-        <v>240</v>
+        <v>241</v>
       </c>
     </row>
     <row r="11">
@@ -6504,13 +6504,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C11" t="n">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="D11" t="n">
-        <v>200</v>
+        <v>198</v>
       </c>
     </row>
     <row r="12">
@@ -6524,7 +6524,7 @@
         <v>113</v>
       </c>
       <c r="D12" t="n">
-        <v>158</v>
+        <v>157</v>
       </c>
     </row>
     <row r="13">
@@ -6535,7 +6535,7 @@
         <v>10</v>
       </c>
       <c r="C13" t="n">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="D13" t="n">
         <v>121</v>
@@ -6546,13 +6546,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C14" t="n">
         <v>69</v>
       </c>
       <c r="D14" t="n">
-        <v>99</v>
+        <v>97</v>
       </c>
     </row>
     <row r="15">
@@ -6563,7 +6563,7 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D15" t="n">
         <v>81</v>
@@ -6591,10 +6591,10 @@
         <v>2</v>
       </c>
       <c r="C17" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D17" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="18">
@@ -6608,7 +6608,7 @@
         <v>33</v>
       </c>
       <c r="D18" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="19">
@@ -6622,7 +6622,7 @@
         <v>31</v>
       </c>
       <c r="D19" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="20">
@@ -6630,7 +6630,7 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C20" t="n">
         <v>29</v>
@@ -6647,7 +6647,7 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D21" t="n">
         <v>7</v>

--- a/output/yearly_population_iteration_4_growth_param_0.5.xlsx
+++ b/output/yearly_population_iteration_4_growth_param_0.5.xlsx
@@ -780,13 +780,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6172</v>
+        <v>5331</v>
       </c>
       <c r="C2" t="n">
-        <v>8171</v>
+        <v>8765</v>
       </c>
       <c r="D2" t="n">
-        <v>22459</v>
+        <v>29088</v>
       </c>
     </row>
     <row r="3">
@@ -794,13 +794,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3564</v>
+        <v>4028</v>
       </c>
       <c r="C3" t="n">
-        <v>6681</v>
+        <v>5033</v>
       </c>
       <c r="D3" t="n">
-        <v>14096</v>
+        <v>15435</v>
       </c>
     </row>
     <row r="4">
@@ -808,13 +808,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2797</v>
+        <v>3197</v>
       </c>
       <c r="C4" t="n">
-        <v>5200</v>
+        <v>5206</v>
       </c>
       <c r="D4" t="n">
-        <v>6433</v>
+        <v>8580</v>
       </c>
     </row>
     <row r="5">
@@ -822,13 +822,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1873</v>
+        <v>2008</v>
       </c>
       <c r="C5" t="n">
-        <v>4697</v>
+        <v>5162</v>
       </c>
       <c r="D5" t="n">
-        <v>2328</v>
+        <v>3289</v>
       </c>
     </row>
     <row r="6">
@@ -836,13 +836,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1103</v>
+        <v>1099</v>
       </c>
       <c r="C6" t="n">
-        <v>3924</v>
+        <v>3574</v>
       </c>
       <c r="D6" t="n">
-        <v>1028</v>
+        <v>1280</v>
       </c>
     </row>
     <row r="7">
@@ -850,13 +850,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>528</v>
+        <v>506</v>
       </c>
       <c r="C7" t="n">
-        <v>2658</v>
+        <v>1864</v>
       </c>
       <c r="D7" t="n">
-        <v>626</v>
+        <v>661</v>
       </c>
     </row>
     <row r="8">
@@ -864,13 +864,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>202</v>
+        <v>187</v>
       </c>
       <c r="C8" t="n">
-        <v>1269</v>
+        <v>782</v>
       </c>
       <c r="D8" t="n">
-        <v>426</v>
+        <v>432</v>
       </c>
     </row>
     <row r="9">
@@ -878,13 +878,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>73</v>
+        <v>68</v>
       </c>
       <c r="C9" t="n">
-        <v>484</v>
+        <v>326</v>
       </c>
       <c r="D9" t="n">
-        <v>301</v>
+        <v>308</v>
       </c>
     </row>
     <row r="10">
@@ -895,10 +895,10 @@
         <v>38</v>
       </c>
       <c r="C10" t="n">
-        <v>228</v>
+        <v>204</v>
       </c>
       <c r="D10" t="n">
-        <v>245</v>
+        <v>246</v>
       </c>
     </row>
     <row r="11">
@@ -906,10 +906,10 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C11" t="n">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="D11" t="n">
         <v>201</v>
@@ -923,10 +923,10 @@
         <v>17</v>
       </c>
       <c r="C12" t="n">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="D12" t="n">
-        <v>159</v>
+        <v>162</v>
       </c>
     </row>
     <row r="13">
@@ -937,7 +937,7 @@
         <v>11</v>
       </c>
       <c r="C13" t="n">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="D13" t="n">
         <v>124</v>
@@ -954,7 +954,7 @@
         <v>75</v>
       </c>
       <c r="D14" t="n">
-        <v>97</v>
+        <v>99</v>
       </c>
     </row>
     <row r="15">
@@ -962,10 +962,10 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="D15" t="n">
         <v>82</v>
@@ -982,7 +982,7 @@
         <v>46</v>
       </c>
       <c r="D16" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="17">
@@ -1007,10 +1007,10 @@
         <v>1</v>
       </c>
       <c r="C18" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D18" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="19">
@@ -1024,7 +1024,7 @@
         <v>31</v>
       </c>
       <c r="D19" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="20">
@@ -1035,7 +1035,7 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D20" t="n">
         <v>16</v>
@@ -1091,13 +1091,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7038</v>
+        <v>7172</v>
       </c>
       <c r="C2" t="n">
-        <v>7871</v>
+        <v>7934</v>
       </c>
       <c r="D2" t="n">
-        <v>23497</v>
+        <v>28701</v>
       </c>
     </row>
     <row r="3">
@@ -1105,13 +1105,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3796</v>
+        <v>3765</v>
       </c>
       <c r="C3" t="n">
-        <v>6472</v>
+        <v>5878</v>
       </c>
       <c r="D3" t="n">
-        <v>14241</v>
+        <v>16170</v>
       </c>
     </row>
     <row r="4">
@@ -1119,13 +1119,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2668</v>
+        <v>3034</v>
       </c>
       <c r="C4" t="n">
-        <v>5774</v>
+        <v>4968</v>
       </c>
       <c r="D4" t="n">
-        <v>7352</v>
+        <v>9289</v>
       </c>
     </row>
     <row r="5">
@@ -1133,13 +1133,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2019</v>
+        <v>2212</v>
       </c>
       <c r="C5" t="n">
-        <v>4776</v>
+        <v>5074</v>
       </c>
       <c r="D5" t="n">
-        <v>2887</v>
+        <v>4001</v>
       </c>
     </row>
     <row r="6">
@@ -1147,13 +1147,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1292</v>
+        <v>1354</v>
       </c>
       <c r="C6" t="n">
-        <v>4182</v>
+        <v>4191</v>
       </c>
       <c r="D6" t="n">
-        <v>1191</v>
+        <v>1539</v>
       </c>
     </row>
     <row r="7">
@@ -1161,13 +1161,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>684</v>
+        <v>669</v>
       </c>
       <c r="C7" t="n">
-        <v>3202</v>
+        <v>2582</v>
       </c>
       <c r="D7" t="n">
-        <v>678</v>
+        <v>745</v>
       </c>
     </row>
     <row r="8">
@@ -1175,13 +1175,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>293</v>
+        <v>277</v>
       </c>
       <c r="C8" t="n">
-        <v>1827</v>
+        <v>1237</v>
       </c>
       <c r="D8" t="n">
-        <v>444</v>
+        <v>454</v>
       </c>
     </row>
     <row r="9">
@@ -1189,13 +1189,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>109</v>
+        <v>100</v>
       </c>
       <c r="C9" t="n">
-        <v>799</v>
+        <v>505</v>
       </c>
       <c r="D9" t="n">
-        <v>315</v>
+        <v>321</v>
       </c>
     </row>
     <row r="10">
@@ -1203,13 +1203,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C10" t="n">
-        <v>323</v>
+        <v>251</v>
       </c>
       <c r="D10" t="n">
-        <v>247</v>
+        <v>248</v>
       </c>
     </row>
     <row r="11">
@@ -1220,7 +1220,7 @@
         <v>27</v>
       </c>
       <c r="C11" t="n">
-        <v>185</v>
+        <v>177</v>
       </c>
       <c r="D11" t="n">
         <v>204</v>
@@ -1234,10 +1234,10 @@
         <v>18</v>
       </c>
       <c r="C12" t="n">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="D12" t="n">
-        <v>160</v>
+        <v>163</v>
       </c>
     </row>
     <row r="13">
@@ -1248,10 +1248,10 @@
         <v>11</v>
       </c>
       <c r="C13" t="n">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="D13" t="n">
-        <v>126</v>
+        <v>127</v>
       </c>
     </row>
     <row r="14">
@@ -1262,10 +1262,10 @@
         <v>6</v>
       </c>
       <c r="C14" t="n">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="D14" t="n">
-        <v>97</v>
+        <v>99</v>
       </c>
     </row>
     <row r="15">
@@ -1273,10 +1273,10 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="D15" t="n">
         <v>82</v>
@@ -1287,13 +1287,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C16" t="n">
         <v>49</v>
       </c>
       <c r="D16" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="17">
@@ -1321,7 +1321,7 @@
         <v>34</v>
       </c>
       <c r="D18" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="19">
@@ -1335,7 +1335,7 @@
         <v>31</v>
       </c>
       <c r="D19" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="20">
@@ -1346,7 +1346,7 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D20" t="n">
         <v>16</v>
@@ -1402,13 +1402,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7251</v>
+        <v>8254</v>
       </c>
       <c r="C2" t="n">
-        <v>10172</v>
+        <v>7332</v>
       </c>
       <c r="D2" t="n">
-        <v>27844</v>
+        <v>35005</v>
       </c>
     </row>
     <row r="3">
@@ -1416,13 +1416,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4096</v>
+        <v>4143</v>
       </c>
       <c r="C3" t="n">
-        <v>6312</v>
+        <v>5952</v>
       </c>
       <c r="D3" t="n">
-        <v>14440</v>
+        <v>16638</v>
       </c>
     </row>
     <row r="4">
@@ -1430,13 +1430,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2641</v>
+        <v>2841</v>
       </c>
       <c r="C4" t="n">
-        <v>5886</v>
+        <v>5201</v>
       </c>
       <c r="D4" t="n">
-        <v>8120</v>
+        <v>9908</v>
       </c>
     </row>
     <row r="5">
@@ -1444,13 +1444,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2026</v>
+        <v>2279</v>
       </c>
       <c r="C5" t="n">
-        <v>5033</v>
+        <v>4924</v>
       </c>
       <c r="D5" t="n">
-        <v>3371</v>
+        <v>4640</v>
       </c>
     </row>
     <row r="6">
@@ -1458,13 +1458,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1434</v>
+        <v>1533</v>
       </c>
       <c r="C6" t="n">
-        <v>4338</v>
+        <v>4461</v>
       </c>
       <c r="D6" t="n">
-        <v>1403</v>
+        <v>1834</v>
       </c>
     </row>
     <row r="7">
@@ -1472,13 +1472,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>823</v>
+        <v>833</v>
       </c>
       <c r="C7" t="n">
-        <v>3584</v>
+        <v>3186</v>
       </c>
       <c r="D7" t="n">
-        <v>729</v>
+        <v>846</v>
       </c>
     </row>
     <row r="8">
@@ -1486,13 +1486,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>391</v>
+        <v>374</v>
       </c>
       <c r="C8" t="n">
-        <v>2320</v>
+        <v>1750</v>
       </c>
       <c r="D8" t="n">
-        <v>464</v>
+        <v>481</v>
       </c>
     </row>
     <row r="9">
@@ -1500,13 +1500,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>152</v>
+        <v>144</v>
       </c>
       <c r="C9" t="n">
-        <v>1163</v>
+        <v>765</v>
       </c>
       <c r="D9" t="n">
-        <v>328</v>
+        <v>334</v>
       </c>
     </row>
     <row r="10">
@@ -1514,13 +1514,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="C10" t="n">
-        <v>490</v>
+        <v>338</v>
       </c>
       <c r="D10" t="n">
-        <v>250</v>
+        <v>251</v>
       </c>
     </row>
     <row r="11">
@@ -1528,13 +1528,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C11" t="n">
-        <v>229</v>
+        <v>200</v>
       </c>
       <c r="D11" t="n">
-        <v>206</v>
+        <v>207</v>
       </c>
     </row>
     <row r="12">
@@ -1548,7 +1548,7 @@
         <v>151</v>
       </c>
       <c r="D12" t="n">
-        <v>161</v>
+        <v>164</v>
       </c>
     </row>
     <row r="13">
@@ -1559,10 +1559,10 @@
         <v>11</v>
       </c>
       <c r="C13" t="n">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="D13" t="n">
-        <v>128</v>
+        <v>129</v>
       </c>
     </row>
     <row r="14">
@@ -1573,10 +1573,10 @@
         <v>6</v>
       </c>
       <c r="C14" t="n">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="D14" t="n">
-        <v>97</v>
+        <v>99</v>
       </c>
     </row>
     <row r="15">
@@ -1584,10 +1584,10 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="D15" t="n">
         <v>82</v>
@@ -1598,13 +1598,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C16" t="n">
         <v>52</v>
       </c>
       <c r="D16" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="17">
@@ -1612,7 +1612,7 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C17" t="n">
         <v>41</v>
@@ -1632,7 +1632,7 @@
         <v>34</v>
       </c>
       <c r="D18" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="19">
@@ -1646,7 +1646,7 @@
         <v>31</v>
       </c>
       <c r="D19" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="20">
@@ -1657,7 +1657,7 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D20" t="n">
         <v>16</v>
@@ -1713,13 +1713,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6751</v>
+        <v>7565</v>
       </c>
       <c r="C2" t="n">
-        <v>7079</v>
+        <v>5044</v>
       </c>
       <c r="D2" t="n">
-        <v>22968</v>
+        <v>28802</v>
       </c>
     </row>
     <row r="3">
@@ -1727,13 +1727,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4797</v>
+        <v>4997</v>
       </c>
       <c r="C3" t="n">
-        <v>9603</v>
+        <v>8732</v>
       </c>
       <c r="D3" t="n">
-        <v>15663</v>
+        <v>18217</v>
       </c>
     </row>
     <row r="4">
@@ -1741,13 +1741,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1872</v>
+        <v>2105</v>
       </c>
       <c r="C4" t="n">
-        <v>7995</v>
+        <v>7523</v>
       </c>
       <c r="D4" t="n">
-        <v>7630</v>
+        <v>9675</v>
       </c>
     </row>
     <row r="5">
@@ -1755,13 +1755,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1325</v>
+        <v>1416</v>
       </c>
       <c r="C5" t="n">
-        <v>4251</v>
+        <v>4371</v>
       </c>
       <c r="D5" t="n">
-        <v>2281</v>
+        <v>3044</v>
       </c>
     </row>
     <row r="6">
@@ -1769,13 +1769,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>760</v>
+        <v>769</v>
       </c>
       <c r="C6" t="n">
-        <v>3512</v>
+        <v>3122</v>
       </c>
       <c r="D6" t="n">
-        <v>714</v>
+        <v>829</v>
       </c>
     </row>
     <row r="7">
@@ -1783,13 +1783,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>361</v>
+        <v>345</v>
       </c>
       <c r="C7" t="n">
-        <v>2273</v>
+        <v>1714</v>
       </c>
       <c r="D7" t="n">
-        <v>454</v>
+        <v>471</v>
       </c>
     </row>
     <row r="8">
@@ -1797,13 +1797,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>140</v>
+        <v>133</v>
       </c>
       <c r="C8" t="n">
-        <v>1139</v>
+        <v>749</v>
       </c>
       <c r="D8" t="n">
-        <v>321</v>
+        <v>327</v>
       </c>
     </row>
     <row r="9">
@@ -1811,10 +1811,10 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="C9" t="n">
-        <v>480</v>
+        <v>331</v>
       </c>
       <c r="D9" t="n">
         <v>245</v>
@@ -1825,13 +1825,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C10" t="n">
-        <v>224</v>
+        <v>196</v>
       </c>
       <c r="D10" t="n">
-        <v>201</v>
+        <v>202</v>
       </c>
     </row>
     <row r="11">
@@ -1845,7 +1845,7 @@
         <v>147</v>
       </c>
       <c r="D11" t="n">
-        <v>157</v>
+        <v>160</v>
       </c>
     </row>
     <row r="12">
@@ -1856,10 +1856,10 @@
         <v>10</v>
       </c>
       <c r="C12" t="n">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="D12" t="n">
-        <v>125</v>
+        <v>126</v>
       </c>
     </row>
     <row r="13">
@@ -1870,10 +1870,10 @@
         <v>5</v>
       </c>
       <c r="C13" t="n">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="D13" t="n">
-        <v>95</v>
+        <v>97</v>
       </c>
     </row>
     <row r="14">
@@ -1881,10 +1881,10 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C14" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="D14" t="n">
         <v>80</v>
@@ -1895,13 +1895,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C15" t="n">
         <v>50</v>
       </c>
       <c r="D15" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="16">
@@ -1909,7 +1909,7 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C16" t="n">
         <v>40</v>
@@ -1929,7 +1929,7 @@
         <v>33</v>
       </c>
       <c r="D17" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="18">
@@ -1943,7 +1943,7 @@
         <v>30</v>
       </c>
       <c r="D18" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="19">
@@ -1954,7 +1954,7 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D19" t="n">
         <v>15</v>
@@ -2024,13 +2024,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4153</v>
+        <v>4557</v>
       </c>
       <c r="C2" t="n">
-        <v>3132</v>
+        <v>3294</v>
       </c>
       <c r="D2" t="n">
-        <v>16370</v>
+        <v>20916</v>
       </c>
     </row>
     <row r="3">
@@ -2038,13 +2038,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4844</v>
+        <v>5230</v>
       </c>
       <c r="C3" t="n">
-        <v>7717</v>
+        <v>6416</v>
       </c>
       <c r="D3" t="n">
-        <v>15904</v>
+        <v>18782</v>
       </c>
     </row>
     <row r="4">
@@ -2052,13 +2052,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2560</v>
+        <v>2810</v>
       </c>
       <c r="C4" t="n">
-        <v>8861</v>
+        <v>8212</v>
       </c>
       <c r="D4" t="n">
-        <v>8701</v>
+        <v>10703</v>
       </c>
     </row>
     <row r="5">
@@ -2066,13 +2066,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1460</v>
+        <v>1568</v>
       </c>
       <c r="C5" t="n">
-        <v>5799</v>
+        <v>5760</v>
       </c>
       <c r="D5" t="n">
-        <v>2871</v>
+        <v>3837</v>
       </c>
     </row>
     <row r="6">
@@ -2080,13 +2080,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>889</v>
+        <v>918</v>
       </c>
       <c r="C6" t="n">
-        <v>3975</v>
+        <v>3702</v>
       </c>
       <c r="D6" t="n">
-        <v>861</v>
+        <v>1064</v>
       </c>
     </row>
     <row r="7">
@@ -2094,13 +2094,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>338</v>
+        <v>322</v>
       </c>
       <c r="C7" t="n">
-        <v>2765</v>
+        <v>2237</v>
       </c>
       <c r="D7" t="n">
-        <v>492</v>
+        <v>515</v>
       </c>
     </row>
     <row r="8">
@@ -2108,13 +2108,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>116</v>
+        <v>110</v>
       </c>
       <c r="C8" t="n">
-        <v>1492</v>
+        <v>1006</v>
       </c>
       <c r="D8" t="n">
-        <v>330</v>
+        <v>336</v>
       </c>
     </row>
     <row r="9">
@@ -2122,13 +2122,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C9" t="n">
-        <v>514</v>
+        <v>376</v>
       </c>
       <c r="D9" t="n">
-        <v>256</v>
+        <v>254</v>
       </c>
     </row>
     <row r="10">
@@ -2139,10 +2139,10 @@
         <v>15</v>
       </c>
       <c r="C10" t="n">
-        <v>236</v>
+        <v>217</v>
       </c>
       <c r="D10" t="n">
-        <v>207</v>
+        <v>210</v>
       </c>
     </row>
     <row r="11">
@@ -2153,10 +2153,10 @@
         <v>9</v>
       </c>
       <c r="C11" t="n">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="D11" t="n">
-        <v>164</v>
+        <v>167</v>
       </c>
     </row>
     <row r="12">
@@ -2167,10 +2167,10 @@
         <v>4</v>
       </c>
       <c r="C12" t="n">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="D12" t="n">
-        <v>128</v>
+        <v>130</v>
       </c>
     </row>
     <row r="13">
@@ -2178,13 +2178,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C13" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="D13" t="n">
-        <v>98</v>
+        <v>99</v>
       </c>
     </row>
     <row r="14">
@@ -2192,13 +2192,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C14" t="n">
         <v>49</v>
       </c>
       <c r="D14" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="15">
@@ -2226,7 +2226,7 @@
         <v>32</v>
       </c>
       <c r="D16" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="17">
@@ -2240,7 +2240,7 @@
         <v>29</v>
       </c>
       <c r="D17" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="18">
@@ -2251,7 +2251,7 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D18" t="n">
         <v>14</v>
@@ -2335,13 +2335,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4065</v>
+        <v>5355</v>
       </c>
       <c r="C2" t="n">
-        <v>4332</v>
+        <v>7484</v>
       </c>
       <c r="D2" t="n">
-        <v>16861</v>
+        <v>25911</v>
       </c>
     </row>
     <row r="3">
@@ -2349,13 +2349,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3871</v>
+        <v>4160</v>
       </c>
       <c r="C3" t="n">
-        <v>4956</v>
+        <v>4423</v>
       </c>
       <c r="D3" t="n">
-        <v>14898</v>
+        <v>17810</v>
       </c>
     </row>
     <row r="4">
@@ -2363,13 +2363,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3003</v>
+        <v>3311</v>
       </c>
       <c r="C4" t="n">
-        <v>8127</v>
+        <v>7179</v>
       </c>
       <c r="D4" t="n">
-        <v>9612</v>
+        <v>11696</v>
       </c>
     </row>
     <row r="5">
@@ -2377,13 +2377,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1705</v>
+        <v>1851</v>
       </c>
       <c r="C5" t="n">
-        <v>7145</v>
+        <v>6770</v>
       </c>
       <c r="D5" t="n">
-        <v>3679</v>
+        <v>4774</v>
       </c>
     </row>
     <row r="6">
@@ -2391,13 +2391,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1038</v>
+        <v>1083</v>
       </c>
       <c r="C6" t="n">
-        <v>4725</v>
+        <v>4611</v>
       </c>
       <c r="D6" t="n">
-        <v>1139</v>
+        <v>1449</v>
       </c>
     </row>
     <row r="7">
@@ -2405,13 +2405,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>479</v>
+        <v>485</v>
       </c>
       <c r="C7" t="n">
-        <v>3300</v>
+        <v>2853</v>
       </c>
       <c r="D7" t="n">
-        <v>537</v>
+        <v>585</v>
       </c>
     </row>
     <row r="8">
@@ -2419,13 +2419,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>168</v>
+        <v>160</v>
       </c>
       <c r="C8" t="n">
-        <v>2005</v>
+        <v>1510</v>
       </c>
       <c r="D8" t="n">
-        <v>347</v>
+        <v>355</v>
       </c>
     </row>
     <row r="9">
@@ -2433,13 +2433,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C9" t="n">
-        <v>873</v>
+        <v>617</v>
       </c>
       <c r="D9" t="n">
-        <v>264</v>
+        <v>263</v>
       </c>
     </row>
     <row r="10">
@@ -2450,10 +2450,10 @@
         <v>19</v>
       </c>
       <c r="C10" t="n">
-        <v>333</v>
+        <v>272</v>
       </c>
       <c r="D10" t="n">
-        <v>209</v>
+        <v>212</v>
       </c>
     </row>
     <row r="11">
@@ -2464,10 +2464,10 @@
         <v>9</v>
       </c>
       <c r="C11" t="n">
-        <v>187</v>
+        <v>183</v>
       </c>
       <c r="D11" t="n">
-        <v>167</v>
+        <v>170</v>
       </c>
     </row>
     <row r="12">
@@ -2481,7 +2481,7 @@
         <v>113</v>
       </c>
       <c r="D12" t="n">
-        <v>130</v>
+        <v>132</v>
       </c>
     </row>
     <row r="13">
@@ -2489,13 +2489,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C13" t="n">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="D13" t="n">
-        <v>100</v>
+        <v>102</v>
       </c>
     </row>
     <row r="14">
@@ -2509,7 +2509,7 @@
         <v>53</v>
       </c>
       <c r="D14" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="15">
@@ -2520,10 +2520,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="D15" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="16">
@@ -2537,7 +2537,7 @@
         <v>34</v>
       </c>
       <c r="D16" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="17">
@@ -2551,7 +2551,7 @@
         <v>31</v>
       </c>
       <c r="D17" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="18">
@@ -2562,7 +2562,7 @@
         <v>6</v>
       </c>
       <c r="C18" t="n">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D18" t="n">
         <v>13</v>
@@ -2646,13 +2646,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2447</v>
+        <v>3207</v>
       </c>
       <c r="C2" t="n">
-        <v>2067</v>
+        <v>3579</v>
       </c>
       <c r="D2" t="n">
-        <v>11758</v>
+        <v>18069</v>
       </c>
     </row>
     <row r="3">
@@ -2660,13 +2660,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3779</v>
+        <v>4283</v>
       </c>
       <c r="C3" t="n">
-        <v>4608</v>
+        <v>5299</v>
       </c>
       <c r="D3" t="n">
-        <v>14768</v>
+        <v>18253</v>
       </c>
     </row>
     <row r="4">
@@ -2674,13 +2674,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3318</v>
+        <v>3640</v>
       </c>
       <c r="C4" t="n">
-        <v>7733</v>
+        <v>6845</v>
       </c>
       <c r="D4" t="n">
-        <v>10273</v>
+        <v>12475</v>
       </c>
     </row>
     <row r="5">
@@ -2688,13 +2688,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1791</v>
+        <v>1921</v>
       </c>
       <c r="C5" t="n">
-        <v>8547</v>
+        <v>7892</v>
       </c>
       <c r="D5" t="n">
-        <v>3896</v>
+        <v>5030</v>
       </c>
     </row>
     <row r="6">
@@ -2702,13 +2702,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>855</v>
+        <v>878</v>
       </c>
       <c r="C6" t="n">
-        <v>5647</v>
+        <v>5495</v>
       </c>
       <c r="D6" t="n">
-        <v>1125</v>
+        <v>1407</v>
       </c>
     </row>
     <row r="7">
@@ -2716,13 +2716,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>155</v>
+        <v>147</v>
       </c>
       <c r="C7" t="n">
-        <v>3542</v>
+        <v>2894</v>
       </c>
       <c r="D7" t="n">
-        <v>544</v>
+        <v>583</v>
       </c>
     </row>
     <row r="8">
@@ -2730,13 +2730,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C8" t="n">
-        <v>1445</v>
+        <v>1063</v>
       </c>
       <c r="D8" t="n">
-        <v>371</v>
+        <v>375</v>
       </c>
     </row>
     <row r="9">
@@ -2747,10 +2747,10 @@
         <v>17</v>
       </c>
       <c r="C9" t="n">
-        <v>326</v>
+        <v>266</v>
       </c>
       <c r="D9" t="n">
-        <v>282</v>
+        <v>285</v>
       </c>
     </row>
     <row r="10">
@@ -2761,10 +2761,10 @@
         <v>8</v>
       </c>
       <c r="C10" t="n">
-        <v>183</v>
+        <v>179</v>
       </c>
       <c r="D10" t="n">
-        <v>163</v>
+        <v>166</v>
       </c>
     </row>
     <row r="11">
@@ -2778,7 +2778,7 @@
         <v>110</v>
       </c>
       <c r="D11" t="n">
-        <v>127</v>
+        <v>129</v>
       </c>
     </row>
     <row r="12">
@@ -2789,10 +2789,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="D12" t="n">
-        <v>98</v>
+        <v>99</v>
       </c>
     </row>
     <row r="13">
@@ -2806,7 +2806,7 @@
         <v>51</v>
       </c>
       <c r="D13" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="14">
@@ -2817,10 +2817,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D14" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
     </row>
     <row r="15">
@@ -2834,7 +2834,7 @@
         <v>33</v>
       </c>
       <c r="D15" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="16">
@@ -2848,7 +2848,7 @@
         <v>30</v>
       </c>
       <c r="D16" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="17">
@@ -2859,7 +2859,7 @@
         <v>5</v>
       </c>
       <c r="C17" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D17" t="n">
         <v>12</v>
@@ -2957,13 +2957,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3490</v>
+        <v>4155</v>
       </c>
       <c r="C2" t="n">
-        <v>3495</v>
+        <v>10536</v>
       </c>
       <c r="D2" t="n">
-        <v>14423</v>
+        <v>20306</v>
       </c>
     </row>
     <row r="3">
@@ -2971,13 +2971,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2747</v>
+        <v>3252</v>
       </c>
       <c r="C3" t="n">
-        <v>3110</v>
+        <v>4048</v>
       </c>
       <c r="D3" t="n">
-        <v>13508</v>
+        <v>17176</v>
       </c>
     </row>
     <row r="4">
@@ -2985,13 +2985,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3093</v>
+        <v>3438</v>
       </c>
       <c r="C4" t="n">
-        <v>6132</v>
+        <v>5990</v>
       </c>
       <c r="D4" t="n">
-        <v>10651</v>
+        <v>12983</v>
       </c>
     </row>
     <row r="5">
@@ -2999,13 +2999,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2131</v>
+        <v>2310</v>
       </c>
       <c r="C5" t="n">
-        <v>8091</v>
+        <v>7341</v>
       </c>
       <c r="D5" t="n">
-        <v>4695</v>
+        <v>5949</v>
       </c>
     </row>
     <row r="6">
@@ -3013,13 +3013,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1097</v>
+        <v>1150</v>
       </c>
       <c r="C6" t="n">
-        <v>6848</v>
+        <v>6488</v>
       </c>
       <c r="D6" t="n">
-        <v>1482</v>
+        <v>1875</v>
       </c>
     </row>
     <row r="7">
@@ -3030,10 +3030,10 @@
         <v>318</v>
       </c>
       <c r="C7" t="n">
-        <v>4435</v>
+        <v>3969</v>
       </c>
       <c r="D7" t="n">
-        <v>617</v>
+        <v>687</v>
       </c>
     </row>
     <row r="8">
@@ -3041,13 +3041,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="C8" t="n">
-        <v>2212</v>
+        <v>1729</v>
       </c>
       <c r="D8" t="n">
-        <v>389</v>
+        <v>397</v>
       </c>
     </row>
     <row r="9">
@@ -3058,10 +3058,10 @@
         <v>21</v>
       </c>
       <c r="C9" t="n">
-        <v>686</v>
+        <v>523</v>
       </c>
       <c r="D9" t="n">
-        <v>289</v>
+        <v>292</v>
       </c>
     </row>
     <row r="10">
@@ -3072,10 +3072,10 @@
         <v>8</v>
       </c>
       <c r="C10" t="n">
-        <v>226</v>
+        <v>207</v>
       </c>
       <c r="D10" t="n">
-        <v>172</v>
+        <v>175</v>
       </c>
     </row>
     <row r="11">
@@ -3086,10 +3086,10 @@
         <v>2</v>
       </c>
       <c r="C11" t="n">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="D11" t="n">
-        <v>131</v>
+        <v>133</v>
       </c>
     </row>
     <row r="12">
@@ -3100,10 +3100,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="D12" t="n">
-        <v>99</v>
+        <v>100</v>
       </c>
     </row>
     <row r="13">
@@ -3117,7 +3117,7 @@
         <v>59</v>
       </c>
       <c r="D13" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="14">
@@ -3128,10 +3128,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D14" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
     <row r="15">
@@ -3145,7 +3145,7 @@
         <v>36</v>
       </c>
       <c r="D15" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="16">
@@ -3156,10 +3156,10 @@
         <v>4</v>
       </c>
       <c r="C16" t="n">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D16" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="17">
@@ -3170,7 +3170,7 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D17" t="n">
         <v>9</v>
@@ -3268,13 +3268,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2475</v>
+        <v>2945</v>
       </c>
       <c r="C2" t="n">
-        <v>2179</v>
+        <v>6062</v>
       </c>
       <c r="D2" t="n">
-        <v>10442</v>
+        <v>14370</v>
       </c>
     </row>
     <row r="3">
@@ -3282,13 +3282,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2615</v>
+        <v>3097</v>
       </c>
       <c r="C3" t="n">
-        <v>2991</v>
+        <v>6001</v>
       </c>
       <c r="D3" t="n">
-        <v>13012</v>
+        <v>16782</v>
       </c>
     </row>
     <row r="4">
@@ -3296,13 +3296,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2757</v>
+        <v>3088</v>
       </c>
       <c r="C4" t="n">
-        <v>4932</v>
+        <v>5216</v>
       </c>
       <c r="D4" t="n">
-        <v>10786</v>
+        <v>13236</v>
       </c>
     </row>
     <row r="5">
@@ -3310,13 +3310,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2312</v>
+        <v>2522</v>
       </c>
       <c r="C5" t="n">
-        <v>7537</v>
+        <v>6990</v>
       </c>
       <c r="D5" t="n">
-        <v>5226</v>
+        <v>6568</v>
       </c>
     </row>
     <row r="6">
@@ -3324,13 +3324,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1276</v>
+        <v>1345</v>
       </c>
       <c r="C6" t="n">
-        <v>7508</v>
+        <v>7016</v>
       </c>
       <c r="D6" t="n">
-        <v>1785</v>
+        <v>2259</v>
       </c>
     </row>
     <row r="7">
@@ -3341,10 +3341,10 @@
         <v>284</v>
       </c>
       <c r="C7" t="n">
-        <v>5305</v>
+        <v>4832</v>
       </c>
       <c r="D7" t="n">
-        <v>682</v>
+        <v>770</v>
       </c>
     </row>
     <row r="8">
@@ -3352,13 +3352,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="C8" t="n">
-        <v>2766</v>
+        <v>2235</v>
       </c>
       <c r="D8" t="n">
-        <v>401</v>
+        <v>412</v>
       </c>
     </row>
     <row r="9">
@@ -3369,7 +3369,7 @@
         <v>15</v>
       </c>
       <c r="C9" t="n">
-        <v>774</v>
+        <v>601</v>
       </c>
       <c r="D9" t="n">
         <v>288</v>
@@ -3383,10 +3383,10 @@
         <v>3</v>
       </c>
       <c r="C10" t="n">
-        <v>230</v>
+        <v>213</v>
       </c>
       <c r="D10" t="n">
-        <v>175</v>
+        <v>178</v>
       </c>
     </row>
     <row r="11">
@@ -3397,10 +3397,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="D11" t="n">
-        <v>133</v>
+        <v>135</v>
       </c>
     </row>
     <row r="12">
@@ -3411,7 +3411,7 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="D12" t="n">
         <v>91</v>
@@ -3425,7 +3425,7 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="D13" t="n">
         <v>61</v>
@@ -3442,7 +3442,7 @@
         <v>35</v>
       </c>
       <c r="D14" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="15">
@@ -3453,10 +3453,10 @@
         <v>3</v>
       </c>
       <c r="C15" t="n">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D15" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="16">
@@ -3467,7 +3467,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D16" t="n">
         <v>8</v>
@@ -3579,13 +3579,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3236</v>
+        <v>3877</v>
       </c>
       <c r="C2" t="n">
-        <v>5722</v>
+        <v>6677</v>
       </c>
       <c r="D2" t="n">
-        <v>11066</v>
+        <v>18346</v>
       </c>
     </row>
     <row r="3">
@@ -3593,13 +3593,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2160</v>
+        <v>2563</v>
       </c>
       <c r="C3" t="n">
-        <v>2374</v>
+        <v>5417</v>
       </c>
       <c r="D3" t="n">
-        <v>11870</v>
+        <v>15418</v>
       </c>
     </row>
     <row r="4">
@@ -3607,13 +3607,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2353</v>
+        <v>2686</v>
       </c>
       <c r="C4" t="n">
-        <v>4009</v>
+        <v>5431</v>
       </c>
       <c r="D4" t="n">
-        <v>10778</v>
+        <v>13344</v>
       </c>
     </row>
     <row r="5">
@@ -3621,13 +3621,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2249</v>
+        <v>2499</v>
       </c>
       <c r="C5" t="n">
-        <v>6329</v>
+        <v>6146</v>
       </c>
       <c r="D5" t="n">
-        <v>5814</v>
+        <v>7264</v>
       </c>
     </row>
     <row r="6">
@@ -3635,13 +3635,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1511</v>
+        <v>1593</v>
       </c>
       <c r="C6" t="n">
-        <v>7456</v>
+        <v>6948</v>
       </c>
       <c r="D6" t="n">
-        <v>2191</v>
+        <v>2767</v>
       </c>
     </row>
     <row r="7">
@@ -3649,13 +3649,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>526</v>
+        <v>547</v>
       </c>
       <c r="C7" t="n">
-        <v>6175</v>
+        <v>5621</v>
       </c>
       <c r="D7" t="n">
-        <v>804</v>
+        <v>937</v>
       </c>
     </row>
     <row r="8">
@@ -3663,13 +3663,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="C8" t="n">
-        <v>3635</v>
+        <v>3146</v>
       </c>
       <c r="D8" t="n">
-        <v>427</v>
+        <v>446</v>
       </c>
     </row>
     <row r="9">
@@ -3680,10 +3680,10 @@
         <v>22</v>
       </c>
       <c r="C9" t="n">
-        <v>1425</v>
+        <v>1113</v>
       </c>
       <c r="D9" t="n">
-        <v>296</v>
+        <v>297</v>
       </c>
     </row>
     <row r="10">
@@ -3694,10 +3694,10 @@
         <v>4</v>
       </c>
       <c r="C10" t="n">
-        <v>392</v>
+        <v>329</v>
       </c>
       <c r="D10" t="n">
-        <v>183</v>
+        <v>185</v>
       </c>
     </row>
     <row r="11">
@@ -3708,10 +3708,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="D11" t="n">
-        <v>136</v>
+        <v>138</v>
       </c>
     </row>
     <row r="12">
@@ -3722,7 +3722,7 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="D12" t="n">
         <v>93</v>
@@ -3736,7 +3736,7 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D13" t="n">
         <v>62</v>
@@ -3764,10 +3764,10 @@
         <v>2</v>
       </c>
       <c r="C15" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D15" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="16">
@@ -3778,7 +3778,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D16" t="n">
         <v>7</v>
@@ -3890,13 +3890,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>8240</v>
+        <v>6352</v>
       </c>
       <c r="C2" t="n">
-        <v>13228</v>
+        <v>4263</v>
       </c>
       <c r="D2" t="n">
-        <v>3322</v>
+        <v>9623</v>
       </c>
     </row>
     <row r="3">
@@ -4201,13 +4201,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2341</v>
+        <v>2804</v>
       </c>
       <c r="C2" t="n">
-        <v>3295</v>
+        <v>3845</v>
       </c>
       <c r="D2" t="n">
-        <v>8233</v>
+        <v>13649</v>
       </c>
     </row>
     <row r="3">
@@ -4215,13 +4215,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2861</v>
+        <v>3363</v>
       </c>
       <c r="C3" t="n">
-        <v>3332</v>
+        <v>6175</v>
       </c>
       <c r="D3" t="n">
-        <v>12739</v>
+        <v>16725</v>
       </c>
     </row>
     <row r="4">
@@ -4229,13 +4229,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3279</v>
+        <v>3681</v>
       </c>
       <c r="C4" t="n">
-        <v>6081</v>
+        <v>7680</v>
       </c>
       <c r="D4" t="n">
-        <v>11017</v>
+        <v>13656</v>
       </c>
     </row>
     <row r="5">
@@ -4243,13 +4243,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1437</v>
+        <v>1518</v>
       </c>
       <c r="C5" t="n">
-        <v>9989</v>
+        <v>9468</v>
       </c>
       <c r="D5" t="n">
-        <v>5259</v>
+        <v>6585</v>
       </c>
     </row>
     <row r="6">
@@ -4257,13 +4257,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>486</v>
+        <v>505</v>
       </c>
       <c r="C6" t="n">
-        <v>7439</v>
+        <v>6802</v>
       </c>
       <c r="D6" t="n">
-        <v>1759</v>
+        <v>2154</v>
       </c>
     </row>
     <row r="7">
@@ -4271,13 +4271,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="C7" t="n">
-        <v>3562</v>
+        <v>3083</v>
       </c>
       <c r="D7" t="n">
-        <v>520</v>
+        <v>556</v>
       </c>
     </row>
     <row r="8">
@@ -4288,10 +4288,10 @@
         <v>20</v>
       </c>
       <c r="C8" t="n">
-        <v>1396</v>
+        <v>1090</v>
       </c>
       <c r="D8" t="n">
-        <v>290</v>
+        <v>291</v>
       </c>
     </row>
     <row r="9">
@@ -4302,10 +4302,10 @@
         <v>3</v>
       </c>
       <c r="C9" t="n">
-        <v>384</v>
+        <v>322</v>
       </c>
       <c r="D9" t="n">
-        <v>179</v>
+        <v>181</v>
       </c>
     </row>
     <row r="10">
@@ -4316,10 +4316,10 @@
         <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>152</v>
+        <v>148</v>
       </c>
       <c r="D10" t="n">
-        <v>133</v>
+        <v>135</v>
       </c>
     </row>
     <row r="11">
@@ -4330,7 +4330,7 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="D11" t="n">
         <v>91</v>
@@ -4372,10 +4372,10 @@
         <v>1</v>
       </c>
       <c r="C14" t="n">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D14" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="15">
@@ -4386,7 +4386,7 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D15" t="n">
         <v>6</v>
@@ -4512,13 +4512,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7151</v>
+        <v>6686</v>
       </c>
       <c r="C2" t="n">
-        <v>8617</v>
+        <v>9194</v>
       </c>
       <c r="D2" t="n">
-        <v>13189</v>
+        <v>27275</v>
       </c>
     </row>
     <row r="3">
@@ -4526,13 +4526,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3499</v>
+        <v>2698</v>
       </c>
       <c r="C3" t="n">
-        <v>6666</v>
+        <v>2148</v>
       </c>
       <c r="D3" t="n">
-        <v>1197</v>
+        <v>2255</v>
       </c>
     </row>
     <row r="4">
@@ -4543,7 +4543,7 @@
         <v>79</v>
       </c>
       <c r="C4" t="n">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="D4" t="n">
         <v>1538</v>
@@ -4554,10 +4554,10 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="C5" t="n">
-        <v>381</v>
+        <v>384</v>
       </c>
       <c r="D5" t="n">
         <v>1161</v>
@@ -4568,13 +4568,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="C6" t="n">
         <v>459</v>
       </c>
       <c r="D6" t="n">
-        <v>816</v>
+        <v>808</v>
       </c>
     </row>
     <row r="7">
@@ -4588,7 +4588,7 @@
         <v>350</v>
       </c>
       <c r="D7" t="n">
-        <v>538</v>
+        <v>546</v>
       </c>
     </row>
     <row r="8">
@@ -4823,13 +4823,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4651</v>
+        <v>5719</v>
       </c>
       <c r="C2" t="n">
-        <v>8680</v>
+        <v>5728</v>
       </c>
       <c r="D2" t="n">
-        <v>17412</v>
+        <v>26292</v>
       </c>
     </row>
     <row r="3">
@@ -4837,13 +4837,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4378</v>
+        <v>3854</v>
       </c>
       <c r="C3" t="n">
-        <v>6700</v>
+        <v>5290</v>
       </c>
       <c r="D3" t="n">
-        <v>3123</v>
+        <v>6292</v>
       </c>
     </row>
     <row r="4">
@@ -4851,13 +4851,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1554</v>
+        <v>1206</v>
       </c>
       <c r="C4" t="n">
-        <v>3949</v>
+        <v>1302</v>
       </c>
       <c r="D4" t="n">
-        <v>1422</v>
+        <v>1635</v>
       </c>
     </row>
     <row r="5">
@@ -4865,10 +4865,10 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="C5" t="n">
-        <v>223</v>
+        <v>219</v>
       </c>
       <c r="D5" t="n">
         <v>1198</v>
@@ -4882,10 +4882,10 @@
         <v>185</v>
       </c>
       <c r="C6" t="n">
-        <v>406</v>
+        <v>411</v>
       </c>
       <c r="D6" t="n">
-        <v>859</v>
+        <v>853</v>
       </c>
     </row>
     <row r="7">
@@ -4893,13 +4893,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="C7" t="n">
         <v>409</v>
       </c>
       <c r="D7" t="n">
-        <v>584</v>
+        <v>589</v>
       </c>
     </row>
     <row r="8">
@@ -4913,7 +4913,7 @@
         <v>307</v>
       </c>
       <c r="D8" t="n">
-        <v>439</v>
+        <v>441</v>
       </c>
     </row>
     <row r="9">
@@ -4952,7 +4952,7 @@
         <v>43</v>
       </c>
       <c r="C11" t="n">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="D11" t="n">
         <v>270</v>
@@ -4966,7 +4966,7 @@
         <v>28</v>
       </c>
       <c r="C12" t="n">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="D12" t="n">
         <v>206</v>
@@ -5025,7 +5025,7 @@
         <v>71</v>
       </c>
       <c r="D16" t="n">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="17">
@@ -5039,7 +5039,7 @@
         <v>67</v>
       </c>
       <c r="D17" t="n">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="18">
@@ -5134,13 +5134,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4860</v>
+        <v>6337</v>
       </c>
       <c r="C2" t="n">
-        <v>7218</v>
+        <v>11192</v>
       </c>
       <c r="D2" t="n">
-        <v>27837</v>
+        <v>32324</v>
       </c>
     </row>
     <row r="3">
@@ -5148,13 +5148,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3762</v>
+        <v>3916</v>
       </c>
       <c r="C3" t="n">
-        <v>6728</v>
+        <v>4785</v>
       </c>
       <c r="D3" t="n">
-        <v>5184</v>
+        <v>9038</v>
       </c>
     </row>
     <row r="4">
@@ -5162,13 +5162,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2492</v>
+        <v>2153</v>
       </c>
       <c r="C4" t="n">
-        <v>5398</v>
+        <v>3533</v>
       </c>
       <c r="D4" t="n">
-        <v>1705</v>
+        <v>2479</v>
       </c>
     </row>
     <row r="5">
@@ -5176,13 +5176,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>685</v>
+        <v>544</v>
       </c>
       <c r="C5" t="n">
-        <v>2219</v>
+        <v>807</v>
       </c>
       <c r="D5" t="n">
-        <v>1190</v>
+        <v>1229</v>
       </c>
     </row>
     <row r="6">
@@ -5190,13 +5190,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="C6" t="n">
         <v>304</v>
       </c>
       <c r="D6" t="n">
-        <v>908</v>
+        <v>903</v>
       </c>
     </row>
     <row r="7">
@@ -5204,13 +5204,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="C7" t="n">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="D7" t="n">
-        <v>626</v>
+        <v>629</v>
       </c>
     </row>
     <row r="8">
@@ -5218,13 +5218,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="C8" t="n">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="D8" t="n">
-        <v>454</v>
+        <v>456</v>
       </c>
     </row>
     <row r="9">
@@ -5232,13 +5232,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C9" t="n">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c r="D9" t="n">
-        <v>371</v>
+        <v>372</v>
       </c>
     </row>
     <row r="10">
@@ -5260,10 +5260,10 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C11" t="n">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="D11" t="n">
         <v>280</v>
@@ -5277,7 +5277,7 @@
         <v>31</v>
       </c>
       <c r="C12" t="n">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="D12" t="n">
         <v>213</v>
@@ -5291,7 +5291,7 @@
         <v>21</v>
       </c>
       <c r="C13" t="n">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="D13" t="n">
         <v>173</v>
@@ -5319,10 +5319,10 @@
         <v>12</v>
       </c>
       <c r="C15" t="n">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D15" t="n">
-        <v>122</v>
+        <v>120</v>
       </c>
     </row>
     <row r="16">
@@ -5333,7 +5333,7 @@
         <v>12</v>
       </c>
       <c r="C16" t="n">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="D16" t="n">
         <v>99</v>
@@ -5350,7 +5350,7 @@
         <v>68</v>
       </c>
       <c r="D17" t="n">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="18">
@@ -5375,7 +5375,7 @@
         <v>10</v>
       </c>
       <c r="C19" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D19" t="n">
         <v>41</v>
@@ -5445,13 +5445,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6748</v>
+        <v>5804</v>
       </c>
       <c r="C2" t="n">
-        <v>7187</v>
+        <v>8791</v>
       </c>
       <c r="D2" t="n">
-        <v>22607</v>
+        <v>30660</v>
       </c>
     </row>
     <row r="3">
@@ -5459,13 +5459,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3519</v>
+        <v>4133</v>
       </c>
       <c r="C3" t="n">
-        <v>6082</v>
+        <v>7035</v>
       </c>
       <c r="D3" t="n">
-        <v>8262</v>
+        <v>11941</v>
       </c>
     </row>
     <row r="4">
@@ -5473,13 +5473,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2663</v>
+        <v>2543</v>
       </c>
       <c r="C4" t="n">
-        <v>5987</v>
+        <v>4132</v>
       </c>
       <c r="D4" t="n">
-        <v>2287</v>
+        <v>3600</v>
       </c>
     </row>
     <row r="5">
@@ -5487,13 +5487,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1294</v>
+        <v>1111</v>
       </c>
       <c r="C5" t="n">
-        <v>3769</v>
+        <v>2203</v>
       </c>
       <c r="D5" t="n">
-        <v>1242</v>
+        <v>1395</v>
       </c>
     </row>
     <row r="6">
@@ -5501,13 +5501,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>352</v>
+        <v>295</v>
       </c>
       <c r="C6" t="n">
-        <v>1256</v>
+        <v>548</v>
       </c>
       <c r="D6" t="n">
-        <v>932</v>
+        <v>946</v>
       </c>
     </row>
     <row r="7">
@@ -5515,13 +5515,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="C7" t="n">
-        <v>356</v>
+        <v>354</v>
       </c>
       <c r="D7" t="n">
-        <v>666</v>
+        <v>662</v>
       </c>
     </row>
     <row r="8">
@@ -5532,10 +5532,10 @@
         <v>128</v>
       </c>
       <c r="C8" t="n">
-        <v>376</v>
+        <v>380</v>
       </c>
       <c r="D8" t="n">
-        <v>471</v>
+        <v>480</v>
       </c>
     </row>
     <row r="9">
@@ -5543,13 +5543,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="C9" t="n">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="D9" t="n">
-        <v>380</v>
+        <v>381</v>
       </c>
     </row>
     <row r="10">
@@ -5560,7 +5560,7 @@
         <v>70</v>
       </c>
       <c r="C10" t="n">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="D10" t="n">
         <v>342</v>
@@ -5571,7 +5571,7 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C11" t="n">
         <v>189</v>
@@ -5585,13 +5585,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C12" t="n">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="D12" t="n">
-        <v>220</v>
+        <v>217</v>
       </c>
     </row>
     <row r="13">
@@ -5602,10 +5602,10 @@
         <v>22</v>
       </c>
       <c r="C13" t="n">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="D13" t="n">
-        <v>174</v>
+        <v>176</v>
       </c>
     </row>
     <row r="14">
@@ -5616,10 +5616,10 @@
         <v>15</v>
       </c>
       <c r="C14" t="n">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="D14" t="n">
-        <v>149</v>
+        <v>148</v>
       </c>
     </row>
     <row r="15">
@@ -5630,7 +5630,7 @@
         <v>12</v>
       </c>
       <c r="C15" t="n">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="D15" t="n">
         <v>122</v>
@@ -5658,10 +5658,10 @@
         <v>10</v>
       </c>
       <c r="C17" t="n">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="D17" t="n">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="18">
@@ -5689,7 +5689,7 @@
         <v>62</v>
       </c>
       <c r="D19" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="20">
@@ -5700,7 +5700,7 @@
         <v>7</v>
       </c>
       <c r="C20" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D20" t="n">
         <v>24</v>
@@ -5756,13 +5756,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6357</v>
+        <v>7595</v>
       </c>
       <c r="C2" t="n">
-        <v>6356</v>
+        <v>8395</v>
       </c>
       <c r="D2" t="n">
-        <v>30351</v>
+        <v>27765</v>
       </c>
     </row>
     <row r="3">
@@ -5770,13 +5770,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3658</v>
+        <v>3627</v>
       </c>
       <c r="C3" t="n">
-        <v>5435</v>
+        <v>6488</v>
       </c>
       <c r="D3" t="n">
-        <v>9171</v>
+        <v>13120</v>
       </c>
     </row>
     <row r="4">
@@ -5784,13 +5784,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1913</v>
+        <v>2042</v>
       </c>
       <c r="C4" t="n">
-        <v>4887</v>
+        <v>4635</v>
       </c>
       <c r="D4" t="n">
-        <v>2814</v>
+        <v>4375</v>
       </c>
     </row>
     <row r="5">
@@ -5798,13 +5798,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1021</v>
+        <v>942</v>
       </c>
       <c r="C5" t="n">
-        <v>3571</v>
+        <v>2340</v>
       </c>
       <c r="D5" t="n">
-        <v>1121</v>
+        <v>1393</v>
       </c>
     </row>
     <row r="6">
@@ -5812,13 +5812,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>381</v>
+        <v>331</v>
       </c>
       <c r="C6" t="n">
-        <v>1656</v>
+        <v>915</v>
       </c>
       <c r="D6" t="n">
-        <v>740</v>
+        <v>778</v>
       </c>
     </row>
     <row r="7">
@@ -5826,13 +5826,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>105</v>
+        <v>95</v>
       </c>
       <c r="C7" t="n">
-        <v>502</v>
+        <v>287</v>
       </c>
       <c r="D7" t="n">
-        <v>520</v>
+        <v>514</v>
       </c>
     </row>
     <row r="8">
@@ -5843,10 +5843,10 @@
         <v>57</v>
       </c>
       <c r="C8" t="n">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="D8" t="n">
-        <v>352</v>
+        <v>361</v>
       </c>
     </row>
     <row r="9">
@@ -5854,13 +5854,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C9" t="n">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="D9" t="n">
-        <v>272</v>
+        <v>274</v>
       </c>
     </row>
     <row r="10">
@@ -5868,10 +5868,10 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C10" t="n">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="D10" t="n">
         <v>233</v>
@@ -5896,13 +5896,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C12" t="n">
         <v>91</v>
       </c>
       <c r="D12" t="n">
-        <v>148</v>
+        <v>147</v>
       </c>
     </row>
     <row r="13">
@@ -5916,7 +5916,7 @@
         <v>73</v>
       </c>
       <c r="D13" t="n">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="14">
@@ -5958,7 +5958,7 @@
         <v>38</v>
       </c>
       <c r="D16" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="17">
@@ -5969,10 +5969,10 @@
         <v>3</v>
       </c>
       <c r="C17" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D17" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="18">
@@ -5980,10 +5980,10 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C18" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D18" t="n">
         <v>38</v>
@@ -6011,7 +6011,7 @@
         <v>2</v>
       </c>
       <c r="C20" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D20" t="n">
         <v>15</v>
@@ -6067,13 +6067,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5103</v>
+        <v>6682</v>
       </c>
       <c r="C2" t="n">
-        <v>7832</v>
+        <v>4390</v>
       </c>
       <c r="D2" t="n">
-        <v>22015</v>
+        <v>24797</v>
       </c>
     </row>
     <row r="3">
@@ -6081,13 +6081,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4120</v>
+        <v>4642</v>
       </c>
       <c r="C3" t="n">
-        <v>5135</v>
+        <v>6530</v>
       </c>
       <c r="D3" t="n">
-        <v>12054</v>
+        <v>14614</v>
       </c>
     </row>
     <row r="4">
@@ -6095,13 +6095,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2404</v>
+        <v>2476</v>
       </c>
       <c r="C4" t="n">
-        <v>5111</v>
+        <v>5641</v>
       </c>
       <c r="D4" t="n">
-        <v>4010</v>
+        <v>6004</v>
       </c>
     </row>
     <row r="5">
@@ -6109,13 +6109,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1305</v>
+        <v>1313</v>
       </c>
       <c r="C5" t="n">
-        <v>4254</v>
+        <v>3590</v>
       </c>
       <c r="D5" t="n">
-        <v>1401</v>
+        <v>1909</v>
       </c>
     </row>
     <row r="6">
@@ -6123,13 +6123,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>639</v>
+        <v>588</v>
       </c>
       <c r="C6" t="n">
-        <v>2702</v>
+        <v>1710</v>
       </c>
       <c r="D6" t="n">
-        <v>802</v>
+        <v>885</v>
       </c>
     </row>
     <row r="7">
@@ -6137,13 +6137,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>218</v>
+        <v>192</v>
       </c>
       <c r="C7" t="n">
-        <v>1135</v>
+        <v>637</v>
       </c>
       <c r="D7" t="n">
-        <v>555</v>
+        <v>552</v>
       </c>
     </row>
     <row r="8">
@@ -6151,13 +6151,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>73</v>
+        <v>68</v>
       </c>
       <c r="C8" t="n">
-        <v>367</v>
+        <v>257</v>
       </c>
       <c r="D8" t="n">
-        <v>374</v>
+        <v>385</v>
       </c>
     </row>
     <row r="9">
@@ -6165,13 +6165,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C9" t="n">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="D9" t="n">
-        <v>283</v>
+        <v>286</v>
       </c>
     </row>
     <row r="10">
@@ -6182,10 +6182,10 @@
         <v>33</v>
       </c>
       <c r="C10" t="n">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="D10" t="n">
-        <v>237</v>
+        <v>235</v>
       </c>
     </row>
     <row r="11">
@@ -6196,10 +6196,10 @@
         <v>23</v>
       </c>
       <c r="C11" t="n">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="D11" t="n">
-        <v>197</v>
+        <v>199</v>
       </c>
     </row>
     <row r="12">
@@ -6210,7 +6210,7 @@
         <v>15</v>
       </c>
       <c r="C12" t="n">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D12" t="n">
         <v>153</v>
@@ -6221,13 +6221,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C13" t="n">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="D13" t="n">
-        <v>118</v>
+        <v>119</v>
       </c>
     </row>
     <row r="14">
@@ -6235,13 +6235,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C14" t="n">
         <v>63</v>
       </c>
       <c r="D14" t="n">
-        <v>97</v>
+        <v>98</v>
       </c>
     </row>
     <row r="15">
@@ -6269,7 +6269,7 @@
         <v>40</v>
       </c>
       <c r="D16" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="17">
@@ -6280,10 +6280,10 @@
         <v>2</v>
       </c>
       <c r="C17" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D17" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="18">
@@ -6297,7 +6297,7 @@
         <v>33</v>
       </c>
       <c r="D18" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="19">
@@ -6305,7 +6305,7 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C19" t="n">
         <v>31</v>
@@ -6322,7 +6322,7 @@
         <v>1</v>
       </c>
       <c r="C20" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D20" t="n">
         <v>16</v>
@@ -6378,13 +6378,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4996</v>
+        <v>5180</v>
       </c>
       <c r="C2" t="n">
-        <v>9758</v>
+        <v>6902</v>
       </c>
       <c r="D2" t="n">
-        <v>28362</v>
+        <v>24147</v>
       </c>
     </row>
     <row r="3">
@@ -6392,13 +6392,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3784</v>
+        <v>4622</v>
       </c>
       <c r="C3" t="n">
-        <v>5691</v>
+        <v>4669</v>
       </c>
       <c r="D3" t="n">
-        <v>12719</v>
+        <v>15191</v>
       </c>
     </row>
     <row r="4">
@@ -6406,13 +6406,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2790</v>
+        <v>3016</v>
       </c>
       <c r="C4" t="n">
-        <v>5017</v>
+        <v>6018</v>
       </c>
       <c r="D4" t="n">
-        <v>5316</v>
+        <v>7474</v>
       </c>
     </row>
     <row r="5">
@@ -6420,13 +6420,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1605</v>
+        <v>1658</v>
       </c>
       <c r="C5" t="n">
-        <v>4577</v>
+        <v>4617</v>
       </c>
       <c r="D5" t="n">
-        <v>1834</v>
+        <v>2597</v>
       </c>
     </row>
     <row r="6">
@@ -6434,13 +6434,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>879</v>
+        <v>850</v>
       </c>
       <c r="C6" t="n">
-        <v>3476</v>
+        <v>2665</v>
       </c>
       <c r="D6" t="n">
-        <v>886</v>
+        <v>1041</v>
       </c>
     </row>
     <row r="7">
@@ -6448,13 +6448,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>370</v>
+        <v>341</v>
       </c>
       <c r="C7" t="n">
-        <v>1933</v>
+        <v>1177</v>
       </c>
       <c r="D7" t="n">
-        <v>592</v>
+        <v>605</v>
       </c>
     </row>
     <row r="8">
@@ -6462,13 +6462,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>125</v>
+        <v>111</v>
       </c>
       <c r="C8" t="n">
-        <v>739</v>
+        <v>446</v>
       </c>
       <c r="D8" t="n">
-        <v>400</v>
+        <v>405</v>
       </c>
     </row>
     <row r="9">
@@ -6476,13 +6476,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C9" t="n">
-        <v>284</v>
+        <v>232</v>
       </c>
       <c r="D9" t="n">
-        <v>291</v>
+        <v>299</v>
       </c>
     </row>
     <row r="10">
@@ -6496,7 +6496,7 @@
         <v>188</v>
       </c>
       <c r="D10" t="n">
-        <v>241</v>
+        <v>240</v>
       </c>
     </row>
     <row r="11">
@@ -6504,13 +6504,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C11" t="n">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="D11" t="n">
-        <v>198</v>
+        <v>200</v>
       </c>
     </row>
     <row r="12">
@@ -6524,7 +6524,7 @@
         <v>113</v>
       </c>
       <c r="D12" t="n">
-        <v>157</v>
+        <v>158</v>
       </c>
     </row>
     <row r="13">
@@ -6532,7 +6532,7 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C13" t="n">
         <v>88</v>
@@ -6546,13 +6546,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C14" t="n">
         <v>69</v>
       </c>
       <c r="D14" t="n">
-        <v>97</v>
+        <v>99</v>
       </c>
     </row>
     <row r="15">
@@ -6563,7 +6563,7 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="D15" t="n">
         <v>81</v>
@@ -6580,7 +6580,7 @@
         <v>43</v>
       </c>
       <c r="D16" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="17">
@@ -6591,7 +6591,7 @@
         <v>2</v>
       </c>
       <c r="C17" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D17" t="n">
         <v>51</v>
@@ -6608,7 +6608,7 @@
         <v>33</v>
       </c>
       <c r="D18" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="19">
@@ -6622,7 +6622,7 @@
         <v>31</v>
       </c>
       <c r="D19" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="20">
@@ -6630,10 +6630,10 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D20" t="n">
         <v>16</v>

--- a/output/yearly_population_iteration_4_growth_param_0.5.xlsx
+++ b/output/yearly_population_iteration_4_growth_param_0.5.xlsx
@@ -780,13 +780,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5331</v>
+        <v>724</v>
       </c>
       <c r="C2" t="n">
-        <v>8765</v>
+        <v>2105</v>
       </c>
       <c r="D2" t="n">
-        <v>29088</v>
+        <v>14952</v>
       </c>
     </row>
     <row r="3">
@@ -794,13 +794,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4028</v>
+        <v>1473</v>
       </c>
       <c r="C3" t="n">
-        <v>5033</v>
+        <v>5434</v>
       </c>
       <c r="D3" t="n">
-        <v>15435</v>
+        <v>13899</v>
       </c>
     </row>
     <row r="4">
@@ -808,13 +808,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3197</v>
+        <v>957</v>
       </c>
       <c r="C4" t="n">
-        <v>5206</v>
+        <v>7153</v>
       </c>
       <c r="D4" t="n">
-        <v>8580</v>
+        <v>6058</v>
       </c>
     </row>
     <row r="5">
@@ -822,13 +822,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2008</v>
+        <v>425</v>
       </c>
       <c r="C5" t="n">
-        <v>5162</v>
+        <v>4337</v>
       </c>
       <c r="D5" t="n">
-        <v>3289</v>
+        <v>1932</v>
       </c>
     </row>
     <row r="6">
@@ -836,13 +836,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1099</v>
+        <v>205</v>
       </c>
       <c r="C6" t="n">
-        <v>3574</v>
+        <v>1578</v>
       </c>
       <c r="D6" t="n">
-        <v>1280</v>
+        <v>760</v>
       </c>
     </row>
     <row r="7">
@@ -850,13 +850,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>506</v>
+        <v>99</v>
       </c>
       <c r="C7" t="n">
-        <v>1864</v>
+        <v>598</v>
       </c>
       <c r="D7" t="n">
-        <v>661</v>
+        <v>494</v>
       </c>
     </row>
     <row r="8">
@@ -864,13 +864,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>187</v>
+        <v>74</v>
       </c>
       <c r="C8" t="n">
-        <v>782</v>
+        <v>337</v>
       </c>
       <c r="D8" t="n">
-        <v>432</v>
+        <v>371</v>
       </c>
     </row>
     <row r="9">
@@ -878,13 +878,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>68</v>
+        <v>54</v>
       </c>
       <c r="C9" t="n">
-        <v>326</v>
+        <v>292</v>
       </c>
       <c r="D9" t="n">
-        <v>308</v>
+        <v>321</v>
       </c>
     </row>
     <row r="10">
@@ -892,13 +892,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>38</v>
+        <v>26</v>
       </c>
       <c r="C10" t="n">
-        <v>204</v>
+        <v>214</v>
       </c>
       <c r="D10" t="n">
-        <v>246</v>
+        <v>268</v>
       </c>
     </row>
     <row r="11">
@@ -906,13 +906,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="C11" t="n">
-        <v>164</v>
+        <v>177</v>
       </c>
       <c r="D11" t="n">
-        <v>201</v>
+        <v>212</v>
       </c>
     </row>
     <row r="12">
@@ -920,13 +920,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="C12" t="n">
-        <v>125</v>
+        <v>112</v>
       </c>
       <c r="D12" t="n">
-        <v>162</v>
+        <v>174</v>
       </c>
     </row>
     <row r="13">
@@ -934,13 +934,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="C13" t="n">
-        <v>97</v>
+        <v>78</v>
       </c>
       <c r="D13" t="n">
-        <v>124</v>
+        <v>139</v>
       </c>
     </row>
     <row r="14">
@@ -948,13 +948,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C14" t="n">
-        <v>75</v>
+        <v>66</v>
       </c>
       <c r="D14" t="n">
-        <v>99</v>
+        <v>89</v>
       </c>
     </row>
     <row r="15">
@@ -965,10 +965,10 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D15" t="n">
-        <v>82</v>
+        <v>72</v>
       </c>
     </row>
     <row r="16">
@@ -976,13 +976,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C16" t="n">
-        <v>46</v>
+        <v>55</v>
       </c>
       <c r="D16" t="n">
-        <v>63</v>
+        <v>53</v>
       </c>
     </row>
     <row r="17">
@@ -990,13 +990,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C17" t="n">
-        <v>38</v>
+        <v>52</v>
       </c>
       <c r="D17" t="n">
-        <v>51</v>
+        <v>37</v>
       </c>
     </row>
     <row r="18">
@@ -1004,13 +1004,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C18" t="n">
-        <v>34</v>
+        <v>50</v>
       </c>
       <c r="D18" t="n">
-        <v>39</v>
+        <v>22</v>
       </c>
     </row>
     <row r="19">
@@ -1018,13 +1018,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="C19" t="n">
-        <v>31</v>
+        <v>142</v>
       </c>
       <c r="D19" t="n">
-        <v>27</v>
+        <v>5</v>
       </c>
     </row>
     <row r="20">
@@ -1035,10 +1035,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1046,13 +1046,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>97</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1091,13 +1091,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7172</v>
+        <v>477</v>
       </c>
       <c r="C2" t="n">
-        <v>7934</v>
+        <v>3783</v>
       </c>
       <c r="D2" t="n">
-        <v>28701</v>
+        <v>15327</v>
       </c>
     </row>
     <row r="3">
@@ -1105,13 +1105,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3765</v>
+        <v>948</v>
       </c>
       <c r="C3" t="n">
-        <v>5878</v>
+        <v>3184</v>
       </c>
       <c r="D3" t="n">
-        <v>16170</v>
+        <v>13066</v>
       </c>
     </row>
     <row r="4">
@@ -1119,13 +1119,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3034</v>
+        <v>1038</v>
       </c>
       <c r="C4" t="n">
-        <v>4968</v>
+        <v>6047</v>
       </c>
       <c r="D4" t="n">
-        <v>9289</v>
+        <v>7379</v>
       </c>
     </row>
     <row r="5">
@@ -1133,13 +1133,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2212</v>
+        <v>598</v>
       </c>
       <c r="C5" t="n">
-        <v>5074</v>
+        <v>5802</v>
       </c>
       <c r="D5" t="n">
-        <v>4001</v>
+        <v>2625</v>
       </c>
     </row>
     <row r="6">
@@ -1147,13 +1147,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1354</v>
+        <v>278</v>
       </c>
       <c r="C6" t="n">
-        <v>4191</v>
+        <v>2979</v>
       </c>
       <c r="D6" t="n">
-        <v>1539</v>
+        <v>959</v>
       </c>
     </row>
     <row r="7">
@@ -1161,13 +1161,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>669</v>
+        <v>132</v>
       </c>
       <c r="C7" t="n">
-        <v>2582</v>
+        <v>1083</v>
       </c>
       <c r="D7" t="n">
-        <v>745</v>
+        <v>530</v>
       </c>
     </row>
     <row r="8">
@@ -1175,13 +1175,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>277</v>
+        <v>79</v>
       </c>
       <c r="C8" t="n">
-        <v>1237</v>
+        <v>460</v>
       </c>
       <c r="D8" t="n">
-        <v>454</v>
+        <v>385</v>
       </c>
     </row>
     <row r="9">
@@ -1189,13 +1189,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>100</v>
+        <v>57</v>
       </c>
       <c r="C9" t="n">
-        <v>505</v>
+        <v>317</v>
       </c>
       <c r="D9" t="n">
-        <v>321</v>
+        <v>327</v>
       </c>
     </row>
     <row r="10">
@@ -1203,13 +1203,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>44</v>
+        <v>31</v>
       </c>
       <c r="C10" t="n">
-        <v>251</v>
+        <v>248</v>
       </c>
       <c r="D10" t="n">
-        <v>248</v>
+        <v>274</v>
       </c>
     </row>
     <row r="11">
@@ -1217,13 +1217,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="C11" t="n">
-        <v>177</v>
+        <v>195</v>
       </c>
       <c r="D11" t="n">
-        <v>204</v>
+        <v>217</v>
       </c>
     </row>
     <row r="12">
@@ -1231,13 +1231,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="C12" t="n">
-        <v>139</v>
+        <v>134</v>
       </c>
       <c r="D12" t="n">
-        <v>163</v>
+        <v>176</v>
       </c>
     </row>
     <row r="13">
@@ -1245,13 +1245,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="C13" t="n">
-        <v>105</v>
+        <v>89</v>
       </c>
       <c r="D13" t="n">
-        <v>127</v>
+        <v>141</v>
       </c>
     </row>
     <row r="14">
@@ -1259,13 +1259,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C14" t="n">
-        <v>82</v>
+        <v>71</v>
       </c>
       <c r="D14" t="n">
-        <v>99</v>
+        <v>94</v>
       </c>
     </row>
     <row r="15">
@@ -1279,7 +1279,7 @@
         <v>63</v>
       </c>
       <c r="D15" t="n">
-        <v>82</v>
+        <v>72</v>
       </c>
     </row>
     <row r="16">
@@ -1290,10 +1290,10 @@
         <v>3</v>
       </c>
       <c r="C16" t="n">
-        <v>49</v>
+        <v>62</v>
       </c>
       <c r="D16" t="n">
-        <v>63</v>
+        <v>52</v>
       </c>
     </row>
     <row r="17">
@@ -1301,13 +1301,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C17" t="n">
-        <v>39</v>
+        <v>57</v>
       </c>
       <c r="D17" t="n">
-        <v>51</v>
+        <v>35</v>
       </c>
     </row>
     <row r="18">
@@ -1315,13 +1315,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1</v>
+        <v>17</v>
       </c>
       <c r="C18" t="n">
-        <v>34</v>
+        <v>95</v>
       </c>
       <c r="D18" t="n">
-        <v>39</v>
+        <v>18</v>
       </c>
     </row>
     <row r="19">
@@ -1332,10 +1332,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>31</v>
+        <v>79</v>
       </c>
       <c r="D19" t="n">
-        <v>27</v>
+        <v>3</v>
       </c>
     </row>
     <row r="20">
@@ -1346,10 +1346,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1357,13 +1357,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>103</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1402,13 +1402,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>8254</v>
+        <v>244</v>
       </c>
       <c r="C2" t="n">
-        <v>7332</v>
+        <v>1526</v>
       </c>
       <c r="D2" t="n">
-        <v>35005</v>
+        <v>10327</v>
       </c>
     </row>
     <row r="3">
@@ -1416,13 +1416,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4143</v>
+        <v>783</v>
       </c>
       <c r="C3" t="n">
-        <v>5952</v>
+        <v>3286</v>
       </c>
       <c r="D3" t="n">
-        <v>16638</v>
+        <v>13000</v>
       </c>
     </row>
     <row r="4">
@@ -1430,13 +1430,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2841</v>
+        <v>1123</v>
       </c>
       <c r="C4" t="n">
-        <v>5201</v>
+        <v>5347</v>
       </c>
       <c r="D4" t="n">
-        <v>9908</v>
+        <v>8164</v>
       </c>
     </row>
     <row r="5">
@@ -1444,13 +1444,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2279</v>
+        <v>603</v>
       </c>
       <c r="C5" t="n">
-        <v>4924</v>
+        <v>6587</v>
       </c>
       <c r="D5" t="n">
-        <v>4640</v>
+        <v>3029</v>
       </c>
     </row>
     <row r="6">
@@ -1458,13 +1458,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1533</v>
+        <v>249</v>
       </c>
       <c r="C6" t="n">
-        <v>4461</v>
+        <v>3919</v>
       </c>
       <c r="D6" t="n">
-        <v>1834</v>
+        <v>969</v>
       </c>
     </row>
     <row r="7">
@@ -1472,13 +1472,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>833</v>
+        <v>74</v>
       </c>
       <c r="C7" t="n">
-        <v>3186</v>
+        <v>1064</v>
       </c>
       <c r="D7" t="n">
-        <v>846</v>
+        <v>563</v>
       </c>
     </row>
     <row r="8">
@@ -1486,13 +1486,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>374</v>
+        <v>52</v>
       </c>
       <c r="C8" t="n">
-        <v>1750</v>
+        <v>481</v>
       </c>
       <c r="D8" t="n">
-        <v>481</v>
+        <v>436</v>
       </c>
     </row>
     <row r="9">
@@ -1500,13 +1500,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>144</v>
+        <v>28</v>
       </c>
       <c r="C9" t="n">
-        <v>765</v>
+        <v>243</v>
       </c>
       <c r="D9" t="n">
-        <v>334</v>
+        <v>371</v>
       </c>
     </row>
     <row r="10">
@@ -1514,13 +1514,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>56</v>
+        <v>14</v>
       </c>
       <c r="C10" t="n">
-        <v>338</v>
+        <v>191</v>
       </c>
       <c r="D10" t="n">
-        <v>251</v>
+        <v>212</v>
       </c>
     </row>
     <row r="11">
@@ -1528,13 +1528,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>30</v>
+        <v>9</v>
       </c>
       <c r="C11" t="n">
-        <v>200</v>
+        <v>131</v>
       </c>
       <c r="D11" t="n">
-        <v>207</v>
+        <v>172</v>
       </c>
     </row>
     <row r="12">
@@ -1542,13 +1542,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>19</v>
+        <v>6</v>
       </c>
       <c r="C12" t="n">
-        <v>151</v>
+        <v>87</v>
       </c>
       <c r="D12" t="n">
-        <v>164</v>
+        <v>138</v>
       </c>
     </row>
     <row r="13">
@@ -1556,13 +1556,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="C13" t="n">
-        <v>114</v>
+        <v>69</v>
       </c>
       <c r="D13" t="n">
-        <v>129</v>
+        <v>92</v>
       </c>
     </row>
     <row r="14">
@@ -1570,13 +1570,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="C14" t="n">
-        <v>88</v>
+        <v>61</v>
       </c>
       <c r="D14" t="n">
-        <v>99</v>
+        <v>70</v>
       </c>
     </row>
     <row r="15">
@@ -1584,13 +1584,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C15" t="n">
-        <v>67</v>
+        <v>60</v>
       </c>
       <c r="D15" t="n">
-        <v>82</v>
+        <v>50</v>
       </c>
     </row>
     <row r="16">
@@ -1598,13 +1598,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C16" t="n">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="D16" t="n">
-        <v>63</v>
+        <v>34</v>
       </c>
     </row>
     <row r="17">
@@ -1612,13 +1612,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="C17" t="n">
-        <v>41</v>
+        <v>93</v>
       </c>
       <c r="D17" t="n">
-        <v>51</v>
+        <v>17</v>
       </c>
     </row>
     <row r="18">
@@ -1626,13 +1626,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>34</v>
+        <v>77</v>
       </c>
       <c r="D18" t="n">
-        <v>39</v>
+        <v>2</v>
       </c>
     </row>
     <row r="19">
@@ -1643,10 +1643,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>27</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -1657,10 +1657,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1668,13 +1668,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>108</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1713,13 +1713,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7565</v>
+        <v>646</v>
       </c>
       <c r="C2" t="n">
-        <v>5044</v>
+        <v>10472</v>
       </c>
       <c r="D2" t="n">
-        <v>28802</v>
+        <v>16632</v>
       </c>
     </row>
     <row r="3">
@@ -1727,13 +1727,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4997</v>
+        <v>458</v>
       </c>
       <c r="C3" t="n">
-        <v>8732</v>
+        <v>2064</v>
       </c>
       <c r="D3" t="n">
-        <v>18217</v>
+        <v>11678</v>
       </c>
     </row>
     <row r="4">
@@ -1741,13 +1741,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2105</v>
+        <v>855</v>
       </c>
       <c r="C4" t="n">
-        <v>7523</v>
+        <v>4159</v>
       </c>
       <c r="D4" t="n">
-        <v>9675</v>
+        <v>8797</v>
       </c>
     </row>
     <row r="5">
@@ -1755,13 +1755,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1416</v>
+        <v>752</v>
       </c>
       <c r="C5" t="n">
-        <v>4371</v>
+        <v>5870</v>
       </c>
       <c r="D5" t="n">
-        <v>3044</v>
+        <v>3853</v>
       </c>
     </row>
     <row r="6">
@@ -1769,13 +1769,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>769</v>
+        <v>362</v>
       </c>
       <c r="C6" t="n">
-        <v>3122</v>
+        <v>5260</v>
       </c>
       <c r="D6" t="n">
-        <v>829</v>
+        <v>1272</v>
       </c>
     </row>
     <row r="7">
@@ -1783,13 +1783,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>345</v>
+        <v>124</v>
       </c>
       <c r="C7" t="n">
-        <v>1714</v>
+        <v>2399</v>
       </c>
       <c r="D7" t="n">
-        <v>471</v>
+        <v>622</v>
       </c>
     </row>
     <row r="8">
@@ -1797,13 +1797,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>133</v>
+        <v>56</v>
       </c>
       <c r="C8" t="n">
-        <v>749</v>
+        <v>740</v>
       </c>
       <c r="D8" t="n">
-        <v>327</v>
+        <v>452</v>
       </c>
     </row>
     <row r="9">
@@ -1811,13 +1811,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>51</v>
+        <v>32</v>
       </c>
       <c r="C9" t="n">
-        <v>331</v>
+        <v>338</v>
       </c>
       <c r="D9" t="n">
-        <v>245</v>
+        <v>377</v>
       </c>
     </row>
     <row r="10">
@@ -1825,13 +1825,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="C10" t="n">
-        <v>196</v>
+        <v>215</v>
       </c>
       <c r="D10" t="n">
-        <v>202</v>
+        <v>228</v>
       </c>
     </row>
     <row r="11">
@@ -1839,13 +1839,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="C11" t="n">
-        <v>147</v>
+        <v>153</v>
       </c>
       <c r="D11" t="n">
-        <v>160</v>
+        <v>177</v>
       </c>
     </row>
     <row r="12">
@@ -1853,13 +1853,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="C12" t="n">
-        <v>111</v>
+        <v>101</v>
       </c>
       <c r="D12" t="n">
-        <v>126</v>
+        <v>143</v>
       </c>
     </row>
     <row r="13">
@@ -1867,13 +1867,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C13" t="n">
-        <v>86</v>
+        <v>81</v>
       </c>
       <c r="D13" t="n">
-        <v>97</v>
+        <v>93</v>
       </c>
     </row>
     <row r="14">
@@ -1881,13 +1881,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C14" t="n">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="D14" t="n">
-        <v>80</v>
+        <v>69</v>
       </c>
     </row>
     <row r="15">
@@ -1898,10 +1898,10 @@
         <v>2</v>
       </c>
       <c r="C15" t="n">
-        <v>50</v>
+        <v>67</v>
       </c>
       <c r="D15" t="n">
-        <v>61</v>
+        <v>49</v>
       </c>
     </row>
     <row r="16">
@@ -1909,13 +1909,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="C16" t="n">
-        <v>40</v>
+        <v>90</v>
       </c>
       <c r="D16" t="n">
-        <v>49</v>
+        <v>30</v>
       </c>
     </row>
     <row r="17">
@@ -1926,10 +1926,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>33</v>
+        <v>103</v>
       </c>
       <c r="D17" t="n">
-        <v>38</v>
+        <v>11</v>
       </c>
     </row>
     <row r="18">
@@ -1940,10 +1940,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>30</v>
+        <v>3</v>
       </c>
       <c r="D18" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -1954,10 +1954,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -1965,13 +1965,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>108</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -2024,13 +2024,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4557</v>
+        <v>330</v>
       </c>
       <c r="C2" t="n">
-        <v>3294</v>
+        <v>4296</v>
       </c>
       <c r="D2" t="n">
-        <v>20916</v>
+        <v>12485</v>
       </c>
     </row>
     <row r="3">
@@ -2038,13 +2038,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>5230</v>
+        <v>462</v>
       </c>
       <c r="C3" t="n">
-        <v>6416</v>
+        <v>5430</v>
       </c>
       <c r="D3" t="n">
-        <v>18782</v>
+        <v>11812</v>
       </c>
     </row>
     <row r="4">
@@ -2052,13 +2052,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2810</v>
+        <v>661</v>
       </c>
       <c r="C4" t="n">
-        <v>8212</v>
+        <v>3186</v>
       </c>
       <c r="D4" t="n">
-        <v>10703</v>
+        <v>9056</v>
       </c>
     </row>
     <row r="5">
@@ -2066,13 +2066,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1568</v>
+        <v>774</v>
       </c>
       <c r="C5" t="n">
-        <v>5760</v>
+        <v>5234</v>
       </c>
       <c r="D5" t="n">
-        <v>3837</v>
+        <v>4474</v>
       </c>
     </row>
     <row r="6">
@@ -2080,13 +2080,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>918</v>
+        <v>449</v>
       </c>
       <c r="C6" t="n">
-        <v>3702</v>
+        <v>5702</v>
       </c>
       <c r="D6" t="n">
-        <v>1064</v>
+        <v>1553</v>
       </c>
     </row>
     <row r="7">
@@ -2094,13 +2094,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>322</v>
+        <v>142</v>
       </c>
       <c r="C7" t="n">
-        <v>2237</v>
+        <v>3483</v>
       </c>
       <c r="D7" t="n">
-        <v>515</v>
+        <v>695</v>
       </c>
     </row>
     <row r="8">
@@ -2108,13 +2108,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>110</v>
+        <v>53</v>
       </c>
       <c r="C8" t="n">
-        <v>1006</v>
+        <v>1162</v>
       </c>
       <c r="D8" t="n">
-        <v>336</v>
+        <v>482</v>
       </c>
     </row>
     <row r="9">
@@ -2122,13 +2122,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>42</v>
+        <v>27</v>
       </c>
       <c r="C9" t="n">
-        <v>376</v>
+        <v>444</v>
       </c>
       <c r="D9" t="n">
-        <v>254</v>
+        <v>379</v>
       </c>
     </row>
     <row r="10">
@@ -2136,13 +2136,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="C10" t="n">
-        <v>217</v>
+        <v>235</v>
       </c>
       <c r="D10" t="n">
-        <v>210</v>
+        <v>236</v>
       </c>
     </row>
     <row r="11">
@@ -2150,13 +2150,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="C11" t="n">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="D11" t="n">
-        <v>167</v>
+        <v>185</v>
       </c>
     </row>
     <row r="12">
@@ -2164,13 +2164,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C12" t="n">
-        <v>94</v>
+        <v>110</v>
       </c>
       <c r="D12" t="n">
-        <v>130</v>
+        <v>137</v>
       </c>
     </row>
     <row r="13">
@@ -2178,13 +2178,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C13" t="n">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="D13" t="n">
-        <v>99</v>
+        <v>93</v>
       </c>
     </row>
     <row r="14">
@@ -2195,10 +2195,10 @@
         <v>1</v>
       </c>
       <c r="C14" t="n">
-        <v>49</v>
+        <v>65</v>
       </c>
       <c r="D14" t="n">
-        <v>59</v>
+        <v>55</v>
       </c>
     </row>
     <row r="15">
@@ -2206,13 +2206,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="C15" t="n">
-        <v>39</v>
+        <v>88</v>
       </c>
       <c r="D15" t="n">
-        <v>48</v>
+        <v>29</v>
       </c>
     </row>
     <row r="16">
@@ -2223,10 +2223,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>32</v>
+        <v>100</v>
       </c>
       <c r="D16" t="n">
-        <v>37</v>
+        <v>10</v>
       </c>
     </row>
     <row r="17">
@@ -2237,10 +2237,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>29</v>
+        <v>2</v>
       </c>
       <c r="D17" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -2251,10 +2251,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -2262,13 +2262,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>105</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -2335,13 +2335,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5355</v>
+        <v>458</v>
       </c>
       <c r="C2" t="n">
-        <v>7484</v>
+        <v>6940</v>
       </c>
       <c r="D2" t="n">
-        <v>25911</v>
+        <v>15102</v>
       </c>
     </row>
     <row r="3">
@@ -2349,13 +2349,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4160</v>
+        <v>341</v>
       </c>
       <c r="C3" t="n">
-        <v>4423</v>
+        <v>4323</v>
       </c>
       <c r="D3" t="n">
-        <v>17810</v>
+        <v>11096</v>
       </c>
     </row>
     <row r="4">
@@ -2363,13 +2363,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3311</v>
+        <v>503</v>
       </c>
       <c r="C4" t="n">
-        <v>7179</v>
+        <v>4239</v>
       </c>
       <c r="D4" t="n">
-        <v>11696</v>
+        <v>9256</v>
       </c>
     </row>
     <row r="5">
@@ -2377,13 +2377,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1851</v>
+        <v>675</v>
       </c>
       <c r="C5" t="n">
-        <v>6770</v>
+        <v>4142</v>
       </c>
       <c r="D5" t="n">
-        <v>4774</v>
+        <v>5085</v>
       </c>
     </row>
     <row r="6">
@@ -2391,13 +2391,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1083</v>
+        <v>538</v>
       </c>
       <c r="C6" t="n">
-        <v>4611</v>
+        <v>5485</v>
       </c>
       <c r="D6" t="n">
-        <v>1449</v>
+        <v>1980</v>
       </c>
     </row>
     <row r="7">
@@ -2405,13 +2405,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>485</v>
+        <v>231</v>
       </c>
       <c r="C7" t="n">
-        <v>2853</v>
+        <v>4494</v>
       </c>
       <c r="D7" t="n">
-        <v>585</v>
+        <v>814</v>
       </c>
     </row>
     <row r="8">
@@ -2419,13 +2419,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>160</v>
+        <v>76</v>
       </c>
       <c r="C8" t="n">
-        <v>1510</v>
+        <v>2128</v>
       </c>
       <c r="D8" t="n">
-        <v>355</v>
+        <v>506</v>
       </c>
     </row>
     <row r="9">
@@ -2433,13 +2433,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>55</v>
+        <v>32</v>
       </c>
       <c r="C9" t="n">
-        <v>617</v>
+        <v>722</v>
       </c>
       <c r="D9" t="n">
-        <v>263</v>
+        <v>391</v>
       </c>
     </row>
     <row r="10">
@@ -2447,13 +2447,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="C10" t="n">
-        <v>272</v>
+        <v>310</v>
       </c>
       <c r="D10" t="n">
-        <v>212</v>
+        <v>249</v>
       </c>
     </row>
     <row r="11">
@@ -2461,13 +2461,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="C11" t="n">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="D11" t="n">
-        <v>170</v>
+        <v>189</v>
       </c>
     </row>
     <row r="12">
@@ -2475,13 +2475,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C12" t="n">
-        <v>113</v>
+        <v>127</v>
       </c>
       <c r="D12" t="n">
-        <v>132</v>
+        <v>140</v>
       </c>
     </row>
     <row r="13">
@@ -2492,10 +2492,10 @@
         <v>1</v>
       </c>
       <c r="C13" t="n">
-        <v>72</v>
+        <v>78</v>
       </c>
       <c r="D13" t="n">
-        <v>102</v>
+        <v>95</v>
       </c>
     </row>
     <row r="14">
@@ -2503,13 +2503,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="C14" t="n">
-        <v>53</v>
+        <v>67</v>
       </c>
       <c r="D14" t="n">
-        <v>61</v>
+        <v>57</v>
       </c>
     </row>
     <row r="15">
@@ -2517,13 +2517,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="C15" t="n">
-        <v>44</v>
+        <v>89</v>
       </c>
       <c r="D15" t="n">
-        <v>48</v>
+        <v>28</v>
       </c>
     </row>
     <row r="16">
@@ -2534,10 +2534,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>34</v>
+        <v>104</v>
       </c>
       <c r="D16" t="n">
-        <v>36</v>
+        <v>9</v>
       </c>
     </row>
     <row r="17">
@@ -2548,10 +2548,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>31</v>
+        <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>23</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -2559,13 +2559,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>64</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -2576,10 +2576,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>56</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -2646,13 +2646,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3207</v>
+        <v>304</v>
       </c>
       <c r="C2" t="n">
-        <v>3579</v>
+        <v>3497</v>
       </c>
       <c r="D2" t="n">
-        <v>18069</v>
+        <v>10873</v>
       </c>
     </row>
     <row r="3">
@@ -2660,13 +2660,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4283</v>
+        <v>485</v>
       </c>
       <c r="C3" t="n">
-        <v>5299</v>
+        <v>5415</v>
       </c>
       <c r="D3" t="n">
-        <v>18253</v>
+        <v>12109</v>
       </c>
     </row>
     <row r="4">
@@ -2674,13 +2674,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3640</v>
+        <v>863</v>
       </c>
       <c r="C4" t="n">
-        <v>6845</v>
+        <v>5852</v>
       </c>
       <c r="D4" t="n">
-        <v>12475</v>
+        <v>9710</v>
       </c>
     </row>
     <row r="5">
@@ -2688,13 +2688,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1921</v>
+        <v>553</v>
       </c>
       <c r="C5" t="n">
-        <v>7892</v>
+        <v>6906</v>
       </c>
       <c r="D5" t="n">
-        <v>5030</v>
+        <v>4739</v>
       </c>
     </row>
     <row r="6">
@@ -2702,13 +2702,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>878</v>
+        <v>213</v>
       </c>
       <c r="C6" t="n">
-        <v>5495</v>
+        <v>5855</v>
       </c>
       <c r="D6" t="n">
-        <v>1407</v>
+        <v>1687</v>
       </c>
     </row>
     <row r="7">
@@ -2716,13 +2716,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>147</v>
+        <v>70</v>
       </c>
       <c r="C7" t="n">
-        <v>2894</v>
+        <v>2085</v>
       </c>
       <c r="D7" t="n">
-        <v>583</v>
+        <v>615</v>
       </c>
     </row>
     <row r="8">
@@ -2730,13 +2730,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>50</v>
+        <v>29</v>
       </c>
       <c r="C8" t="n">
-        <v>1063</v>
+        <v>707</v>
       </c>
       <c r="D8" t="n">
-        <v>375</v>
+        <v>383</v>
       </c>
     </row>
     <row r="9">
@@ -2744,13 +2744,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="C9" t="n">
-        <v>266</v>
+        <v>303</v>
       </c>
       <c r="D9" t="n">
-        <v>285</v>
+        <v>244</v>
       </c>
     </row>
     <row r="10">
@@ -2758,13 +2758,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="C10" t="n">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="D10" t="n">
-        <v>166</v>
+        <v>185</v>
       </c>
     </row>
     <row r="11">
@@ -2772,13 +2772,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C11" t="n">
-        <v>110</v>
+        <v>124</v>
       </c>
       <c r="D11" t="n">
-        <v>129</v>
+        <v>137</v>
       </c>
     </row>
     <row r="12">
@@ -2789,10 +2789,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>70</v>
+        <v>76</v>
       </c>
       <c r="D12" t="n">
-        <v>99</v>
+        <v>93</v>
       </c>
     </row>
     <row r="13">
@@ -2800,13 +2800,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C13" t="n">
-        <v>51</v>
+        <v>65</v>
       </c>
       <c r="D13" t="n">
-        <v>59</v>
+        <v>55</v>
       </c>
     </row>
     <row r="14">
@@ -2814,13 +2814,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="C14" t="n">
-        <v>43</v>
+        <v>87</v>
       </c>
       <c r="D14" t="n">
-        <v>47</v>
+        <v>27</v>
       </c>
     </row>
     <row r="15">
@@ -2831,10 +2831,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>33</v>
+        <v>101</v>
       </c>
       <c r="D15" t="n">
-        <v>35</v>
+        <v>8</v>
       </c>
     </row>
     <row r="16">
@@ -2845,10 +2845,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -2856,13 +2856,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>62</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -2873,10 +2873,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>54</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -2957,13 +2957,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4155</v>
+        <v>182</v>
       </c>
       <c r="C2" t="n">
-        <v>10536</v>
+        <v>2060</v>
       </c>
       <c r="D2" t="n">
-        <v>20306</v>
+        <v>7386</v>
       </c>
     </row>
     <row r="3">
@@ -2971,13 +2971,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3252</v>
+        <v>343</v>
       </c>
       <c r="C3" t="n">
-        <v>4048</v>
+        <v>3918</v>
       </c>
       <c r="D3" t="n">
-        <v>17176</v>
+        <v>11149</v>
       </c>
     </row>
     <row r="4">
@@ -2985,13 +2985,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3438</v>
+        <v>574</v>
       </c>
       <c r="C4" t="n">
-        <v>5990</v>
+        <v>5290</v>
       </c>
       <c r="D4" t="n">
-        <v>12983</v>
+        <v>9423</v>
       </c>
     </row>
     <row r="5">
@@ -2999,13 +2999,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2310</v>
+        <v>498</v>
       </c>
       <c r="C5" t="n">
-        <v>7341</v>
+        <v>5675</v>
       </c>
       <c r="D5" t="n">
-        <v>5949</v>
+        <v>4870</v>
       </c>
     </row>
     <row r="6">
@@ -3013,13 +3013,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1150</v>
+        <v>208</v>
       </c>
       <c r="C6" t="n">
-        <v>6488</v>
+        <v>5269</v>
       </c>
       <c r="D6" t="n">
-        <v>1875</v>
+        <v>1807</v>
       </c>
     </row>
     <row r="7">
@@ -3027,13 +3027,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>318</v>
+        <v>58</v>
       </c>
       <c r="C7" t="n">
-        <v>3969</v>
+        <v>2701</v>
       </c>
       <c r="D7" t="n">
-        <v>687</v>
+        <v>608</v>
       </c>
     </row>
     <row r="8">
@@ -3041,13 +3041,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>68</v>
+        <v>15</v>
       </c>
       <c r="C8" t="n">
-        <v>1729</v>
+        <v>818</v>
       </c>
       <c r="D8" t="n">
-        <v>397</v>
+        <v>332</v>
       </c>
     </row>
     <row r="9">
@@ -3055,13 +3055,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>21</v>
+        <v>4</v>
       </c>
       <c r="C9" t="n">
-        <v>523</v>
+        <v>285</v>
       </c>
       <c r="D9" t="n">
-        <v>292</v>
+        <v>195</v>
       </c>
     </row>
     <row r="10">
@@ -3069,13 +3069,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>207</v>
+        <v>135</v>
       </c>
       <c r="D10" t="n">
-        <v>175</v>
+        <v>143</v>
       </c>
     </row>
     <row r="11">
@@ -3083,13 +3083,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>130</v>
+        <v>79</v>
       </c>
       <c r="D11" t="n">
-        <v>133</v>
+        <v>100</v>
       </c>
     </row>
     <row r="12">
@@ -3100,10 +3100,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>80</v>
+        <v>54</v>
       </c>
       <c r="D12" t="n">
-        <v>100</v>
+        <v>62</v>
       </c>
     </row>
     <row r="13">
@@ -3111,13 +3111,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C13" t="n">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="D13" t="n">
-        <v>59</v>
+        <v>32</v>
       </c>
     </row>
     <row r="14">
@@ -3128,10 +3128,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>45</v>
+        <v>56</v>
       </c>
       <c r="D14" t="n">
-        <v>46</v>
+        <v>9</v>
       </c>
     </row>
     <row r="15">
@@ -3142,10 +3142,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="D15" t="n">
-        <v>33</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -3153,13 +3153,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>57</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -3170,10 +3170,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>70</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -3184,10 +3184,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -3268,13 +3268,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2945</v>
+        <v>395</v>
       </c>
       <c r="C2" t="n">
-        <v>6062</v>
+        <v>3771</v>
       </c>
       <c r="D2" t="n">
-        <v>14370</v>
+        <v>11090</v>
       </c>
     </row>
     <row r="3">
@@ -3282,13 +3282,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3097</v>
+        <v>221</v>
       </c>
       <c r="C3" t="n">
-        <v>6001</v>
+        <v>2493</v>
       </c>
       <c r="D3" t="n">
-        <v>16782</v>
+        <v>9744</v>
       </c>
     </row>
     <row r="4">
@@ -3296,13 +3296,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3088</v>
+        <v>407</v>
       </c>
       <c r="C4" t="n">
-        <v>5216</v>
+        <v>4440</v>
       </c>
       <c r="D4" t="n">
-        <v>13236</v>
+        <v>9467</v>
       </c>
     </row>
     <row r="5">
@@ -3310,13 +3310,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2522</v>
+        <v>487</v>
       </c>
       <c r="C5" t="n">
-        <v>6990</v>
+        <v>5346</v>
       </c>
       <c r="D5" t="n">
-        <v>6568</v>
+        <v>5552</v>
       </c>
     </row>
     <row r="6">
@@ -3324,13 +3324,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1345</v>
+        <v>313</v>
       </c>
       <c r="C6" t="n">
-        <v>7016</v>
+        <v>5474</v>
       </c>
       <c r="D6" t="n">
-        <v>2259</v>
+        <v>2311</v>
       </c>
     </row>
     <row r="7">
@@ -3338,13 +3338,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>284</v>
+        <v>110</v>
       </c>
       <c r="C7" t="n">
-        <v>4832</v>
+        <v>4035</v>
       </c>
       <c r="D7" t="n">
-        <v>770</v>
+        <v>801</v>
       </c>
     </row>
     <row r="8">
@@ -3352,13 +3352,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>55</v>
+        <v>29</v>
       </c>
       <c r="C8" t="n">
-        <v>2235</v>
+        <v>1729</v>
       </c>
       <c r="D8" t="n">
-        <v>412</v>
+        <v>371</v>
       </c>
     </row>
     <row r="9">
@@ -3366,13 +3366,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="C9" t="n">
-        <v>601</v>
+        <v>527</v>
       </c>
       <c r="D9" t="n">
-        <v>288</v>
+        <v>213</v>
       </c>
     </row>
     <row r="10">
@@ -3380,13 +3380,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C10" t="n">
-        <v>213</v>
+        <v>199</v>
       </c>
       <c r="D10" t="n">
-        <v>178</v>
+        <v>150</v>
       </c>
     </row>
     <row r="11">
@@ -3397,10 +3397,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>128</v>
+        <v>102</v>
       </c>
       <c r="D11" t="n">
-        <v>135</v>
+        <v>104</v>
       </c>
     </row>
     <row r="12">
@@ -3411,10 +3411,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>78</v>
+        <v>63</v>
       </c>
       <c r="D12" t="n">
-        <v>91</v>
+        <v>66</v>
       </c>
     </row>
     <row r="13">
@@ -3422,13 +3422,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C13" t="n">
-        <v>44</v>
+        <v>55</v>
       </c>
       <c r="D13" t="n">
-        <v>61</v>
+        <v>34</v>
       </c>
     </row>
     <row r="14">
@@ -3439,10 +3439,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>35</v>
+        <v>57</v>
       </c>
       <c r="D14" t="n">
-        <v>36</v>
+        <v>10</v>
       </c>
     </row>
     <row r="15">
@@ -3450,13 +3450,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>55</v>
+        <v>11</v>
       </c>
       <c r="D15" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -3467,10 +3467,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>68</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -3484,7 +3484,7 @@
         <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -3579,13 +3579,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3877</v>
+        <v>108</v>
       </c>
       <c r="C2" t="n">
-        <v>6677</v>
+        <v>9214</v>
       </c>
       <c r="D2" t="n">
-        <v>18346</v>
+        <v>18631</v>
       </c>
     </row>
     <row r="3">
@@ -3593,13 +3593,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2563</v>
+        <v>248</v>
       </c>
       <c r="C3" t="n">
-        <v>5417</v>
+        <v>2736</v>
       </c>
       <c r="D3" t="n">
-        <v>15418</v>
+        <v>9262</v>
       </c>
     </row>
     <row r="4">
@@ -3607,13 +3607,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2686</v>
+        <v>278</v>
       </c>
       <c r="C4" t="n">
-        <v>5431</v>
+        <v>3319</v>
       </c>
       <c r="D4" t="n">
-        <v>13344</v>
+        <v>9229</v>
       </c>
     </row>
     <row r="5">
@@ -3621,13 +3621,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2499</v>
+        <v>413</v>
       </c>
       <c r="C5" t="n">
-        <v>6146</v>
+        <v>4773</v>
       </c>
       <c r="D5" t="n">
-        <v>7264</v>
+        <v>6059</v>
       </c>
     </row>
     <row r="6">
@@ -3635,13 +3635,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1593</v>
+        <v>362</v>
       </c>
       <c r="C6" t="n">
-        <v>6948</v>
+        <v>5353</v>
       </c>
       <c r="D6" t="n">
-        <v>2767</v>
+        <v>2785</v>
       </c>
     </row>
     <row r="7">
@@ -3649,13 +3649,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>547</v>
+        <v>178</v>
       </c>
       <c r="C7" t="n">
-        <v>5621</v>
+        <v>4724</v>
       </c>
       <c r="D7" t="n">
-        <v>937</v>
+        <v>1044</v>
       </c>
     </row>
     <row r="8">
@@ -3663,13 +3663,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>103</v>
+        <v>55</v>
       </c>
       <c r="C8" t="n">
-        <v>3146</v>
+        <v>2790</v>
       </c>
       <c r="D8" t="n">
-        <v>446</v>
+        <v>434</v>
       </c>
     </row>
     <row r="9">
@@ -3677,13 +3677,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="C9" t="n">
-        <v>1113</v>
+        <v>1056</v>
       </c>
       <c r="D9" t="n">
-        <v>297</v>
+        <v>234</v>
       </c>
     </row>
     <row r="10">
@@ -3691,13 +3691,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C10" t="n">
-        <v>329</v>
+        <v>337</v>
       </c>
       <c r="D10" t="n">
-        <v>185</v>
+        <v>155</v>
       </c>
     </row>
     <row r="11">
@@ -3708,10 +3708,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>152</v>
+        <v>140</v>
       </c>
       <c r="D11" t="n">
-        <v>138</v>
+        <v>109</v>
       </c>
     </row>
     <row r="12">
@@ -3722,10 +3722,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>90</v>
+        <v>77</v>
       </c>
       <c r="D12" t="n">
-        <v>93</v>
+        <v>70</v>
       </c>
     </row>
     <row r="13">
@@ -3736,10 +3736,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>51</v>
+        <v>57</v>
       </c>
       <c r="D13" t="n">
-        <v>62</v>
+        <v>37</v>
       </c>
     </row>
     <row r="14">
@@ -3750,10 +3750,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>37</v>
+        <v>56</v>
       </c>
       <c r="D14" t="n">
-        <v>36</v>
+        <v>12</v>
       </c>
     </row>
     <row r="15">
@@ -3761,13 +3761,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>58</v>
+        <v>25</v>
       </c>
       <c r="D15" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -3778,10 +3778,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>65</v>
+        <v>3</v>
       </c>
       <c r="D16" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -3890,13 +3890,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6352</v>
+        <v>2517</v>
       </c>
       <c r="C2" t="n">
-        <v>4263</v>
+        <v>6002</v>
       </c>
       <c r="D2" t="n">
-        <v>9623</v>
+        <v>9342</v>
       </c>
     </row>
     <row r="3">
@@ -3904,13 +3904,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C3" t="n">
         <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>843</v>
+        <v>855</v>
       </c>
     </row>
     <row r="4">
@@ -3918,13 +3918,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>175</v>
+        <v>205</v>
       </c>
       <c r="C4" t="n">
-        <v>313</v>
+        <v>344</v>
       </c>
       <c r="D4" t="n">
-        <v>1805</v>
+        <v>1906</v>
       </c>
     </row>
     <row r="5">
@@ -3932,13 +3932,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>249</v>
+        <v>314</v>
       </c>
       <c r="C5" t="n">
-        <v>515</v>
+        <v>586</v>
       </c>
       <c r="D5" t="n">
-        <v>1038</v>
+        <v>1139</v>
       </c>
     </row>
     <row r="6">
@@ -3946,13 +3946,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>182</v>
+        <v>255</v>
       </c>
       <c r="C6" t="n">
-        <v>395</v>
+        <v>488</v>
       </c>
       <c r="D6" t="n">
-        <v>777</v>
+        <v>898</v>
       </c>
     </row>
     <row r="7">
@@ -3960,13 +3960,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>129</v>
+        <v>202</v>
       </c>
       <c r="C7" t="n">
-        <v>293</v>
+        <v>388</v>
       </c>
       <c r="D7" t="n">
-        <v>496</v>
+        <v>596</v>
       </c>
     </row>
     <row r="8">
@@ -3974,13 +3974,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>99</v>
+        <v>171</v>
       </c>
       <c r="C8" t="n">
-        <v>222</v>
+        <v>307</v>
       </c>
       <c r="D8" t="n">
-        <v>420</v>
+        <v>531</v>
       </c>
     </row>
     <row r="9">
@@ -3988,13 +3988,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>75</v>
+        <v>136</v>
       </c>
       <c r="C9" t="n">
-        <v>187</v>
+        <v>277</v>
       </c>
       <c r="D9" t="n">
-        <v>349</v>
+        <v>445</v>
       </c>
     </row>
     <row r="10">
@@ -4002,13 +4002,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>53</v>
+        <v>105</v>
       </c>
       <c r="C10" t="n">
-        <v>173</v>
+        <v>265</v>
       </c>
       <c r="D10" t="n">
-        <v>362</v>
+        <v>485</v>
       </c>
     </row>
     <row r="11">
@@ -4016,13 +4016,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>34</v>
+        <v>71</v>
       </c>
       <c r="C11" t="n">
-        <v>137</v>
+        <v>215</v>
       </c>
       <c r="D11" t="n">
-        <v>245</v>
+        <v>327</v>
       </c>
     </row>
     <row r="12">
@@ -4030,13 +4030,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>24</v>
+        <v>52</v>
       </c>
       <c r="C12" t="n">
-        <v>104</v>
+        <v>169</v>
       </c>
       <c r="D12" t="n">
-        <v>196</v>
+        <v>274</v>
       </c>
     </row>
     <row r="13">
@@ -4044,13 +4044,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>18</v>
+        <v>42</v>
       </c>
       <c r="C13" t="n">
-        <v>84</v>
+        <v>142</v>
       </c>
       <c r="D13" t="n">
-        <v>168</v>
+        <v>234</v>
       </c>
     </row>
     <row r="14">
@@ -4058,13 +4058,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>16</v>
+        <v>38</v>
       </c>
       <c r="C14" t="n">
-        <v>75</v>
+        <v>128</v>
       </c>
       <c r="D14" t="n">
-        <v>145</v>
+        <v>207</v>
       </c>
     </row>
     <row r="15">
@@ -4072,13 +4072,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>16</v>
+        <v>38</v>
       </c>
       <c r="C15" t="n">
-        <v>72</v>
+        <v>127</v>
       </c>
       <c r="D15" t="n">
-        <v>117</v>
+        <v>171</v>
       </c>
     </row>
     <row r="16">
@@ -4086,13 +4086,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>15</v>
+        <v>36</v>
       </c>
       <c r="C16" t="n">
-        <v>70</v>
+        <v>124</v>
       </c>
       <c r="D16" t="n">
-        <v>97</v>
+        <v>140</v>
       </c>
     </row>
     <row r="17">
@@ -4100,13 +4100,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>14</v>
+        <v>36</v>
       </c>
       <c r="C17" t="n">
-        <v>66</v>
+        <v>119</v>
       </c>
       <c r="D17" t="n">
-        <v>76</v>
+        <v>114</v>
       </c>
     </row>
     <row r="18">
@@ -4114,13 +4114,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>13</v>
+        <v>34</v>
       </c>
       <c r="C18" t="n">
-        <v>63</v>
+        <v>116</v>
       </c>
       <c r="D18" t="n">
-        <v>57</v>
+        <v>85</v>
       </c>
     </row>
     <row r="19">
@@ -4128,13 +4128,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>13</v>
+        <v>34</v>
       </c>
       <c r="C19" t="n">
-        <v>60</v>
+        <v>111</v>
       </c>
       <c r="D19" t="n">
-        <v>38</v>
+        <v>58</v>
       </c>
     </row>
     <row r="20">
@@ -4142,13 +4142,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>11</v>
+        <v>31</v>
       </c>
       <c r="C20" t="n">
-        <v>58</v>
+        <v>109</v>
       </c>
       <c r="D20" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
     </row>
     <row r="21">
@@ -4156,10 +4156,10 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>15</v>
+        <v>36</v>
       </c>
       <c r="C21" t="n">
-        <v>72</v>
+        <v>131</v>
       </c>
       <c r="D21" t="n">
         <v>1</v>
@@ -4201,13 +4201,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2804</v>
+        <v>502</v>
       </c>
       <c r="C2" t="n">
-        <v>3845</v>
+        <v>13433</v>
       </c>
       <c r="D2" t="n">
-        <v>13649</v>
+        <v>19208</v>
       </c>
     </row>
     <row r="3">
@@ -4215,13 +4215,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3363</v>
+        <v>160</v>
       </c>
       <c r="C3" t="n">
-        <v>6175</v>
+        <v>4998</v>
       </c>
       <c r="D3" t="n">
-        <v>16725</v>
+        <v>9913</v>
       </c>
     </row>
     <row r="4">
@@ -4229,13 +4229,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3681</v>
+        <v>228</v>
       </c>
       <c r="C4" t="n">
-        <v>7680</v>
+        <v>2970</v>
       </c>
       <c r="D4" t="n">
-        <v>13656</v>
+        <v>8953</v>
       </c>
     </row>
     <row r="5">
@@ -4243,13 +4243,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1518</v>
+        <v>331</v>
       </c>
       <c r="C5" t="n">
-        <v>9468</v>
+        <v>3957</v>
       </c>
       <c r="D5" t="n">
-        <v>6585</v>
+        <v>6303</v>
       </c>
     </row>
     <row r="6">
@@ -4257,13 +4257,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>505</v>
+        <v>355</v>
       </c>
       <c r="C6" t="n">
-        <v>6802</v>
+        <v>5038</v>
       </c>
       <c r="D6" t="n">
-        <v>2154</v>
+        <v>3250</v>
       </c>
     </row>
     <row r="7">
@@ -4271,13 +4271,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>95</v>
+        <v>230</v>
       </c>
       <c r="C7" t="n">
-        <v>3083</v>
+        <v>4999</v>
       </c>
       <c r="D7" t="n">
-        <v>556</v>
+        <v>1279</v>
       </c>
     </row>
     <row r="8">
@@ -4285,13 +4285,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>20</v>
+        <v>91</v>
       </c>
       <c r="C8" t="n">
-        <v>1090</v>
+        <v>3603</v>
       </c>
       <c r="D8" t="n">
-        <v>291</v>
+        <v>519</v>
       </c>
     </row>
     <row r="9">
@@ -4299,13 +4299,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>3</v>
+        <v>25</v>
       </c>
       <c r="C9" t="n">
-        <v>322</v>
+        <v>1741</v>
       </c>
       <c r="D9" t="n">
-        <v>181</v>
+        <v>259</v>
       </c>
     </row>
     <row r="10">
@@ -4313,13 +4313,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="C10" t="n">
-        <v>148</v>
+        <v>618</v>
       </c>
       <c r="D10" t="n">
-        <v>135</v>
+        <v>161</v>
       </c>
     </row>
     <row r="11">
@@ -4330,10 +4330,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>88</v>
+        <v>213</v>
       </c>
       <c r="D11" t="n">
-        <v>91</v>
+        <v>113</v>
       </c>
     </row>
     <row r="12">
@@ -4344,10 +4344,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>49</v>
+        <v>98</v>
       </c>
       <c r="D12" t="n">
-        <v>60</v>
+        <v>73</v>
       </c>
     </row>
     <row r="13">
@@ -4358,10 +4358,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>36</v>
+        <v>63</v>
       </c>
       <c r="D13" t="n">
-        <v>35</v>
+        <v>40</v>
       </c>
     </row>
     <row r="14">
@@ -4369,13 +4369,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C14" t="n">
         <v>56</v>
       </c>
       <c r="D14" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
     </row>
     <row r="15">
@@ -4386,10 +4386,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>63</v>
+        <v>34</v>
       </c>
       <c r="D15" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="16">
@@ -4400,7 +4400,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="D16" t="n">
         <v>0</v>
@@ -4512,13 +4512,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6686</v>
+        <v>2856</v>
       </c>
       <c r="C2" t="n">
-        <v>9194</v>
+        <v>8312</v>
       </c>
       <c r="D2" t="n">
-        <v>27275</v>
+        <v>18937</v>
       </c>
     </row>
     <row r="3">
@@ -4526,13 +4526,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2698</v>
+        <v>834</v>
       </c>
       <c r="C3" t="n">
-        <v>2148</v>
+        <v>2370</v>
       </c>
       <c r="D3" t="n">
-        <v>2255</v>
+        <v>1894</v>
       </c>
     </row>
     <row r="4">
@@ -4540,13 +4540,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>79</v>
+        <v>72</v>
       </c>
       <c r="C4" t="n">
-        <v>114</v>
+        <v>134</v>
       </c>
       <c r="D4" t="n">
-        <v>1538</v>
+        <v>1446</v>
       </c>
     </row>
     <row r="5">
@@ -4554,13 +4554,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>191</v>
+        <v>148</v>
       </c>
       <c r="C5" t="n">
-        <v>384</v>
+        <v>334</v>
       </c>
       <c r="D5" t="n">
-        <v>1161</v>
+        <v>986</v>
       </c>
     </row>
     <row r="6">
@@ -4568,13 +4568,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>202</v>
+        <v>143</v>
       </c>
       <c r="C6" t="n">
-        <v>459</v>
+        <v>360</v>
       </c>
       <c r="D6" t="n">
-        <v>808</v>
+        <v>712</v>
       </c>
     </row>
     <row r="7">
@@ -4582,13 +4582,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>145</v>
+        <v>102</v>
       </c>
       <c r="C7" t="n">
-        <v>350</v>
+        <v>277</v>
       </c>
       <c r="D7" t="n">
-        <v>546</v>
+        <v>466</v>
       </c>
     </row>
     <row r="8">
@@ -4596,13 +4596,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>105</v>
+        <v>78</v>
       </c>
       <c r="C8" t="n">
-        <v>260</v>
+        <v>206</v>
       </c>
       <c r="D8" t="n">
-        <v>429</v>
+        <v>384</v>
       </c>
     </row>
     <row r="9">
@@ -4610,13 +4610,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>80</v>
+        <v>60</v>
       </c>
       <c r="C9" t="n">
-        <v>205</v>
+        <v>169</v>
       </c>
       <c r="D9" t="n">
-        <v>354</v>
+        <v>313</v>
       </c>
     </row>
     <row r="10">
@@ -4624,13 +4624,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>58</v>
+        <v>44</v>
       </c>
       <c r="C10" t="n">
-        <v>180</v>
+        <v>151</v>
       </c>
       <c r="D10" t="n">
-        <v>356</v>
+        <v>324</v>
       </c>
     </row>
     <row r="11">
@@ -4638,13 +4638,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="C11" t="n">
-        <v>154</v>
+        <v>129</v>
       </c>
       <c r="D11" t="n">
-        <v>261</v>
+        <v>231</v>
       </c>
     </row>
     <row r="12">
@@ -4652,13 +4652,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="C12" t="n">
-        <v>119</v>
+        <v>100</v>
       </c>
       <c r="D12" t="n">
-        <v>199</v>
+        <v>182</v>
       </c>
     </row>
     <row r="13">
@@ -4666,13 +4666,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="C13" t="n">
-        <v>92</v>
+        <v>79</v>
       </c>
       <c r="D13" t="n">
-        <v>170</v>
+        <v>154</v>
       </c>
     </row>
     <row r="14">
@@ -4680,13 +4680,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>78</v>
+        <v>69</v>
       </c>
       <c r="D14" t="n">
-        <v>146</v>
+        <v>133</v>
       </c>
     </row>
     <row r="15">
@@ -4694,13 +4694,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C15" t="n">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="D15" t="n">
-        <v>118</v>
+        <v>111</v>
       </c>
     </row>
     <row r="16">
@@ -4708,13 +4708,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C16" t="n">
-        <v>70</v>
+        <v>63</v>
       </c>
       <c r="D16" t="n">
-        <v>98</v>
+        <v>89</v>
       </c>
     </row>
     <row r="17">
@@ -4722,13 +4722,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C17" t="n">
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="D17" t="n">
-        <v>77</v>
+        <v>73</v>
       </c>
     </row>
     <row r="18">
@@ -4736,13 +4736,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C18" t="n">
-        <v>64</v>
+        <v>58</v>
       </c>
       <c r="D18" t="n">
-        <v>58</v>
+        <v>54</v>
       </c>
     </row>
     <row r="19">
@@ -4750,13 +4750,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C19" t="n">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="D19" t="n">
-        <v>39</v>
+        <v>36</v>
       </c>
     </row>
     <row r="20">
@@ -4767,10 +4767,10 @@
         <v>10</v>
       </c>
       <c r="C20" t="n">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="D20" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
     </row>
     <row r="21">
@@ -4778,13 +4778,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C21" t="n">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="D21" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -4823,13 +4823,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5719</v>
+        <v>1705</v>
       </c>
       <c r="C2" t="n">
-        <v>5728</v>
+        <v>6151</v>
       </c>
       <c r="D2" t="n">
-        <v>26292</v>
+        <v>18503</v>
       </c>
     </row>
     <row r="3">
@@ -4837,13 +4837,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3854</v>
+        <v>1560</v>
       </c>
       <c r="C3" t="n">
-        <v>5290</v>
+        <v>5118</v>
       </c>
       <c r="D3" t="n">
-        <v>6292</v>
+        <v>4751</v>
       </c>
     </row>
     <row r="4">
@@ -4851,13 +4851,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1206</v>
+        <v>413</v>
       </c>
       <c r="C4" t="n">
-        <v>1302</v>
+        <v>1526</v>
       </c>
       <c r="D4" t="n">
-        <v>1635</v>
+        <v>1496</v>
       </c>
     </row>
     <row r="5">
@@ -4865,13 +4865,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>124</v>
+        <v>98</v>
       </c>
       <c r="C5" t="n">
-        <v>219</v>
+        <v>206</v>
       </c>
       <c r="D5" t="n">
-        <v>1198</v>
+        <v>1039</v>
       </c>
     </row>
     <row r="6">
@@ -4879,13 +4879,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>185</v>
+        <v>137</v>
       </c>
       <c r="C6" t="n">
-        <v>411</v>
+        <v>340</v>
       </c>
       <c r="D6" t="n">
-        <v>853</v>
+        <v>756</v>
       </c>
     </row>
     <row r="7">
@@ -4893,13 +4893,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>159</v>
+        <v>114</v>
       </c>
       <c r="C7" t="n">
-        <v>409</v>
+        <v>324</v>
       </c>
       <c r="D7" t="n">
-        <v>589</v>
+        <v>509</v>
       </c>
     </row>
     <row r="8">
@@ -4907,13 +4907,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>115</v>
+        <v>83</v>
       </c>
       <c r="C8" t="n">
-        <v>307</v>
+        <v>245</v>
       </c>
       <c r="D8" t="n">
-        <v>441</v>
+        <v>395</v>
       </c>
     </row>
     <row r="9">
@@ -4921,13 +4921,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>85</v>
+        <v>64</v>
       </c>
       <c r="C9" t="n">
-        <v>232</v>
+        <v>188</v>
       </c>
       <c r="D9" t="n">
-        <v>363</v>
+        <v>319</v>
       </c>
     </row>
     <row r="10">
@@ -4935,13 +4935,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>62</v>
+        <v>47</v>
       </c>
       <c r="C10" t="n">
-        <v>192</v>
+        <v>161</v>
       </c>
       <c r="D10" t="n">
-        <v>352</v>
+        <v>318</v>
       </c>
     </row>
     <row r="11">
@@ -4949,13 +4949,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>43</v>
+        <v>33</v>
       </c>
       <c r="C11" t="n">
-        <v>164</v>
+        <v>139</v>
       </c>
       <c r="D11" t="n">
-        <v>270</v>
+        <v>244</v>
       </c>
     </row>
     <row r="12">
@@ -4963,13 +4963,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="C12" t="n">
-        <v>135</v>
+        <v>113</v>
       </c>
       <c r="D12" t="n">
-        <v>206</v>
+        <v>186</v>
       </c>
     </row>
     <row r="13">
@@ -4977,13 +4977,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="C13" t="n">
-        <v>103</v>
+        <v>88</v>
       </c>
       <c r="D13" t="n">
-        <v>172</v>
+        <v>156</v>
       </c>
     </row>
     <row r="14">
@@ -4991,13 +4991,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C14" t="n">
-        <v>83</v>
+        <v>73</v>
       </c>
       <c r="D14" t="n">
-        <v>146</v>
+        <v>134</v>
       </c>
     </row>
     <row r="15">
@@ -5005,13 +5005,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C15" t="n">
-        <v>74</v>
+        <v>66</v>
       </c>
       <c r="D15" t="n">
-        <v>120</v>
+        <v>112</v>
       </c>
     </row>
     <row r="16">
@@ -5019,13 +5019,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C16" t="n">
-        <v>71</v>
+        <v>63</v>
       </c>
       <c r="D16" t="n">
-        <v>98</v>
+        <v>90</v>
       </c>
     </row>
     <row r="17">
@@ -5033,13 +5033,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C17" t="n">
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="D17" t="n">
-        <v>78</v>
+        <v>74</v>
       </c>
     </row>
     <row r="18">
@@ -5047,13 +5047,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C18" t="n">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="D18" t="n">
-        <v>59</v>
+        <v>55</v>
       </c>
     </row>
     <row r="19">
@@ -5061,13 +5061,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C19" t="n">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="D19" t="n">
-        <v>40</v>
+        <v>37</v>
       </c>
     </row>
     <row r="20">
@@ -5078,10 +5078,10 @@
         <v>9</v>
       </c>
       <c r="C20" t="n">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="D20" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
     </row>
     <row r="21">
@@ -5089,13 +5089,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="C21" t="n">
-        <v>106</v>
+        <v>92</v>
       </c>
       <c r="D21" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
   </sheetData>
@@ -5134,13 +5134,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6337</v>
+        <v>1378</v>
       </c>
       <c r="C2" t="n">
-        <v>11192</v>
+        <v>4866</v>
       </c>
       <c r="D2" t="n">
-        <v>32324</v>
+        <v>22994</v>
       </c>
     </row>
     <row r="3">
@@ -5148,13 +5148,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3916</v>
+        <v>1347</v>
       </c>
       <c r="C3" t="n">
-        <v>4785</v>
+        <v>4918</v>
       </c>
       <c r="D3" t="n">
-        <v>9038</v>
+        <v>6711</v>
       </c>
     </row>
     <row r="4">
@@ -5162,13 +5162,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2153</v>
+        <v>863</v>
       </c>
       <c r="C4" t="n">
-        <v>3533</v>
+        <v>3666</v>
       </c>
       <c r="D4" t="n">
-        <v>2479</v>
+        <v>2092</v>
       </c>
     </row>
     <row r="5">
@@ -5176,13 +5176,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>544</v>
+        <v>225</v>
       </c>
       <c r="C5" t="n">
-        <v>807</v>
+        <v>974</v>
       </c>
       <c r="D5" t="n">
-        <v>1229</v>
+        <v>1099</v>
       </c>
     </row>
     <row r="6">
@@ -5190,13 +5190,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>148</v>
+        <v>111</v>
       </c>
       <c r="C6" t="n">
-        <v>304</v>
+        <v>259</v>
       </c>
       <c r="D6" t="n">
-        <v>903</v>
+        <v>799</v>
       </c>
     </row>
     <row r="7">
@@ -5204,13 +5204,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>158</v>
+        <v>117</v>
       </c>
       <c r="C7" t="n">
-        <v>405</v>
+        <v>332</v>
       </c>
       <c r="D7" t="n">
-        <v>629</v>
+        <v>544</v>
       </c>
     </row>
     <row r="8">
@@ -5218,13 +5218,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>125</v>
+        <v>90</v>
       </c>
       <c r="C8" t="n">
-        <v>358</v>
+        <v>287</v>
       </c>
       <c r="D8" t="n">
-        <v>456</v>
+        <v>412</v>
       </c>
     </row>
     <row r="9">
@@ -5232,13 +5232,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>90</v>
+        <v>68</v>
       </c>
       <c r="C9" t="n">
-        <v>268</v>
+        <v>217</v>
       </c>
       <c r="D9" t="n">
-        <v>372</v>
+        <v>329</v>
       </c>
     </row>
     <row r="10">
@@ -5246,13 +5246,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>66</v>
+        <v>50</v>
       </c>
       <c r="C10" t="n">
-        <v>210</v>
+        <v>174</v>
       </c>
       <c r="D10" t="n">
-        <v>346</v>
+        <v>314</v>
       </c>
     </row>
     <row r="11">
@@ -5260,13 +5260,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>46</v>
+        <v>36</v>
       </c>
       <c r="C11" t="n">
-        <v>174</v>
+        <v>149</v>
       </c>
       <c r="D11" t="n">
-        <v>280</v>
+        <v>250</v>
       </c>
     </row>
     <row r="12">
@@ -5274,13 +5274,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="C12" t="n">
-        <v>147</v>
+        <v>124</v>
       </c>
       <c r="D12" t="n">
-        <v>213</v>
+        <v>193</v>
       </c>
     </row>
     <row r="13">
@@ -5288,13 +5288,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="C13" t="n">
-        <v>116</v>
+        <v>98</v>
       </c>
       <c r="D13" t="n">
-        <v>173</v>
+        <v>158</v>
       </c>
     </row>
     <row r="14">
@@ -5302,13 +5302,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C14" t="n">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="D14" t="n">
-        <v>148</v>
+        <v>134</v>
       </c>
     </row>
     <row r="15">
@@ -5316,13 +5316,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C15" t="n">
-        <v>76</v>
+        <v>68</v>
       </c>
       <c r="D15" t="n">
-        <v>120</v>
+        <v>113</v>
       </c>
     </row>
     <row r="16">
@@ -5330,13 +5330,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C16" t="n">
-        <v>72</v>
+        <v>64</v>
       </c>
       <c r="D16" t="n">
-        <v>99</v>
+        <v>91</v>
       </c>
     </row>
     <row r="17">
@@ -5344,13 +5344,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C17" t="n">
-        <v>68</v>
+        <v>61</v>
       </c>
       <c r="D17" t="n">
-        <v>79</v>
+        <v>75</v>
       </c>
     </row>
     <row r="18">
@@ -5358,13 +5358,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C18" t="n">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="D18" t="n">
-        <v>59</v>
+        <v>55</v>
       </c>
     </row>
     <row r="19">
@@ -5372,13 +5372,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C19" t="n">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="D19" t="n">
-        <v>41</v>
+        <v>38</v>
       </c>
     </row>
     <row r="20">
@@ -5389,10 +5389,10 @@
         <v>8</v>
       </c>
       <c r="C20" t="n">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="D20" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
     </row>
     <row r="21">
@@ -5400,13 +5400,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C21" t="n">
-        <v>122</v>
+        <v>106</v>
       </c>
       <c r="D21" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
   </sheetData>
@@ -5445,13 +5445,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5804</v>
+        <v>2159</v>
       </c>
       <c r="C2" t="n">
-        <v>8791</v>
+        <v>6721</v>
       </c>
       <c r="D2" t="n">
-        <v>30660</v>
+        <v>24084</v>
       </c>
     </row>
     <row r="3">
@@ -5459,13 +5459,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4133</v>
+        <v>1125</v>
       </c>
       <c r="C3" t="n">
-        <v>7035</v>
+        <v>4224</v>
       </c>
       <c r="D3" t="n">
-        <v>11941</v>
+        <v>8833</v>
       </c>
     </row>
     <row r="4">
@@ -5473,13 +5473,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2543</v>
+        <v>956</v>
       </c>
       <c r="C4" t="n">
-        <v>4132</v>
+        <v>4310</v>
       </c>
       <c r="D4" t="n">
-        <v>3600</v>
+        <v>2895</v>
       </c>
     </row>
     <row r="5">
@@ -5487,13 +5487,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1111</v>
+        <v>463</v>
       </c>
       <c r="C5" t="n">
-        <v>2203</v>
+        <v>2452</v>
       </c>
       <c r="D5" t="n">
-        <v>1395</v>
+        <v>1256</v>
       </c>
     </row>
     <row r="6">
@@ -5501,13 +5501,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>295</v>
+        <v>154</v>
       </c>
       <c r="C6" t="n">
-        <v>548</v>
+        <v>640</v>
       </c>
       <c r="D6" t="n">
-        <v>946</v>
+        <v>842</v>
       </c>
     </row>
     <row r="7">
@@ -5515,13 +5515,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>145</v>
+        <v>107</v>
       </c>
       <c r="C7" t="n">
-        <v>354</v>
+        <v>293</v>
       </c>
       <c r="D7" t="n">
-        <v>662</v>
+        <v>578</v>
       </c>
     </row>
     <row r="8">
@@ -5529,13 +5529,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>128</v>
+        <v>94</v>
       </c>
       <c r="C8" t="n">
-        <v>380</v>
+        <v>307</v>
       </c>
       <c r="D8" t="n">
-        <v>480</v>
+        <v>431</v>
       </c>
     </row>
     <row r="9">
@@ -5543,13 +5543,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>96</v>
+        <v>72</v>
       </c>
       <c r="C9" t="n">
-        <v>306</v>
+        <v>251</v>
       </c>
       <c r="D9" t="n">
-        <v>381</v>
+        <v>339</v>
       </c>
     </row>
     <row r="10">
@@ -5557,13 +5557,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>70</v>
+        <v>53</v>
       </c>
       <c r="C10" t="n">
-        <v>236</v>
+        <v>194</v>
       </c>
       <c r="D10" t="n">
-        <v>342</v>
+        <v>310</v>
       </c>
     </row>
     <row r="11">
@@ -5571,13 +5571,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>49</v>
+        <v>38</v>
       </c>
       <c r="C11" t="n">
-        <v>189</v>
+        <v>160</v>
       </c>
       <c r="D11" t="n">
-        <v>286</v>
+        <v>257</v>
       </c>
     </row>
     <row r="12">
@@ -5585,13 +5585,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="C12" t="n">
-        <v>156</v>
+        <v>134</v>
       </c>
       <c r="D12" t="n">
-        <v>217</v>
+        <v>199</v>
       </c>
     </row>
     <row r="13">
@@ -5599,13 +5599,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="C13" t="n">
-        <v>128</v>
+        <v>108</v>
       </c>
       <c r="D13" t="n">
-        <v>176</v>
+        <v>159</v>
       </c>
     </row>
     <row r="14">
@@ -5613,13 +5613,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C14" t="n">
-        <v>100</v>
+        <v>86</v>
       </c>
       <c r="D14" t="n">
-        <v>148</v>
+        <v>135</v>
       </c>
     </row>
     <row r="15">
@@ -5627,13 +5627,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C15" t="n">
-        <v>80</v>
+        <v>72</v>
       </c>
       <c r="D15" t="n">
-        <v>122</v>
+        <v>114</v>
       </c>
     </row>
     <row r="16">
@@ -5641,13 +5641,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C16" t="n">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="D16" t="n">
-        <v>100</v>
+        <v>91</v>
       </c>
     </row>
     <row r="17">
@@ -5655,13 +5655,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C17" t="n">
-        <v>69</v>
+        <v>62</v>
       </c>
       <c r="D17" t="n">
-        <v>79</v>
+        <v>76</v>
       </c>
     </row>
     <row r="18">
@@ -5669,13 +5669,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C18" t="n">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="D18" t="n">
-        <v>60</v>
+        <v>56</v>
       </c>
     </row>
     <row r="19">
@@ -5683,13 +5683,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C19" t="n">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="D19" t="n">
-        <v>41</v>
+        <v>38</v>
       </c>
     </row>
     <row r="20">
@@ -5700,10 +5700,10 @@
         <v>7</v>
       </c>
       <c r="C20" t="n">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="D20" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
     </row>
     <row r="21">
@@ -5711,13 +5711,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="C21" t="n">
-        <v>137</v>
+        <v>120</v>
       </c>
       <c r="D21" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
     </row>
   </sheetData>
@@ -5756,13 +5756,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7595</v>
+        <v>2195</v>
       </c>
       <c r="C2" t="n">
-        <v>8395</v>
+        <v>6686</v>
       </c>
       <c r="D2" t="n">
-        <v>27765</v>
+        <v>26877</v>
       </c>
     </row>
     <row r="3">
@@ -5770,13 +5770,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3627</v>
+        <v>1327</v>
       </c>
       <c r="C3" t="n">
-        <v>6488</v>
+        <v>4808</v>
       </c>
       <c r="D3" t="n">
-        <v>13120</v>
+        <v>10529</v>
       </c>
     </row>
     <row r="4">
@@ -5784,13 +5784,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2042</v>
+        <v>899</v>
       </c>
       <c r="C4" t="n">
-        <v>4635</v>
+        <v>4173</v>
       </c>
       <c r="D4" t="n">
-        <v>4375</v>
+        <v>3862</v>
       </c>
     </row>
     <row r="5">
@@ -5798,13 +5798,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>942</v>
+        <v>609</v>
       </c>
       <c r="C5" t="n">
-        <v>2340</v>
+        <v>3358</v>
       </c>
       <c r="D5" t="n">
-        <v>1393</v>
+        <v>1516</v>
       </c>
     </row>
     <row r="6">
@@ -5812,13 +5812,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>331</v>
+        <v>273</v>
       </c>
       <c r="C6" t="n">
-        <v>915</v>
+        <v>1572</v>
       </c>
       <c r="D6" t="n">
-        <v>778</v>
+        <v>893</v>
       </c>
     </row>
     <row r="7">
@@ -5826,13 +5826,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>95</v>
+        <v>119</v>
       </c>
       <c r="C7" t="n">
-        <v>287</v>
+        <v>469</v>
       </c>
       <c r="D7" t="n">
-        <v>514</v>
+        <v>618</v>
       </c>
     </row>
     <row r="8">
@@ -5840,13 +5840,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>57</v>
+        <v>92</v>
       </c>
       <c r="C8" t="n">
-        <v>224</v>
+        <v>300</v>
       </c>
       <c r="D8" t="n">
-        <v>361</v>
+        <v>451</v>
       </c>
     </row>
     <row r="9">
@@ -5854,13 +5854,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>44</v>
+        <v>75</v>
       </c>
       <c r="C9" t="n">
-        <v>196</v>
+        <v>277</v>
       </c>
       <c r="D9" t="n">
-        <v>274</v>
+        <v>346</v>
       </c>
     </row>
     <row r="10">
@@ -5868,13 +5868,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>30</v>
+        <v>56</v>
       </c>
       <c r="C10" t="n">
-        <v>151</v>
+        <v>219</v>
       </c>
       <c r="D10" t="n">
-        <v>233</v>
+        <v>311</v>
       </c>
     </row>
     <row r="11">
@@ -5882,13 +5882,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>21</v>
+        <v>40</v>
       </c>
       <c r="C11" t="n">
-        <v>114</v>
+        <v>173</v>
       </c>
       <c r="D11" t="n">
-        <v>195</v>
+        <v>262</v>
       </c>
     </row>
     <row r="12">
@@ -5896,13 +5896,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="C12" t="n">
-        <v>91</v>
+        <v>144</v>
       </c>
       <c r="D12" t="n">
-        <v>147</v>
+        <v>202</v>
       </c>
     </row>
     <row r="13">
@@ -5910,13 +5910,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="C13" t="n">
-        <v>73</v>
+        <v>118</v>
       </c>
       <c r="D13" t="n">
-        <v>117</v>
+        <v>162</v>
       </c>
     </row>
     <row r="14">
@@ -5924,13 +5924,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="C14" t="n">
-        <v>57</v>
+        <v>94</v>
       </c>
       <c r="D14" t="n">
-        <v>96</v>
+        <v>136</v>
       </c>
     </row>
     <row r="15">
@@ -5938,13 +5938,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="C15" t="n">
-        <v>45</v>
+        <v>77</v>
       </c>
       <c r="D15" t="n">
-        <v>79</v>
+        <v>114</v>
       </c>
     </row>
     <row r="16">
@@ -5952,13 +5952,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="C16" t="n">
-        <v>38</v>
+        <v>67</v>
       </c>
       <c r="D16" t="n">
-        <v>63</v>
+        <v>92</v>
       </c>
     </row>
     <row r="17">
@@ -5966,13 +5966,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="C17" t="n">
-        <v>35</v>
+        <v>62</v>
       </c>
       <c r="D17" t="n">
-        <v>50</v>
+        <v>76</v>
       </c>
     </row>
     <row r="18">
@@ -5980,13 +5980,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="C18" t="n">
-        <v>32</v>
+        <v>59</v>
       </c>
       <c r="D18" t="n">
-        <v>38</v>
+        <v>56</v>
       </c>
     </row>
     <row r="19">
@@ -5994,13 +5994,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C19" t="n">
-        <v>31</v>
+        <v>56</v>
       </c>
       <c r="D19" t="n">
-        <v>26</v>
+        <v>39</v>
       </c>
     </row>
     <row r="20">
@@ -6008,13 +6008,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C20" t="n">
-        <v>28</v>
+        <v>54</v>
       </c>
       <c r="D20" t="n">
-        <v>15</v>
+        <v>23</v>
       </c>
     </row>
     <row r="21">
@@ -6022,10 +6022,10 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="C21" t="n">
-        <v>75</v>
+        <v>133</v>
       </c>
       <c r="D21" t="n">
         <v>5</v>
@@ -6067,13 +6067,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6682</v>
+        <v>1628</v>
       </c>
       <c r="C2" t="n">
-        <v>4390</v>
+        <v>7540</v>
       </c>
       <c r="D2" t="n">
-        <v>24797</v>
+        <v>27189</v>
       </c>
     </row>
     <row r="3">
@@ -6081,13 +6081,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4642</v>
+        <v>1412</v>
       </c>
       <c r="C3" t="n">
-        <v>6530</v>
+        <v>5011</v>
       </c>
       <c r="D3" t="n">
-        <v>14614</v>
+        <v>12158</v>
       </c>
     </row>
     <row r="4">
@@ -6095,13 +6095,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2476</v>
+        <v>937</v>
       </c>
       <c r="C4" t="n">
-        <v>5641</v>
+        <v>4415</v>
       </c>
       <c r="D4" t="n">
-        <v>6004</v>
+        <v>4859</v>
       </c>
     </row>
     <row r="5">
@@ -6109,13 +6109,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1313</v>
+        <v>663</v>
       </c>
       <c r="C5" t="n">
-        <v>3590</v>
+        <v>3662</v>
       </c>
       <c r="D5" t="n">
-        <v>1909</v>
+        <v>1875</v>
       </c>
     </row>
     <row r="6">
@@ -6123,13 +6123,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>588</v>
+        <v>385</v>
       </c>
       <c r="C6" t="n">
-        <v>1710</v>
+        <v>2429</v>
       </c>
       <c r="D6" t="n">
-        <v>885</v>
+        <v>973</v>
       </c>
     </row>
     <row r="7">
@@ -6137,13 +6137,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>192</v>
+        <v>170</v>
       </c>
       <c r="C7" t="n">
-        <v>637</v>
+        <v>998</v>
       </c>
       <c r="D7" t="n">
-        <v>552</v>
+        <v>657</v>
       </c>
     </row>
     <row r="8">
@@ -6151,13 +6151,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>68</v>
+        <v>96</v>
       </c>
       <c r="C8" t="n">
-        <v>257</v>
+        <v>377</v>
       </c>
       <c r="D8" t="n">
-        <v>385</v>
+        <v>472</v>
       </c>
     </row>
     <row r="9">
@@ -6165,13 +6165,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>46</v>
+        <v>75</v>
       </c>
       <c r="C9" t="n">
-        <v>210</v>
+        <v>284</v>
       </c>
       <c r="D9" t="n">
-        <v>286</v>
+        <v>354</v>
       </c>
     </row>
     <row r="10">
@@ -6179,13 +6179,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>33</v>
+        <v>59</v>
       </c>
       <c r="C10" t="n">
-        <v>173</v>
+        <v>243</v>
       </c>
       <c r="D10" t="n">
-        <v>235</v>
+        <v>312</v>
       </c>
     </row>
     <row r="11">
@@ -6193,13 +6193,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>23</v>
+        <v>42</v>
       </c>
       <c r="C11" t="n">
-        <v>131</v>
+        <v>191</v>
       </c>
       <c r="D11" t="n">
-        <v>199</v>
+        <v>263</v>
       </c>
     </row>
     <row r="12">
@@ -6207,13 +6207,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="C12" t="n">
-        <v>100</v>
+        <v>155</v>
       </c>
       <c r="D12" t="n">
-        <v>153</v>
+        <v>208</v>
       </c>
     </row>
     <row r="13">
@@ -6221,13 +6221,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="C13" t="n">
-        <v>81</v>
+        <v>126</v>
       </c>
       <c r="D13" t="n">
-        <v>119</v>
+        <v>165</v>
       </c>
     </row>
     <row r="14">
@@ -6235,13 +6235,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="C14" t="n">
-        <v>63</v>
+        <v>102</v>
       </c>
       <c r="D14" t="n">
-        <v>98</v>
+        <v>136</v>
       </c>
     </row>
     <row r="15">
@@ -6249,13 +6249,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="C15" t="n">
-        <v>49</v>
+        <v>82</v>
       </c>
       <c r="D15" t="n">
-        <v>80</v>
+        <v>115</v>
       </c>
     </row>
     <row r="16">
@@ -6263,13 +6263,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="C16" t="n">
-        <v>40</v>
+        <v>70</v>
       </c>
       <c r="D16" t="n">
-        <v>63</v>
+        <v>93</v>
       </c>
     </row>
     <row r="17">
@@ -6277,13 +6277,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C17" t="n">
-        <v>36</v>
+        <v>62</v>
       </c>
       <c r="D17" t="n">
-        <v>51</v>
+        <v>76</v>
       </c>
     </row>
     <row r="18">
@@ -6291,13 +6291,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C18" t="n">
-        <v>33</v>
+        <v>59</v>
       </c>
       <c r="D18" t="n">
-        <v>39</v>
+        <v>57</v>
       </c>
     </row>
     <row r="19">
@@ -6305,13 +6305,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="C19" t="n">
-        <v>31</v>
+        <v>56</v>
       </c>
       <c r="D19" t="n">
-        <v>26</v>
+        <v>39</v>
       </c>
     </row>
     <row r="20">
@@ -6319,13 +6319,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="C20" t="n">
-        <v>28</v>
+        <v>54</v>
       </c>
       <c r="D20" t="n">
-        <v>16</v>
+        <v>24</v>
       </c>
     </row>
     <row r="21">
@@ -6333,10 +6333,10 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8</v>
+        <v>21</v>
       </c>
       <c r="C21" t="n">
-        <v>83</v>
+        <v>145</v>
       </c>
       <c r="D21" t="n">
         <v>6</v>
@@ -6378,13 +6378,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5180</v>
+        <v>1518</v>
       </c>
       <c r="C2" t="n">
-        <v>6902</v>
+        <v>4584</v>
       </c>
       <c r="D2" t="n">
-        <v>24147</v>
+        <v>21215</v>
       </c>
     </row>
     <row r="3">
@@ -6392,13 +6392,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4622</v>
+        <v>1784</v>
       </c>
       <c r="C3" t="n">
-        <v>4669</v>
+        <v>7656</v>
       </c>
       <c r="D3" t="n">
-        <v>15191</v>
+        <v>13560</v>
       </c>
     </row>
     <row r="4">
@@ -6406,13 +6406,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3016</v>
+        <v>612</v>
       </c>
       <c r="C4" t="n">
-        <v>6018</v>
+        <v>6355</v>
       </c>
       <c r="D4" t="n">
-        <v>7474</v>
+        <v>4553</v>
       </c>
     </row>
     <row r="5">
@@ -6420,13 +6420,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1658</v>
+        <v>355</v>
       </c>
       <c r="C5" t="n">
-        <v>4617</v>
+        <v>2380</v>
       </c>
       <c r="D5" t="n">
-        <v>2597</v>
+        <v>1511</v>
       </c>
     </row>
     <row r="6">
@@ -6434,13 +6434,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>850</v>
+        <v>157</v>
       </c>
       <c r="C6" t="n">
-        <v>2665</v>
+        <v>978</v>
       </c>
       <c r="D6" t="n">
-        <v>1041</v>
+        <v>643</v>
       </c>
     </row>
     <row r="7">
@@ -6448,13 +6448,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>341</v>
+        <v>88</v>
       </c>
       <c r="C7" t="n">
-        <v>1177</v>
+        <v>369</v>
       </c>
       <c r="D7" t="n">
-        <v>605</v>
+        <v>462</v>
       </c>
     </row>
     <row r="8">
@@ -6462,13 +6462,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>111</v>
+        <v>69</v>
       </c>
       <c r="C8" t="n">
-        <v>446</v>
+        <v>278</v>
       </c>
       <c r="D8" t="n">
-        <v>405</v>
+        <v>346</v>
       </c>
     </row>
     <row r="9">
@@ -6476,13 +6476,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="C9" t="n">
-        <v>232</v>
+        <v>238</v>
       </c>
       <c r="D9" t="n">
-        <v>299</v>
+        <v>305</v>
       </c>
     </row>
     <row r="10">
@@ -6490,13 +6490,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="C10" t="n">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="D10" t="n">
-        <v>240</v>
+        <v>257</v>
       </c>
     </row>
     <row r="11">
@@ -6504,13 +6504,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="C11" t="n">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="D11" t="n">
-        <v>200</v>
+        <v>203</v>
       </c>
     </row>
     <row r="12">
@@ -6518,13 +6518,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C12" t="n">
-        <v>113</v>
+        <v>123</v>
       </c>
       <c r="D12" t="n">
-        <v>158</v>
+        <v>161</v>
       </c>
     </row>
     <row r="13">
@@ -6535,10 +6535,10 @@
         <v>11</v>
       </c>
       <c r="C13" t="n">
-        <v>88</v>
+        <v>99</v>
       </c>
       <c r="D13" t="n">
-        <v>121</v>
+        <v>133</v>
       </c>
     </row>
     <row r="14">
@@ -6546,13 +6546,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C14" t="n">
-        <v>69</v>
+        <v>80</v>
       </c>
       <c r="D14" t="n">
-        <v>99</v>
+        <v>112</v>
       </c>
     </row>
     <row r="15">
@@ -6560,13 +6560,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C15" t="n">
-        <v>54</v>
+        <v>68</v>
       </c>
       <c r="D15" t="n">
-        <v>81</v>
+        <v>91</v>
       </c>
     </row>
     <row r="16">
@@ -6574,13 +6574,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C16" t="n">
-        <v>43</v>
+        <v>60</v>
       </c>
       <c r="D16" t="n">
-        <v>63</v>
+        <v>74</v>
       </c>
     </row>
     <row r="17">
@@ -6588,13 +6588,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C17" t="n">
-        <v>37</v>
+        <v>57</v>
       </c>
       <c r="D17" t="n">
-        <v>51</v>
+        <v>55</v>
       </c>
     </row>
     <row r="18">
@@ -6602,13 +6602,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C18" t="n">
-        <v>33</v>
+        <v>54</v>
       </c>
       <c r="D18" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="19">
@@ -6616,13 +6616,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C19" t="n">
-        <v>31</v>
+        <v>52</v>
       </c>
       <c r="D19" t="n">
-        <v>27</v>
+        <v>23</v>
       </c>
     </row>
     <row r="20">
@@ -6630,13 +6630,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="C20" t="n">
-        <v>28</v>
+        <v>145</v>
       </c>
       <c r="D20" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
     </row>
     <row r="21">
@@ -6644,13 +6644,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>90</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
